--- a/studies/case_study_bachelor_thesis/results/Case_study_results_MC_mean.xlsx
+++ b/studies/case_study_bachelor_thesis/results/Case_study_results_MC_mean.xlsx
@@ -630,88 +630,88 @@
         <v>2020</v>
       </c>
       <c r="B2">
-        <v>99.65929135075932</v>
+        <v>100.6403865688288</v>
       </c>
       <c r="C2">
-        <v>5.370349517179254</v>
+        <v>4.056962783841528</v>
       </c>
       <c r="D2">
-        <v>50.01829104151307</v>
+        <v>50.0336253681736</v>
       </c>
       <c r="E2">
-        <v>3.440149426168108</v>
+        <v>2.584793726329579</v>
       </c>
       <c r="F2">
-        <v>49.64100030924627</v>
+        <v>50.60676120065523</v>
       </c>
       <c r="G2">
-        <v>3.401724306546281</v>
+        <v>2.662599466909347</v>
       </c>
       <c r="H2">
-        <v>14.9351582288041</v>
+        <v>15.08489566962486</v>
       </c>
       <c r="I2">
-        <v>0.9993194706263422</v>
+        <v>0.8885442635143215</v>
       </c>
       <c r="J2">
-        <v>14.877324454353</v>
+        <v>15.20631614824232</v>
       </c>
       <c r="K2">
-        <v>1.353715535680051</v>
+        <v>1.191010779202271</v>
       </c>
       <c r="L2">
-        <v>4.937575416233701</v>
+        <v>5.160675200272165</v>
       </c>
       <c r="M2">
-        <v>0.4686255178028998</v>
+        <v>0.453364169885097</v>
       </c>
       <c r="N2">
-        <v>9.944810057922803</v>
+        <v>10.08444457704735</v>
       </c>
       <c r="O2">
-        <v>0.8110045184583866</v>
+        <v>0.6793821805808953</v>
       </c>
       <c r="P2">
-        <v>4.94613215193266</v>
+        <v>5.070429605468534</v>
       </c>
       <c r="Q2">
-        <v>0.5186043960364086</v>
+        <v>0.4313717702867806</v>
       </c>
       <c r="R2">
-        <v>14.9351582288041</v>
+        <v>15.08489566962486</v>
       </c>
       <c r="S2">
-        <v>0.9993194706263422</v>
+        <v>0.8885442635143215</v>
       </c>
       <c r="T2">
-        <v>10.4264353236929</v>
+        <v>10.63308157967123</v>
       </c>
       <c r="U2">
-        <v>0.9565564255656037</v>
+        <v>0.8615662173317238</v>
       </c>
       <c r="V2">
-        <v>2.218285568490615</v>
+        <v>2.300401236674583</v>
       </c>
       <c r="W2">
-        <v>0.2798004788920362</v>
+        <v>0.2687353349647911</v>
       </c>
       <c r="X2">
-        <v>2.232603562169483</v>
+        <v>2.272833331896503</v>
       </c>
       <c r="Y2">
-        <v>0.2821736521231317</v>
+        <v>0.2592255986680573</v>
       </c>
       <c r="Z2">
-        <v>4.937575416233701</v>
+        <v>5.160675200272165</v>
       </c>
       <c r="AA2">
-        <v>0.4686255178028998</v>
+        <v>0.453364169885097</v>
       </c>
       <c r="AB2">
-        <v>9.944810057922803</v>
+        <v>10.08444457704735</v>
       </c>
       <c r="AC2">
-        <v>0.8110045184583866</v>
+        <v>0.6793821805808953</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -725,94 +725,94 @@
         <v>2021</v>
       </c>
       <c r="B3">
-        <v>111.0108347237785</v>
+        <v>109.707197948252</v>
       </c>
       <c r="C3">
-        <v>5.073970333571842</v>
+        <v>5.600001281764813</v>
       </c>
       <c r="D3">
-        <v>55.8881713556068</v>
+        <v>54.88528218102728</v>
       </c>
       <c r="E3">
-        <v>3.779937685649497</v>
+        <v>3.814345276896495</v>
       </c>
       <c r="F3">
-        <v>55.12266336817164</v>
+        <v>54.8219157672247</v>
       </c>
       <c r="G3">
-        <v>2.736263378021224</v>
+        <v>3.337221790741664</v>
       </c>
       <c r="H3">
-        <v>16.32668540476753</v>
+        <v>16.50556507218209</v>
       </c>
       <c r="I3">
-        <v>1.035924851940982</v>
+        <v>1.17480551694136</v>
       </c>
       <c r="J3">
-        <v>16.61726585231726</v>
+        <v>16.41047995979266</v>
       </c>
       <c r="K3">
-        <v>1.235151805418875</v>
+        <v>1.349135753726936</v>
       </c>
       <c r="L3">
-        <v>5.474957459082651</v>
+        <v>5.488499033788274</v>
       </c>
       <c r="M3">
-        <v>0.3675929624336128</v>
+        <v>0.4685944001703194</v>
       </c>
       <c r="N3">
-        <v>11.06781920911673</v>
+        <v>10.93911938527347</v>
       </c>
       <c r="O3">
-        <v>0.7199697209255199</v>
+        <v>0.8297115254532789</v>
       </c>
       <c r="P3">
-        <v>5.635935442887479</v>
+        <v>5.478252316188206</v>
       </c>
       <c r="Q3">
-        <v>0.4457024004850813</v>
+        <v>0.4238342256434968</v>
       </c>
       <c r="R3">
-        <v>16.32668540476753</v>
+        <v>16.50556507218209</v>
       </c>
       <c r="S3">
-        <v>1.035924851940982</v>
+        <v>1.17480551694136</v>
       </c>
       <c r="T3">
-        <v>11.57310212909792</v>
+        <v>11.44836149977372</v>
       </c>
       <c r="U3">
-        <v>0.8476140821985769</v>
+        <v>1.06037475863937</v>
       </c>
       <c r="V3">
-        <v>2.52494133796541</v>
+        <v>2.488658157901453</v>
       </c>
       <c r="W3">
-        <v>0.2860964983120027</v>
+        <v>0.2622986861775511</v>
       </c>
       <c r="X3">
-        <v>2.519222385253921</v>
+        <v>2.473460302117485</v>
       </c>
       <c r="Y3">
-        <v>0.301669293607653</v>
+        <v>0.2705255710472279</v>
       </c>
       <c r="Z3">
-        <v>5.474957459082651</v>
+        <v>5.488499033788274</v>
       </c>
       <c r="AA3">
-        <v>0.3675929624336128</v>
+        <v>0.4685944001703194</v>
       </c>
       <c r="AB3">
-        <v>11.06781920911673</v>
+        <v>10.93911938527347</v>
       </c>
       <c r="AC3">
-        <v>0.7199697209255199</v>
+        <v>0.8297115254532789</v>
       </c>
       <c r="AD3">
-        <v>8.432478015182891</v>
+        <v>8.145441325734485</v>
       </c>
       <c r="AE3">
-        <v>0.732956966255864</v>
+        <v>0.6854890023616238</v>
       </c>
     </row>
     <row r="4" spans="1:31">
@@ -820,94 +820,94 @@
         <v>2022</v>
       </c>
       <c r="B4">
-        <v>120.3860901813022</v>
+        <v>121.1751965132662</v>
       </c>
       <c r="C4">
-        <v>6.047896088148898</v>
+        <v>5.242792029086821</v>
       </c>
       <c r="D4">
-        <v>60.13697746945844</v>
+        <v>60.39157475059026</v>
       </c>
       <c r="E4">
-        <v>3.588374917452811</v>
+        <v>3.08948858569708</v>
       </c>
       <c r="F4">
-        <v>60.2491127118438</v>
+        <v>60.78362176267596</v>
       </c>
       <c r="G4">
-        <v>3.702132938718513</v>
+        <v>3.32012347839391</v>
       </c>
       <c r="H4">
-        <v>18.24536687071804</v>
+        <v>18.36650353140548</v>
       </c>
       <c r="I4">
-        <v>1.18522159275431</v>
+        <v>1.36063057102117</v>
       </c>
       <c r="J4">
-        <v>18.21717052542595</v>
+        <v>18.3170618892905</v>
       </c>
       <c r="K4">
-        <v>1.326718204096044</v>
+        <v>1.248207508997669</v>
       </c>
       <c r="L4">
-        <v>5.905198449691945</v>
+        <v>5.908768465629979</v>
       </c>
       <c r="M4">
-        <v>0.6076073420637319</v>
+        <v>0.5080695878834797</v>
       </c>
       <c r="N4">
-        <v>11.95271126012129</v>
+        <v>12.1479269865022</v>
       </c>
       <c r="O4">
-        <v>0.8928293942683135</v>
+        <v>0.7495047471716796</v>
       </c>
       <c r="P4">
-        <v>5.92866560588659</v>
+        <v>6.043360889847785</v>
       </c>
       <c r="Q4">
-        <v>0.5900786522873195</v>
+        <v>0.5353084161761348</v>
       </c>
       <c r="R4">
-        <v>18.24536687071804</v>
+        <v>18.36650353140548</v>
       </c>
       <c r="S4">
-        <v>1.18522159275431</v>
+        <v>1.36063057102117</v>
       </c>
       <c r="T4">
-        <v>12.68771883024843</v>
+        <v>13.00125974533451</v>
       </c>
       <c r="U4">
-        <v>1.039591036207337</v>
+        <v>0.9175246200953349</v>
       </c>
       <c r="V4">
-        <v>2.758486190679132</v>
+        <v>2.672638853686346</v>
       </c>
       <c r="W4">
-        <v>0.2996221365045205</v>
+        <v>0.3302600471623399</v>
       </c>
       <c r="X4">
-        <v>2.770965504498378</v>
+        <v>2.643163290269645</v>
       </c>
       <c r="Y4">
-        <v>0.3115786942876588</v>
+        <v>0.3186622331203489</v>
       </c>
       <c r="Z4">
-        <v>5.905198449691945</v>
+        <v>5.908768465629979</v>
       </c>
       <c r="AA4">
-        <v>0.6076073420637319</v>
+        <v>0.5080695878834797</v>
       </c>
       <c r="AB4">
-        <v>11.95271126012129</v>
+        <v>12.1479269865022</v>
       </c>
       <c r="AC4">
-        <v>0.8928293942683135</v>
+        <v>0.7495047471716796</v>
       </c>
       <c r="AD4">
-        <v>12.03977937623752</v>
+        <v>11.78263359053208</v>
       </c>
       <c r="AE4">
-        <v>0.6911221910382833</v>
+        <v>0.6910499037910857</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -915,94 +915,94 @@
         <v>2023</v>
       </c>
       <c r="B5">
-        <v>131.3778941296251</v>
+        <v>131.2054100305348</v>
       </c>
       <c r="C5">
-        <v>6.483655566038395</v>
+        <v>8.116993265021959</v>
       </c>
       <c r="D5">
-        <v>65.35264196351619</v>
+        <v>65.37674470455526</v>
       </c>
       <c r="E5">
-        <v>4.421814173181794</v>
+        <v>4.383919590805982</v>
       </c>
       <c r="F5">
-        <v>66.02525216610881</v>
+        <v>65.82866532597947</v>
       </c>
       <c r="G5">
-        <v>3.813503197860028</v>
+        <v>5.043569035986869</v>
       </c>
       <c r="H5">
-        <v>19.8948830692408</v>
+        <v>19.79027532300575</v>
       </c>
       <c r="I5">
-        <v>1.624391614302522</v>
+        <v>1.852285994619337</v>
       </c>
       <c r="J5">
-        <v>19.88544717137408</v>
+        <v>19.67884467846289</v>
       </c>
       <c r="K5">
-        <v>1.417219231003413</v>
+        <v>1.710560976693991</v>
       </c>
       <c r="L5">
-        <v>6.523602912725925</v>
+        <v>6.582455009570723</v>
       </c>
       <c r="M5">
-        <v>0.5578460381172156</v>
+        <v>0.5536533763419272</v>
       </c>
       <c r="N5">
-        <v>13.19862464833586</v>
+        <v>13.16358045612916</v>
       </c>
       <c r="O5">
-        <v>0.9400065305691808</v>
+        <v>1.159109180215018</v>
       </c>
       <c r="P5">
-        <v>6.52269436443217</v>
+        <v>6.613509858810958</v>
       </c>
       <c r="Q5">
-        <v>0.5334991507131777</v>
+        <v>0.6497249480812332</v>
       </c>
       <c r="R5">
-        <v>19.8948830692408</v>
+        <v>19.79027532300575</v>
       </c>
       <c r="S5">
-        <v>1.624391614302522</v>
+        <v>1.852285994619337</v>
       </c>
       <c r="T5">
-        <v>13.91927429608681</v>
+        <v>13.69548413625282</v>
       </c>
       <c r="U5">
-        <v>1.035530010259855</v>
+        <v>1.381058060463542</v>
       </c>
       <c r="V5">
-        <v>2.957123585283505</v>
+        <v>2.986019621453599</v>
       </c>
       <c r="W5">
-        <v>0.3881326844320035</v>
+        <v>0.3016099263224518</v>
       </c>
       <c r="X5">
-        <v>3.009049290003767</v>
+        <v>2.997340920756467</v>
       </c>
       <c r="Y5">
-        <v>0.347677936798344</v>
+        <v>0.3057035537517128</v>
       </c>
       <c r="Z5">
-        <v>6.523602912725925</v>
+        <v>6.582455009570723</v>
       </c>
       <c r="AA5">
-        <v>0.5578460381172156</v>
+        <v>0.5536533763419272</v>
       </c>
       <c r="AB5">
-        <v>13.19862464833586</v>
+        <v>13.16358045612916</v>
       </c>
       <c r="AC5">
-        <v>0.9400065305691808</v>
+        <v>1.159109180215018</v>
       </c>
       <c r="AD5">
-        <v>14.16159562427607</v>
+        <v>13.92010459445073</v>
       </c>
       <c r="AE5">
-        <v>0.7471464226910715</v>
+        <v>0.8105229448820823</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -1010,94 +1010,94 @@
         <v>2024</v>
       </c>
       <c r="B6">
-        <v>140.7517141766136</v>
+        <v>138.4781808844324</v>
       </c>
       <c r="C6">
-        <v>7.102574820046908</v>
+        <v>6.608691183778803</v>
       </c>
       <c r="D6">
-        <v>69.97096129877912</v>
+        <v>69.22265045851476</v>
       </c>
       <c r="E6">
-        <v>4.131067040066861</v>
+        <v>3.861725991315873</v>
       </c>
       <c r="F6">
-        <v>70.78075287783447</v>
+        <v>69.25553042591753</v>
       </c>
       <c r="G6">
-        <v>4.319818410281661</v>
+        <v>4.032105200116379</v>
       </c>
       <c r="H6">
-        <v>21.35138751221885</v>
+        <v>20.80213024661373</v>
       </c>
       <c r="I6">
-        <v>1.652527534639696</v>
+        <v>1.514020549337848</v>
       </c>
       <c r="J6">
-        <v>21.1056822443614</v>
+        <v>20.69399521361503</v>
       </c>
       <c r="K6">
-        <v>1.3895124083286</v>
+        <v>1.611685415482329</v>
       </c>
       <c r="L6">
-        <v>7.055588197206814</v>
+        <v>6.893885716448566</v>
       </c>
       <c r="M6">
-        <v>0.6407676187261481</v>
+        <v>0.5883234689141176</v>
       </c>
       <c r="N6">
-        <v>14.11605532127795</v>
+        <v>13.93201632147551</v>
       </c>
       <c r="O6">
-        <v>0.9960396243365772</v>
+        <v>0.9756411007417036</v>
       </c>
       <c r="P6">
-        <v>7.152039602769468</v>
+        <v>6.9335029277647</v>
       </c>
       <c r="Q6">
-        <v>0.7123056696959089</v>
+        <v>0.6194686978181358</v>
       </c>
       <c r="R6">
-        <v>21.35138751221885</v>
+        <v>20.80213024661373</v>
       </c>
       <c r="S6">
-        <v>1.652527534639696</v>
+        <v>1.514020549337848</v>
       </c>
       <c r="T6">
-        <v>14.71089692372784</v>
+        <v>14.56260082834332</v>
       </c>
       <c r="U6">
-        <v>1.089295984971314</v>
+        <v>1.179844489639878</v>
       </c>
       <c r="V6">
-        <v>3.1934275140428</v>
+        <v>3.05772223964645</v>
       </c>
       <c r="W6">
-        <v>0.3443206762476778</v>
+        <v>0.3395007362303014</v>
       </c>
       <c r="X6">
-        <v>3.201357806590762</v>
+        <v>3.07367214562526</v>
       </c>
       <c r="Y6">
-        <v>0.3854500132017702</v>
+        <v>0.3624294001673468</v>
       </c>
       <c r="Z6">
-        <v>7.055588197206814</v>
+        <v>6.893885716448566</v>
       </c>
       <c r="AA6">
-        <v>0.6407676187261481</v>
+        <v>0.5883234689141176</v>
       </c>
       <c r="AB6">
-        <v>14.11605532127795</v>
+        <v>13.93201632147551</v>
       </c>
       <c r="AC6">
-        <v>0.9960396243365772</v>
+        <v>0.9756411007417036</v>
       </c>
       <c r="AD6">
-        <v>15.71994171008613</v>
+        <v>15.54900028584319</v>
       </c>
       <c r="AE6">
-        <v>0.7530791221794212</v>
+        <v>0.6958198363738696</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -1105,94 +1105,94 @@
         <v>2025</v>
       </c>
       <c r="B7">
-        <v>149.9070611186919</v>
+        <v>149.5579464704375</v>
       </c>
       <c r="C7">
-        <v>8.069727511933744</v>
+        <v>7.747688827093858</v>
       </c>
       <c r="D7">
-        <v>75.5021616446129</v>
+        <v>74.823240145325</v>
       </c>
       <c r="E7">
-        <v>4.321379384286475</v>
+        <v>4.561285773060686</v>
       </c>
       <c r="F7">
-        <v>74.40489947407896</v>
+        <v>74.73470632511253</v>
       </c>
       <c r="G7">
-        <v>5.294286599641778</v>
+        <v>4.532882862286606</v>
       </c>
       <c r="H7">
-        <v>22.32006637369019</v>
+        <v>22.40833719967301</v>
       </c>
       <c r="I7">
-        <v>1.973865068765267</v>
+        <v>1.525767013042533</v>
       </c>
       <c r="J7">
-        <v>22.29311717276881</v>
+        <v>22.37818528454978</v>
       </c>
       <c r="K7">
-        <v>1.643419441038765</v>
+        <v>1.775687821594246</v>
       </c>
       <c r="L7">
-        <v>7.463714251615519</v>
+        <v>7.528236486663773</v>
       </c>
       <c r="M7">
-        <v>0.7342468435036472</v>
+        <v>0.644694569565913</v>
       </c>
       <c r="N7">
-        <v>14.90591753007235</v>
+        <v>14.9731836614055</v>
       </c>
       <c r="O7">
-        <v>1.222089748645675</v>
+        <v>1.189332554976774</v>
       </c>
       <c r="P7">
-        <v>7.422084145932107</v>
+        <v>7.446763692820443</v>
       </c>
       <c r="Q7">
-        <v>0.7385067320001737</v>
+        <v>0.648819439345996</v>
       </c>
       <c r="R7">
-        <v>22.32006637369019</v>
+        <v>22.40833719967301</v>
       </c>
       <c r="S7">
-        <v>1.973865068765267</v>
+        <v>1.525767013042533</v>
       </c>
       <c r="T7">
-        <v>15.61451174930572</v>
+        <v>15.5773265123503</v>
       </c>
       <c r="U7">
-        <v>1.223707912553136</v>
+        <v>1.466430837235251</v>
       </c>
       <c r="V7">
-        <v>3.286291536630631</v>
+        <v>3.431613274974648</v>
       </c>
       <c r="W7">
-        <v>0.3679864905703745</v>
+        <v>0.4500020557153877</v>
       </c>
       <c r="X7">
-        <v>3.392313886832446</v>
+        <v>3.36924549722484</v>
       </c>
       <c r="Y7">
-        <v>0.344340229146733</v>
+        <v>0.4262868247239823</v>
       </c>
       <c r="Z7">
-        <v>7.463714251615519</v>
+        <v>7.528236486663773</v>
       </c>
       <c r="AA7">
-        <v>0.7342468435036472</v>
+        <v>0.644694569565913</v>
       </c>
       <c r="AB7">
-        <v>14.90591753007235</v>
+        <v>14.9731836614055</v>
       </c>
       <c r="AC7">
-        <v>1.222089748645675</v>
+        <v>1.189332554976774</v>
       </c>
       <c r="AD7">
-        <v>17.1618417115429</v>
+        <v>17.03407692948743</v>
       </c>
       <c r="AE7">
-        <v>0.8072314226524555</v>
+        <v>0.8602674710753158</v>
       </c>
     </row>
     <row r="8" spans="1:31">
@@ -1200,94 +1200,94 @@
         <v>2026</v>
       </c>
       <c r="B8">
-        <v>161.3508438070665</v>
+        <v>159.7501370621347</v>
       </c>
       <c r="C8">
-        <v>7.169539943821018</v>
+        <v>7.193633993623568</v>
       </c>
       <c r="D8">
-        <v>80.74585004836531</v>
+        <v>79.60134766598752</v>
       </c>
       <c r="E8">
-        <v>4.403476841683715</v>
+        <v>4.317286795918008</v>
       </c>
       <c r="F8">
-        <v>80.60499375870114</v>
+        <v>80.14878939614718</v>
       </c>
       <c r="G8">
-        <v>4.692669551631326</v>
+        <v>5.00926148249895</v>
       </c>
       <c r="H8">
-        <v>24.35966510072809</v>
+        <v>24.12774684780427</v>
       </c>
       <c r="I8">
-        <v>1.801330904274815</v>
+        <v>1.703010218489755</v>
       </c>
       <c r="J8">
-        <v>24.14787456943647</v>
+        <v>23.85187516977221</v>
       </c>
       <c r="K8">
-        <v>1.896608405151086</v>
+        <v>1.707668321206136</v>
       </c>
       <c r="L8">
-        <v>8.024501500706497</v>
+        <v>7.978557593855401</v>
       </c>
       <c r="M8">
-        <v>0.6193885540636963</v>
+        <v>0.722326357597139</v>
       </c>
       <c r="N8">
-        <v>16.1024669020996</v>
+        <v>16.05313539791384</v>
       </c>
       <c r="O8">
-        <v>1.216421307968362</v>
+        <v>1.436900858796063</v>
       </c>
       <c r="P8">
-        <v>7.970485685730497</v>
+        <v>8.137474386801449</v>
       </c>
       <c r="Q8">
-        <v>0.6044464662983786</v>
+        <v>0.6179138987464504</v>
       </c>
       <c r="R8">
-        <v>24.35966510072809</v>
+        <v>24.12774684780427</v>
       </c>
       <c r="S8">
-        <v>1.801330904274815</v>
+        <v>1.703010218489755</v>
       </c>
       <c r="T8">
-        <v>16.67074091080441</v>
+        <v>16.77989045898098</v>
       </c>
       <c r="U8">
-        <v>1.352384241714857</v>
+        <v>1.112161779695143</v>
       </c>
       <c r="V8">
-        <v>3.736239496560366</v>
+        <v>3.52887461659744</v>
       </c>
       <c r="W8">
-        <v>0.3722814744725848</v>
+        <v>0.4442198839518614</v>
       </c>
       <c r="X8">
-        <v>3.740894162071686</v>
+        <v>3.543110094193791</v>
       </c>
       <c r="Y8">
-        <v>0.427375410799588</v>
+        <v>0.471740909670426</v>
       </c>
       <c r="Z8">
-        <v>8.024501500706497</v>
+        <v>7.978557593855401</v>
       </c>
       <c r="AA8">
-        <v>0.6193885540636963</v>
+        <v>0.722326357597139</v>
       </c>
       <c r="AB8">
-        <v>16.1024669020996</v>
+        <v>16.05313539791384</v>
       </c>
       <c r="AC8">
-        <v>1.216421307968362</v>
+        <v>1.436900858796063</v>
       </c>
       <c r="AD8">
-        <v>18.49086229811295</v>
+        <v>18.49376550815364</v>
       </c>
       <c r="AE8">
-        <v>0.8866091548176133</v>
+        <v>0.7392438033404323</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -1295,94 +1295,94 @@
         <v>2027</v>
       </c>
       <c r="B9">
-        <v>171.7597659598013</v>
+        <v>169.5359863310549</v>
       </c>
       <c r="C9">
-        <v>8.089696683764892</v>
+        <v>7.840530835392824</v>
       </c>
       <c r="D9">
-        <v>86.24183332126397</v>
+        <v>84.79233301725377</v>
       </c>
       <c r="E9">
-        <v>4.586001308598784</v>
+        <v>5.35509961237626</v>
       </c>
       <c r="F9">
-        <v>85.51793263853735</v>
+        <v>84.74365331380109</v>
       </c>
       <c r="G9">
-        <v>4.993995697795954</v>
+        <v>4.535013010975676</v>
       </c>
       <c r="H9">
-        <v>25.53836985563269</v>
+        <v>25.36977774331421</v>
       </c>
       <c r="I9">
-        <v>1.657450471646909</v>
+        <v>1.533188030931857</v>
       </c>
       <c r="J9">
-        <v>25.61274215628388</v>
+        <v>25.54364833262409</v>
       </c>
       <c r="K9">
-        <v>1.56783777059093</v>
+        <v>1.793031214792107</v>
       </c>
       <c r="L9">
-        <v>8.632804064330818</v>
+        <v>8.385549846478147</v>
       </c>
       <c r="M9">
-        <v>0.7157112401403799</v>
+        <v>0.642754223566259</v>
       </c>
       <c r="N9">
-        <v>17.06296113700017</v>
+        <v>16.95300152578353</v>
       </c>
       <c r="O9">
-        <v>1.454097009617309</v>
+        <v>1.297492715672742</v>
       </c>
       <c r="P9">
-        <v>8.671055425289774</v>
+        <v>8.491675865601144</v>
       </c>
       <c r="Q9">
-        <v>0.7161060926805919</v>
+        <v>0.735242053870342</v>
       </c>
       <c r="R9">
-        <v>25.53836985563269</v>
+        <v>25.36977774331421</v>
       </c>
       <c r="S9">
-        <v>1.657450471646909</v>
+        <v>1.533188030931857</v>
       </c>
       <c r="T9">
-        <v>17.82328961807612</v>
+        <v>17.9113844028785</v>
       </c>
       <c r="U9">
-        <v>1.386996863124921</v>
+        <v>1.420529097958285</v>
       </c>
       <c r="V9">
-        <v>3.890769114690414</v>
+        <v>3.801067256639805</v>
       </c>
       <c r="W9">
-        <v>0.3591588467304866</v>
+        <v>0.4121490534573972</v>
       </c>
       <c r="X9">
-        <v>3.89868342351734</v>
+        <v>3.83119667310576</v>
       </c>
       <c r="Y9">
-        <v>0.312653510220951</v>
+        <v>0.4549782963768986</v>
       </c>
       <c r="Z9">
-        <v>8.632804064330818</v>
+        <v>8.385549846478147</v>
       </c>
       <c r="AA9">
-        <v>0.7157112401403799</v>
+        <v>0.642754223566259</v>
       </c>
       <c r="AB9">
-        <v>17.06296113700017</v>
+        <v>16.95300152578353</v>
       </c>
       <c r="AC9">
-        <v>1.454097009617309</v>
+        <v>1.297492715672742</v>
       </c>
       <c r="AD9">
-        <v>19.83105514796485</v>
+        <v>19.78024101673869</v>
       </c>
       <c r="AE9">
-        <v>0.7962594059248428</v>
+        <v>0.9821075683319498</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -1390,94 +1390,94 @@
         <v>2028</v>
       </c>
       <c r="B10">
-        <v>179.254037270706</v>
+        <v>179.5928562187499</v>
       </c>
       <c r="C10">
-        <v>9.882376558578661</v>
+        <v>8.459205362288113</v>
       </c>
       <c r="D10">
-        <v>89.64766067452625</v>
+        <v>89.99151951960113</v>
       </c>
       <c r="E10">
-        <v>6.376371245979247</v>
+        <v>5.592691907133609</v>
       </c>
       <c r="F10">
-        <v>89.60637659617969</v>
+        <v>89.60133669914885</v>
       </c>
       <c r="G10">
-        <v>5.546603166493175</v>
+        <v>4.565694115098204</v>
       </c>
       <c r="H10">
-        <v>27.0592184531031</v>
+        <v>27.41007320597872</v>
       </c>
       <c r="I10">
-        <v>2.059250299989649</v>
+        <v>1.918046484018668</v>
       </c>
       <c r="J10">
-        <v>26.72512042808085</v>
+        <v>26.61443866670993</v>
       </c>
       <c r="K10">
-        <v>2.076147391777888</v>
+        <v>1.80041173665264</v>
       </c>
       <c r="L10">
-        <v>8.897077996470479</v>
+        <v>8.762841214160892</v>
       </c>
       <c r="M10">
-        <v>0.8700247803473564</v>
+        <v>0.6587568615560411</v>
       </c>
       <c r="N10">
-        <v>17.97791652051432</v>
+        <v>17.90415042624437</v>
       </c>
       <c r="O10">
-        <v>1.267720358310986</v>
+        <v>1.08593551549099</v>
       </c>
       <c r="P10">
-        <v>8.947043198010958</v>
+        <v>8.909833186054932</v>
       </c>
       <c r="Q10">
-        <v>0.909847459665953</v>
+        <v>0.6427649747902198</v>
       </c>
       <c r="R10">
-        <v>27.0592184531031</v>
+        <v>27.41007320597872</v>
       </c>
       <c r="S10">
-        <v>2.059250299989649</v>
+        <v>1.918046484018668</v>
       </c>
       <c r="T10">
-        <v>18.69764434188136</v>
+        <v>18.69208550003964</v>
       </c>
       <c r="U10">
-        <v>1.617874354511632</v>
+        <v>1.366282978962309</v>
       </c>
       <c r="V10">
-        <v>4.023578814302006</v>
+        <v>3.975163451166972</v>
       </c>
       <c r="W10">
-        <v>0.4906611800522839</v>
+        <v>0.4149313151182608</v>
       </c>
       <c r="X10">
-        <v>4.003897271897484</v>
+        <v>3.947189715503322</v>
       </c>
       <c r="Y10">
-        <v>0.4295108135839393</v>
+        <v>0.4577298977062312</v>
       </c>
       <c r="Z10">
-        <v>8.897077996470479</v>
+        <v>8.762841214160892</v>
       </c>
       <c r="AA10">
-        <v>0.8700247803473564</v>
+        <v>0.6587568615560411</v>
       </c>
       <c r="AB10">
-        <v>17.97791652051432</v>
+        <v>17.90415042624437</v>
       </c>
       <c r="AC10">
-        <v>1.267720358310986</v>
+        <v>1.08593551549099</v>
       </c>
       <c r="AD10">
-        <v>20.85317276364365</v>
+        <v>20.94292490947764</v>
       </c>
       <c r="AE10">
-        <v>1.115793186809303</v>
+        <v>0.8497780303697596</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -1485,94 +1485,94 @@
         <v>2029</v>
       </c>
       <c r="B11">
-        <v>192.8835208052257</v>
+        <v>190.5182792572138</v>
       </c>
       <c r="C11">
-        <v>10.25475734311689</v>
+        <v>8.634354409744079</v>
       </c>
       <c r="D11">
-        <v>96.5482921813462</v>
+        <v>96.20086273848023</v>
       </c>
       <c r="E11">
-        <v>6.786374106708037</v>
+        <v>6.307482570279485</v>
       </c>
       <c r="F11">
-        <v>96.33522862387946</v>
+        <v>94.31741651873361</v>
       </c>
       <c r="G11">
-        <v>5.344164523113721</v>
+        <v>5.848449921258791</v>
       </c>
       <c r="H11">
-        <v>29.04421357078695</v>
+        <v>28.36738049356445</v>
       </c>
       <c r="I11">
-        <v>1.815760656263506</v>
+        <v>2.070218965167807</v>
       </c>
       <c r="J11">
-        <v>28.99206076668689</v>
+        <v>28.53780995450396</v>
       </c>
       <c r="K11">
-        <v>1.803571608714574</v>
+        <v>2.019233836286949</v>
       </c>
       <c r="L11">
-        <v>9.678644279272238</v>
+        <v>9.329805654090947</v>
       </c>
       <c r="M11">
-        <v>0.971384806772149</v>
+        <v>0.9205068480907442</v>
       </c>
       <c r="N11">
-        <v>19.02635871361927</v>
+        <v>18.65977266481204</v>
       </c>
       <c r="O11">
-        <v>1.593092210842484</v>
+        <v>1.382606280207493</v>
       </c>
       <c r="P11">
-        <v>9.593951293514131</v>
+        <v>9.422647751762211</v>
       </c>
       <c r="Q11">
-        <v>0.8175905165446359</v>
+        <v>1.026958380259368</v>
       </c>
       <c r="R11">
-        <v>29.04421357078695</v>
+        <v>28.36738049356445</v>
       </c>
       <c r="S11">
-        <v>1.815760656263506</v>
+        <v>2.070218965167807</v>
       </c>
       <c r="T11">
-        <v>20.29175597175793</v>
+        <v>19.83892296341196</v>
       </c>
       <c r="U11">
-        <v>1.430443287058769</v>
+        <v>1.545915655453503</v>
       </c>
       <c r="V11">
-        <v>4.323173336208528</v>
+        <v>4.317896219812617</v>
       </c>
       <c r="W11">
-        <v>0.4731120884914745</v>
+        <v>0.4614818868782464</v>
       </c>
       <c r="X11">
-        <v>4.377131458720441</v>
+        <v>4.380990771279371</v>
       </c>
       <c r="Y11">
-        <v>0.4943279805493067</v>
+        <v>0.454098511441366</v>
       </c>
       <c r="Z11">
-        <v>9.678644279272238</v>
+        <v>9.329805654090947</v>
       </c>
       <c r="AA11">
-        <v>0.971384806772149</v>
+        <v>0.9205068480907442</v>
       </c>
       <c r="AB11">
-        <v>19.02635871361927</v>
+        <v>18.65977266481204</v>
       </c>
       <c r="AC11">
-        <v>1.593092210842484</v>
+        <v>1.382606280207493</v>
       </c>
       <c r="AD11">
-        <v>21.80297806371473</v>
+        <v>22.38405371969056</v>
       </c>
       <c r="AE11">
-        <v>1.177844564609393</v>
+        <v>1.028057269222813</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -1580,94 +1580,94 @@
         <v>2030</v>
       </c>
       <c r="B12">
-        <v>201.899111641602</v>
+        <v>199.8836094534406</v>
       </c>
       <c r="C12">
-        <v>8.527741070007115</v>
+        <v>7.78385735548061</v>
       </c>
       <c r="D12">
-        <v>100.5365971061737</v>
+        <v>99.49319704361611</v>
       </c>
       <c r="E12">
-        <v>5.51019054207956</v>
+        <v>4.651662286092257</v>
       </c>
       <c r="F12">
-        <v>101.3625145354282</v>
+        <v>100.3904124098245</v>
       </c>
       <c r="G12">
-        <v>5.377622814039644</v>
+        <v>5.588181423818395</v>
       </c>
       <c r="H12">
-        <v>30.1424410958135</v>
+        <v>30.29449498028398</v>
       </c>
       <c r="I12">
-        <v>2.24391179419833</v>
+        <v>2.055982358703981</v>
       </c>
       <c r="J12">
-        <v>30.41278680700726</v>
+        <v>29.93685878477212</v>
       </c>
       <c r="K12">
-        <v>1.860759792575941</v>
+        <v>2.239797988320535</v>
       </c>
       <c r="L12">
-        <v>10.23160021772606</v>
+        <v>9.962237180443097</v>
       </c>
       <c r="M12">
-        <v>0.7478799877728595</v>
+        <v>0.84634784625934</v>
       </c>
       <c r="N12">
-        <v>20.28597807559426</v>
+        <v>20.02429232688875</v>
       </c>
       <c r="O12">
-        <v>1.426705933478293</v>
+        <v>1.340358561713614</v>
       </c>
       <c r="P12">
-        <v>10.28970833928713</v>
+        <v>10.17252913743659</v>
       </c>
       <c r="Q12">
-        <v>0.9209066096450853</v>
+        <v>0.7512832979047136</v>
       </c>
       <c r="R12">
-        <v>30.1424410958135</v>
+        <v>30.29449498028398</v>
       </c>
       <c r="S12">
-        <v>2.24391179419833</v>
+        <v>2.055982358703981</v>
       </c>
       <c r="T12">
-        <v>21.47854798805133</v>
+        <v>21.0074288982952</v>
       </c>
       <c r="U12">
-        <v>1.413128821727788</v>
+        <v>1.634345671812459</v>
       </c>
       <c r="V12">
-        <v>4.452172669460165</v>
+        <v>4.461660978171627</v>
       </c>
       <c r="W12">
-        <v>0.4975004904143065</v>
+        <v>0.5292843468862031</v>
       </c>
       <c r="X12">
-        <v>4.482066149495769</v>
+        <v>4.467768908305294</v>
       </c>
       <c r="Y12">
-        <v>0.5214101156522724</v>
+        <v>0.5188156163577634</v>
       </c>
       <c r="Z12">
-        <v>10.23160021772606</v>
+        <v>9.962237180443097</v>
       </c>
       <c r="AA12">
-        <v>0.7478799877728595</v>
+        <v>0.84634784625934</v>
       </c>
       <c r="AB12">
-        <v>20.28597807559426</v>
+        <v>20.02429232688875</v>
       </c>
       <c r="AC12">
-        <v>1.426705933478293</v>
+        <v>1.340358561713614</v>
       </c>
       <c r="AD12">
-        <v>23.40444621885204</v>
+        <v>23.54953965161856</v>
       </c>
       <c r="AE12">
-        <v>1.21515423962389</v>
+        <v>0.9122841611698583</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -1675,94 +1675,94 @@
         <v>2031</v>
       </c>
       <c r="B13">
-        <v>9.91471809586818</v>
+        <v>10.03102287016553</v>
       </c>
       <c r="C13">
-        <v>0.6193424618857135</v>
+        <v>0.5443836842336359</v>
       </c>
       <c r="D13">
-        <v>4.96306769192384</v>
+        <v>5.034852664688315</v>
       </c>
       <c r="E13">
-        <v>0.3575408954078905</v>
+        <v>0.3215102335926248</v>
       </c>
       <c r="F13">
-        <v>4.951650403944338</v>
+        <v>4.996170205477211</v>
       </c>
       <c r="G13">
-        <v>0.3322481900733361</v>
+        <v>0.3213515928619303</v>
       </c>
       <c r="H13">
-        <v>1.497318327161941</v>
+        <v>1.497506347457914</v>
       </c>
       <c r="I13">
-        <v>0.1285282137602</v>
+        <v>0.116718815957407</v>
       </c>
       <c r="J13">
-        <v>1.485553248752512</v>
+        <v>1.519160266689835</v>
       </c>
       <c r="K13">
-        <v>0.1085215647654262</v>
+        <v>0.1147973229073277</v>
       </c>
       <c r="L13">
-        <v>0.492508763215644</v>
+        <v>0.4900566294261982</v>
       </c>
       <c r="M13">
-        <v>0.04119662049599428</v>
+        <v>0.04311346261550086</v>
       </c>
       <c r="N13">
-        <v>0.9824291139181051</v>
+        <v>1.0008128319849</v>
       </c>
       <c r="O13">
-        <v>0.08000989124660723</v>
+        <v>0.08113039858379265</v>
       </c>
       <c r="P13">
-        <v>0.4938409508961342</v>
+        <v>0.488634129918365</v>
       </c>
       <c r="Q13">
-        <v>0.04351263995507974</v>
+        <v>0.04022006517907811</v>
       </c>
       <c r="R13">
-        <v>1.497318327161941</v>
+        <v>1.497506347457914</v>
       </c>
       <c r="S13">
-        <v>0.1285282137602</v>
+        <v>0.116718815957407</v>
       </c>
       <c r="T13">
-        <v>1.030477194462664</v>
+        <v>1.055154446230241</v>
       </c>
       <c r="U13">
-        <v>0.07661341057940722</v>
+        <v>0.09364978934941852</v>
       </c>
       <c r="V13">
-        <v>0.2256423740590987</v>
+        <v>0.2318979918880623</v>
       </c>
       <c r="W13">
-        <v>0.02483513153739136</v>
+        <v>0.02266163657518803</v>
       </c>
       <c r="X13">
-        <v>0.2294336802307498</v>
+        <v>0.232107828571531</v>
       </c>
       <c r="Y13">
-        <v>0.02655896142331275</v>
+        <v>0.02474247993098665</v>
       </c>
       <c r="Z13">
-        <v>0.492508763215644</v>
+        <v>0.4900566294261982</v>
       </c>
       <c r="AA13">
-        <v>0.04119662049599428</v>
+        <v>0.04311346261550086</v>
       </c>
       <c r="AB13">
-        <v>0.9824291139181051</v>
+        <v>1.0008128319849</v>
       </c>
       <c r="AC13">
-        <v>0.08000989124660723</v>
+        <v>0.08113039858379265</v>
       </c>
       <c r="AD13">
-        <v>24.91056139256165</v>
+        <v>24.77010441214048</v>
       </c>
       <c r="AE13">
-        <v>1.059228629637211</v>
+        <v>1.134343656537446</v>
       </c>
     </row>
     <row r="14" spans="1:31">
@@ -1770,94 +1770,94 @@
         <v>2032</v>
       </c>
       <c r="B14">
-        <v>220.0678246443459</v>
+        <v>219.3251347632988</v>
       </c>
       <c r="C14">
-        <v>11.29023378153569</v>
+        <v>10.6367888283859</v>
       </c>
       <c r="D14">
-        <v>109.94408266929</v>
+        <v>110.1881756583443</v>
       </c>
       <c r="E14">
-        <v>7.568462038282229</v>
+        <v>6.574460869264921</v>
       </c>
       <c r="F14">
-        <v>110.1237419750558</v>
+        <v>109.1369591049545</v>
       </c>
       <c r="G14">
-        <v>5.490202984212675</v>
+        <v>6.732473316166803</v>
       </c>
       <c r="H14">
-        <v>32.94945289241066</v>
+        <v>32.78606132021898</v>
       </c>
       <c r="I14">
-        <v>2.19811672757769</v>
+        <v>2.625064106441558</v>
       </c>
       <c r="J14">
-        <v>33.01215685418055</v>
+        <v>32.57291507849209</v>
       </c>
       <c r="K14">
-        <v>2.033019600017863</v>
+        <v>2.503342204540523</v>
       </c>
       <c r="L14">
-        <v>11.06581718885142</v>
+        <v>11.03442667941683</v>
       </c>
       <c r="M14">
-        <v>0.9112181937454661</v>
+        <v>0.9745794924362211</v>
       </c>
       <c r="N14">
-        <v>22.08643180141765</v>
+        <v>21.71669062335756</v>
       </c>
       <c r="O14">
-        <v>1.473020931818486</v>
+        <v>1.611402976495356</v>
       </c>
       <c r="P14">
-        <v>11.00988323819557</v>
+        <v>11.02686540346899</v>
       </c>
       <c r="Q14">
-        <v>0.8589248754794996</v>
+        <v>0.7655752384803146</v>
       </c>
       <c r="R14">
-        <v>32.94945289241066</v>
+        <v>32.78606132021898</v>
       </c>
       <c r="S14">
-        <v>2.19811672757769</v>
+        <v>2.625064106441558</v>
       </c>
       <c r="T14">
-        <v>23.36581606185156</v>
+        <v>22.9287588880334</v>
       </c>
       <c r="U14">
-        <v>1.671233501298373</v>
+        <v>2.117374591148037</v>
       </c>
       <c r="V14">
-        <v>4.801633434369475</v>
+        <v>4.797490142976542</v>
       </c>
       <c r="W14">
-        <v>0.4801633818541594</v>
+        <v>0.5542607219918291</v>
       </c>
       <c r="X14">
-        <v>4.844707357959497</v>
+        <v>4.846666047482144</v>
       </c>
       <c r="Y14">
-        <v>0.5006528146953788</v>
+        <v>0.528172138871399</v>
       </c>
       <c r="Z14">
-        <v>11.06581718885142</v>
+        <v>11.03442667941683</v>
       </c>
       <c r="AA14">
-        <v>0.9112181937454661</v>
+        <v>0.9745794924362211</v>
       </c>
       <c r="AB14">
-        <v>22.08643180141765</v>
+        <v>21.71669062335756</v>
       </c>
       <c r="AC14">
-        <v>1.473020931818486</v>
+        <v>1.611402976495356</v>
       </c>
       <c r="AD14">
-        <v>9.381436585081444</v>
+        <v>9.636244132684487</v>
       </c>
       <c r="AE14">
-        <v>0.8964178838194994</v>
+        <v>0.8403565304243213</v>
       </c>
     </row>
     <row r="15" spans="1:31">
@@ -1865,94 +1865,94 @@
         <v>2033</v>
       </c>
       <c r="B15">
-        <v>230.4805701568168</v>
+        <v>228.5869164165639</v>
       </c>
       <c r="C15">
-        <v>12.54828107613254</v>
+        <v>10.78264700389407</v>
       </c>
       <c r="D15">
-        <v>115.0690247835456</v>
+        <v>114.1698285244135</v>
       </c>
       <c r="E15">
-        <v>7.473711825895886</v>
+        <v>6.115110142787806</v>
       </c>
       <c r="F15">
-        <v>115.4115453732711</v>
+        <v>114.4170878921503</v>
       </c>
       <c r="G15">
-        <v>7.070676548706905</v>
+        <v>6.864368027420091</v>
       </c>
       <c r="H15">
-        <v>34.64716201907963</v>
+        <v>34.55260453359924</v>
       </c>
       <c r="I15">
-        <v>2.443414374345373</v>
+        <v>2.460049849630255</v>
       </c>
       <c r="J15">
-        <v>34.17961827280225</v>
+        <v>34.3132331615647</v>
       </c>
       <c r="K15">
-        <v>2.732879384396091</v>
+        <v>2.735007836609764</v>
       </c>
       <c r="L15">
-        <v>11.58127327996176</v>
+        <v>11.31874454292144</v>
       </c>
       <c r="M15">
-        <v>1.037078347555774</v>
+        <v>0.9300565362734418</v>
       </c>
       <c r="N15">
-        <v>23.3895871205753</v>
+        <v>22.84474844645841</v>
       </c>
       <c r="O15">
-        <v>1.532277050174877</v>
+        <v>1.681587374175531</v>
       </c>
       <c r="P15">
-        <v>11.61390468085213</v>
+        <v>11.38775720760655</v>
       </c>
       <c r="Q15">
-        <v>0.9583488220063886</v>
+        <v>1.179878481142806</v>
       </c>
       <c r="R15">
-        <v>34.64716201907963</v>
+        <v>34.55260453359924</v>
       </c>
       <c r="S15">
-        <v>2.443414374345373</v>
+        <v>2.460049849630255</v>
       </c>
       <c r="T15">
-        <v>24.0522348474775</v>
+        <v>24.0246984807797</v>
       </c>
       <c r="U15">
-        <v>1.984227605419423</v>
+        <v>2.012238590913085</v>
       </c>
       <c r="V15">
-        <v>5.093364460019556</v>
+        <v>5.119887376475408</v>
       </c>
       <c r="W15">
-        <v>0.6675384164838605</v>
+        <v>0.6360202344284307</v>
       </c>
       <c r="X15">
-        <v>5.034018965305209</v>
+        <v>5.168647304309602</v>
       </c>
       <c r="Y15">
-        <v>0.5829366723677003</v>
+        <v>0.6661360380584068</v>
       </c>
       <c r="Z15">
-        <v>11.58127327996176</v>
+        <v>11.31874454292144</v>
       </c>
       <c r="AA15">
-        <v>1.037078347555774</v>
+        <v>0.9300565362734418</v>
       </c>
       <c r="AB15">
-        <v>23.3895871205753</v>
+        <v>22.84474844645841</v>
       </c>
       <c r="AC15">
-        <v>1.532277050174877</v>
+        <v>1.681587374175531</v>
       </c>
       <c r="AD15">
-        <v>21.68048299247199</v>
+        <v>21.35404435493049</v>
       </c>
       <c r="AE15">
-        <v>1.17139616875477</v>
+        <v>1.056338940331217</v>
       </c>
     </row>
     <row r="16" spans="1:31">
@@ -1960,94 +1960,94 @@
         <v>2034</v>
       </c>
       <c r="B16">
-        <v>241.4497209879471</v>
+        <v>241.2035266057145</v>
       </c>
       <c r="C16">
-        <v>12.62660045491908</v>
+        <v>11.39676413245357</v>
       </c>
       <c r="D16">
-        <v>121.4945412313238</v>
+        <v>120.9115785252184</v>
       </c>
       <c r="E16">
-        <v>7.995843448649803</v>
+        <v>6.292735000800104</v>
       </c>
       <c r="F16">
-        <v>119.9551797566234</v>
+        <v>120.2919480804961</v>
       </c>
       <c r="G16">
-        <v>8.15404692434497</v>
+        <v>7.791325397822564</v>
       </c>
       <c r="H16">
-        <v>35.76814855952816</v>
+        <v>36.54383900098379</v>
       </c>
       <c r="I16">
-        <v>2.536435791538767</v>
+        <v>2.941883744157522</v>
       </c>
       <c r="J16">
-        <v>36.25149133604626</v>
+        <v>36.38612674701355</v>
       </c>
       <c r="K16">
-        <v>2.760300857947104</v>
+        <v>2.856151659781042</v>
       </c>
       <c r="L16">
-        <v>11.924370391289</v>
+        <v>11.7562844770112</v>
       </c>
       <c r="M16">
-        <v>1.229399835517537</v>
+        <v>0.9730117077422595</v>
       </c>
       <c r="N16">
-        <v>24.05912981504266</v>
+        <v>23.69835776766359</v>
       </c>
       <c r="O16">
-        <v>2.149798005540269</v>
+        <v>1.935254290415513</v>
       </c>
       <c r="P16">
-        <v>11.95203965471728</v>
+        <v>11.90734008782399</v>
       </c>
       <c r="Q16">
-        <v>1.258372681407443</v>
+        <v>1.040214907440805</v>
       </c>
       <c r="R16">
-        <v>35.76814855952816</v>
+        <v>36.54383900098379</v>
       </c>
       <c r="S16">
-        <v>2.536435791538767</v>
+        <v>2.941883744157522</v>
       </c>
       <c r="T16">
-        <v>25.18195038055564</v>
+        <v>25.33803515620602</v>
       </c>
       <c r="U16">
-        <v>2.120919040340391</v>
+        <v>2.06608037676627</v>
       </c>
       <c r="V16">
-        <v>5.520416173383563</v>
+        <v>5.542650739602935</v>
       </c>
       <c r="W16">
-        <v>0.6007319662093972</v>
+        <v>0.6892634898789542</v>
       </c>
       <c r="X16">
-        <v>5.549124782107046</v>
+        <v>5.505440851204591</v>
       </c>
       <c r="Y16">
-        <v>0.6168418189922523</v>
+        <v>0.6973164814900846</v>
       </c>
       <c r="Z16">
-        <v>11.924370391289</v>
+        <v>11.7562844770112</v>
       </c>
       <c r="AA16">
-        <v>1.229399835517537</v>
+        <v>0.9730117077422595</v>
       </c>
       <c r="AB16">
-        <v>24.05912981504266</v>
+        <v>23.69835776766359</v>
       </c>
       <c r="AC16">
-        <v>2.149798005540269</v>
+        <v>1.935254290415513</v>
       </c>
       <c r="AD16">
-        <v>26.35205300897196</v>
+        <v>26.28136179859146</v>
       </c>
       <c r="AE16">
-        <v>1.366240998383971</v>
+        <v>1.26625716955997</v>
       </c>
     </row>
     <row r="17" spans="1:31">
@@ -2055,94 +2055,94 @@
         <v>2035</v>
       </c>
       <c r="B17">
-        <v>251.5700049439125</v>
+        <v>252.3926285942676</v>
       </c>
       <c r="C17">
-        <v>12.41571904070672</v>
+        <v>13.75393600399752</v>
       </c>
       <c r="D17">
-        <v>123.7462191688878</v>
+        <v>126.6854902733556</v>
       </c>
       <c r="E17">
-        <v>7.671069770159747</v>
+        <v>7.212554576954148</v>
       </c>
       <c r="F17">
-        <v>127.8237857750246</v>
+        <v>125.707138320912</v>
       </c>
       <c r="G17">
-        <v>7.134105487779445</v>
+        <v>9.446911041703725</v>
       </c>
       <c r="H17">
-        <v>38.13550084933743</v>
+        <v>37.84575338966323</v>
       </c>
       <c r="I17">
-        <v>2.473138813236921</v>
+        <v>3.422036880724241</v>
       </c>
       <c r="J17">
-        <v>37.98232602057959</v>
+        <v>37.87256404004835</v>
       </c>
       <c r="K17">
-        <v>3.1117725075047</v>
+        <v>3.254425842582663</v>
       </c>
       <c r="L17">
-        <v>12.98692794965982</v>
+        <v>12.33184075338253</v>
       </c>
       <c r="M17">
-        <v>1.111893699720728</v>
+        <v>1.194746438162932</v>
       </c>
       <c r="N17">
-        <v>25.7821221242636</v>
+        <v>25.14384119648459</v>
       </c>
       <c r="O17">
-        <v>1.735148901226616</v>
+        <v>2.123665680467754</v>
       </c>
       <c r="P17">
-        <v>12.93690883118416</v>
+        <v>12.51313894133322</v>
       </c>
       <c r="Q17">
-        <v>1.036343703103887</v>
+        <v>1.04841199997707</v>
       </c>
       <c r="R17">
-        <v>38.13550084933743</v>
+        <v>37.84575338966323</v>
       </c>
       <c r="S17">
-        <v>2.473138813236921</v>
+        <v>3.422036880724241</v>
       </c>
       <c r="T17">
-        <v>26.55712907630024</v>
+        <v>26.31950549566004</v>
       </c>
       <c r="U17">
-        <v>2.624542268504651</v>
+        <v>2.146116622049239</v>
       </c>
       <c r="V17">
-        <v>5.693392243803665</v>
+        <v>5.751183036167959</v>
       </c>
       <c r="W17">
-        <v>0.6132701891079936</v>
+        <v>0.7396991459743012</v>
       </c>
       <c r="X17">
-        <v>5.731804700475699</v>
+        <v>5.801875508220352</v>
       </c>
       <c r="Y17">
-        <v>0.6168648116551047</v>
+        <v>0.7943681588744124</v>
       </c>
       <c r="Z17">
-        <v>12.98692794965982</v>
+        <v>12.33184075338253</v>
       </c>
       <c r="AA17">
-        <v>1.111893699720728</v>
+        <v>1.194746438162932</v>
       </c>
       <c r="AB17">
-        <v>25.7821221242636</v>
+        <v>25.14384119648459</v>
       </c>
       <c r="AC17">
-        <v>1.735148901226616</v>
+        <v>2.123665680467754</v>
       </c>
       <c r="AD17">
-        <v>29.00433816646633</v>
+        <v>28.66069954198206</v>
       </c>
       <c r="AE17">
-        <v>1.393243059515049</v>
+        <v>1.381818955101963</v>
       </c>
     </row>
     <row r="18" spans="1:31">
@@ -2150,94 +2150,94 @@
         <v>2036</v>
       </c>
       <c r="B18">
-        <v>258.0349339165385</v>
+        <v>258.6581058099305</v>
       </c>
       <c r="C18">
-        <v>11.24372493789721</v>
+        <v>13.26700737573397</v>
       </c>
       <c r="D18">
-        <v>128.4848720019804</v>
+        <v>128.0364649514355</v>
       </c>
       <c r="E18">
-        <v>7.166212240204943</v>
+        <v>8.133443447914372</v>
       </c>
       <c r="F18">
-        <v>129.5500619145579</v>
+        <v>130.621640858495</v>
       </c>
       <c r="G18">
-        <v>7.187925875320881</v>
+        <v>8.30633699354189</v>
       </c>
       <c r="H18">
-        <v>39.23241072891084</v>
+        <v>39.40611767062969</v>
       </c>
       <c r="I18">
-        <v>2.962755288067917</v>
+        <v>2.905048771366013</v>
       </c>
       <c r="J18">
-        <v>38.73693490224757</v>
+        <v>38.83640025028139</v>
       </c>
       <c r="K18">
-        <v>2.451285753605619</v>
+        <v>2.854007702291298</v>
       </c>
       <c r="L18">
-        <v>13.0645427225726</v>
+        <v>13.19754854280539</v>
       </c>
       <c r="M18">
-        <v>1.076976148634934</v>
+        <v>1.141740503257863</v>
       </c>
       <c r="N18">
-        <v>25.73545203240464</v>
+        <v>26.07070388246726</v>
       </c>
       <c r="O18">
-        <v>1.653404469993699</v>
+        <v>1.879699988849146</v>
       </c>
       <c r="P18">
-        <v>12.78072152842234</v>
+        <v>13.11087051231128</v>
       </c>
       <c r="Q18">
-        <v>1.035583712788841</v>
+        <v>1.102299422209987</v>
       </c>
       <c r="R18">
-        <v>39.23241072891084</v>
+        <v>39.40611767062969</v>
       </c>
       <c r="S18">
-        <v>2.962755288067917</v>
+        <v>2.905048771366013</v>
       </c>
       <c r="T18">
-        <v>27.36469755196639</v>
+        <v>26.90085271680333</v>
       </c>
       <c r="U18">
-        <v>2.125001835362001</v>
+        <v>2.193166724462815</v>
       </c>
       <c r="V18">
-        <v>5.687256103053643</v>
+        <v>5.96741612617721</v>
       </c>
       <c r="W18">
-        <v>0.6668914482576355</v>
+        <v>0.6957975798619251</v>
       </c>
       <c r="X18">
-        <v>5.684981247227537</v>
+        <v>5.968131407300851</v>
       </c>
       <c r="Y18">
-        <v>0.6237727741670931</v>
+        <v>0.5786656214747021</v>
       </c>
       <c r="Z18">
-        <v>13.0645427225726</v>
+        <v>13.19754854280539</v>
       </c>
       <c r="AA18">
-        <v>1.076976148634934</v>
+        <v>1.141740503257863</v>
       </c>
       <c r="AB18">
-        <v>25.73545203240464</v>
+        <v>26.07070388246726</v>
       </c>
       <c r="AC18">
-        <v>1.653404469993699</v>
+        <v>1.879699988849146</v>
       </c>
       <c r="AD18">
-        <v>30.87800932907932</v>
+        <v>30.80132938749169</v>
       </c>
       <c r="AE18">
-        <v>1.265739246065167</v>
+        <v>1.492468402434688</v>
       </c>
     </row>
     <row r="19" spans="1:31">
@@ -2245,94 +2245,94 @@
         <v>2037</v>
       </c>
       <c r="B19">
-        <v>271.5224371202158</v>
+        <v>269.4756893572456</v>
       </c>
       <c r="C19">
-        <v>15.50058250267784</v>
+        <v>12.76560850105919</v>
       </c>
       <c r="D19">
-        <v>135.6187486293811</v>
+        <v>135.2202483110052</v>
       </c>
       <c r="E19">
-        <v>8.289130160632219</v>
+        <v>8.642332270980875</v>
       </c>
       <c r="F19">
-        <v>135.9036884908348</v>
+        <v>134.2554410462403</v>
       </c>
       <c r="G19">
-        <v>9.408967542480859</v>
+        <v>6.753051451430523</v>
       </c>
       <c r="H19">
-        <v>40.71683104850362</v>
+        <v>40.25493165780733</v>
       </c>
       <c r="I19">
-        <v>3.630729215825271</v>
+        <v>2.350544725420522</v>
       </c>
       <c r="J19">
-        <v>40.84815789702323</v>
+        <v>40.22421193746814</v>
       </c>
       <c r="K19">
-        <v>3.129848993913456</v>
+        <v>2.562377778041068</v>
       </c>
       <c r="L19">
-        <v>13.64767624867755</v>
+        <v>13.48231723018475</v>
       </c>
       <c r="M19">
-        <v>1.326474333026474</v>
+        <v>0.8976722448455615</v>
       </c>
       <c r="N19">
-        <v>27.3199914015247</v>
+        <v>26.90521819202925</v>
       </c>
       <c r="O19">
-        <v>1.961103197635754</v>
+        <v>2.026310320701457</v>
       </c>
       <c r="P19">
-        <v>13.37103189510567</v>
+        <v>13.38876202875087</v>
       </c>
       <c r="Q19">
-        <v>1.211337871939661</v>
+        <v>1.141340987644304</v>
       </c>
       <c r="R19">
-        <v>40.71683104850362</v>
+        <v>40.25493165780733</v>
       </c>
       <c r="S19">
-        <v>3.630729215825271</v>
+        <v>2.350544725420522</v>
       </c>
       <c r="T19">
-        <v>28.7837774262948</v>
+        <v>28.02176025326649</v>
       </c>
       <c r="U19">
-        <v>2.459302802985705</v>
+        <v>2.166617783790343</v>
       </c>
       <c r="V19">
-        <v>6.026608015696002</v>
+        <v>6.110466933315581</v>
       </c>
       <c r="W19">
-        <v>0.6008619896156603</v>
+        <v>0.5040963567265895</v>
       </c>
       <c r="X19">
-        <v>6.03777245503243</v>
+        <v>6.091984750886077</v>
       </c>
       <c r="Y19">
-        <v>0.6143716167438155</v>
+        <v>0.4799532532772439</v>
       </c>
       <c r="Z19">
-        <v>13.64767624867755</v>
+        <v>13.48231723018475</v>
       </c>
       <c r="AA19">
-        <v>1.326474333026474</v>
+        <v>0.8976722448455615</v>
       </c>
       <c r="AB19">
-        <v>27.3199914015247</v>
+        <v>26.90521819202925</v>
       </c>
       <c r="AC19">
-        <v>1.961103197635754</v>
+        <v>2.026310320701457</v>
       </c>
       <c r="AD19">
-        <v>32.54598185927996</v>
+        <v>32.1114711158643</v>
       </c>
       <c r="AE19">
-        <v>1.664570175522567</v>
+        <v>1.586697590581737</v>
       </c>
     </row>
     <row r="20" spans="1:31">
@@ -2340,94 +2340,94 @@
         <v>2038</v>
       </c>
       <c r="B20">
-        <v>278.1266381679294</v>
+        <v>279.3373421017232</v>
       </c>
       <c r="C20">
-        <v>11.48587804483608</v>
+        <v>15.73740064407725</v>
       </c>
       <c r="D20">
-        <v>140.0071567166134</v>
+        <v>141.0461372254723</v>
       </c>
       <c r="E20">
-        <v>7.647462801756485</v>
+        <v>9.756221514738273</v>
       </c>
       <c r="F20">
-        <v>138.1194814513161</v>
+        <v>138.2912048762508</v>
       </c>
       <c r="G20">
-        <v>7.064208065408102</v>
+        <v>8.738209548243667</v>
       </c>
       <c r="H20">
-        <v>41.13344652763803</v>
+        <v>41.53670724209366</v>
       </c>
       <c r="I20">
-        <v>2.444280694040182</v>
+        <v>3.544625601402149</v>
       </c>
       <c r="J20">
-        <v>41.51441099755021</v>
+        <v>41.80425113952093</v>
       </c>
       <c r="K20">
-        <v>2.941027069478786</v>
+        <v>3.391083189978238</v>
       </c>
       <c r="L20">
-        <v>13.87279022958028</v>
+        <v>13.52067390786488</v>
       </c>
       <c r="M20">
-        <v>1.106906148520808</v>
+        <v>1.246111645968557</v>
       </c>
       <c r="N20">
-        <v>27.71725191439331</v>
+        <v>27.68647301358285</v>
       </c>
       <c r="O20">
-        <v>2.054701350909416</v>
+        <v>1.898620795617301</v>
       </c>
       <c r="P20">
-        <v>13.88158178215427</v>
+        <v>13.74309957318855</v>
       </c>
       <c r="Q20">
-        <v>1.070939599701074</v>
+        <v>1.265231554255073</v>
       </c>
       <c r="R20">
-        <v>41.13344652763803</v>
+        <v>41.53670724209366</v>
       </c>
       <c r="S20">
-        <v>2.444280694040182</v>
+        <v>3.544625601402149</v>
       </c>
       <c r="T20">
-        <v>29.07108264547598</v>
+        <v>29.39195643647531</v>
       </c>
       <c r="U20">
-        <v>2.434729956283965</v>
+        <v>2.558977583667447</v>
       </c>
       <c r="V20">
-        <v>6.200435747263612</v>
+        <v>6.1241105721918</v>
       </c>
       <c r="W20">
-        <v>0.7194000756058445</v>
+        <v>0.7221987274198942</v>
       </c>
       <c r="X20">
-        <v>6.242892604810628</v>
+        <v>6.288184130853799</v>
       </c>
       <c r="Y20">
-        <v>0.7277447522080653</v>
+        <v>0.723867837872305</v>
       </c>
       <c r="Z20">
-        <v>13.87279022958028</v>
+        <v>13.52067390786488</v>
       </c>
       <c r="AA20">
-        <v>1.106906148520808</v>
+        <v>1.246111645968557</v>
       </c>
       <c r="AB20">
-        <v>27.71725191439331</v>
+        <v>27.68647301358285</v>
       </c>
       <c r="AC20">
-        <v>2.054701350909416</v>
+        <v>1.898620795617301</v>
       </c>
       <c r="AD20">
-        <v>33.8602150594628</v>
+        <v>33.47266392190529</v>
       </c>
       <c r="AE20">
-        <v>1.675637486094809</v>
+        <v>1.767156864419818</v>
       </c>
     </row>
     <row r="21" spans="1:31">
@@ -2435,94 +2435,94 @@
         <v>2039</v>
       </c>
       <c r="B21">
-        <v>290.7917905465197</v>
+        <v>288.5725310903781</v>
       </c>
       <c r="C21">
-        <v>17.26344551710425</v>
+        <v>12.97848735408828</v>
       </c>
       <c r="D21">
-        <v>145.9589959137425</v>
+        <v>144.3851681554447</v>
       </c>
       <c r="E21">
-        <v>9.378734230831009</v>
+        <v>7.545617962740461</v>
       </c>
       <c r="F21">
-        <v>144.8327946327773</v>
+        <v>144.1873629349334</v>
       </c>
       <c r="G21">
-        <v>10.03812117181093</v>
+        <v>8.483386422426731</v>
       </c>
       <c r="H21">
-        <v>43.61737048787968</v>
+        <v>43.47623415104587</v>
       </c>
       <c r="I21">
-        <v>3.685065421917021</v>
+        <v>3.337438598601046</v>
       </c>
       <c r="J21">
-        <v>43.52421418616216</v>
+        <v>43.18347144804882</v>
       </c>
       <c r="K21">
-        <v>3.74527883695878</v>
+        <v>2.980097671756825</v>
       </c>
       <c r="L21">
-        <v>14.27757021139899</v>
+        <v>14.39210447609536</v>
       </c>
       <c r="M21">
-        <v>1.277489664522069</v>
+        <v>1.232665862611602</v>
       </c>
       <c r="N21">
-        <v>29.0640086346624</v>
+        <v>28.73115656717914</v>
       </c>
       <c r="O21">
-        <v>2.380311397004779</v>
+        <v>1.952833574611439</v>
       </c>
       <c r="P21">
-        <v>14.34963111267409</v>
+        <v>14.40439629256414</v>
       </c>
       <c r="Q21">
-        <v>1.250361129848153</v>
+        <v>1.224225835812796</v>
       </c>
       <c r="R21">
-        <v>43.61737048787968</v>
+        <v>43.47623415104587</v>
       </c>
       <c r="S21">
-        <v>3.685065421917021</v>
+        <v>3.337438598601046</v>
       </c>
       <c r="T21">
-        <v>30.84984856542938</v>
+        <v>30.05598847386051</v>
       </c>
       <c r="U21">
-        <v>3.015907002190632</v>
+        <v>2.173872387896236</v>
       </c>
       <c r="V21">
-        <v>6.298622914248117</v>
+        <v>6.586201226257025</v>
       </c>
       <c r="W21">
-        <v>0.7917991463288239</v>
+        <v>0.7277908030647346</v>
       </c>
       <c r="X21">
-        <v>6.375742706484647</v>
+        <v>6.541281747931266</v>
       </c>
       <c r="Y21">
-        <v>0.9028712732922046</v>
+        <v>0.7837316587308233</v>
       </c>
       <c r="Z21">
-        <v>14.27757021139899</v>
+        <v>14.39210447609536</v>
       </c>
       <c r="AA21">
-        <v>1.277489664522069</v>
+        <v>1.232665862611602</v>
       </c>
       <c r="AB21">
-        <v>29.0640086346624</v>
+        <v>28.73115656717914</v>
       </c>
       <c r="AC21">
-        <v>2.380311397004779</v>
+        <v>1.952833574611439</v>
       </c>
       <c r="AD21">
-        <v>34.9499018165866</v>
+        <v>34.84934155448439</v>
       </c>
       <c r="AE21">
-        <v>1.628650568763459</v>
+        <v>1.558374448772369</v>
       </c>
     </row>
     <row r="22" spans="1:31">
@@ -2530,94 +2530,94 @@
         <v>2040</v>
       </c>
       <c r="B22">
-        <v>299.2936047120006</v>
+        <v>300.3431790166694</v>
       </c>
       <c r="C22">
-        <v>16.46518744476242</v>
+        <v>18.06898295140154</v>
       </c>
       <c r="D22">
-        <v>149.3750372937881</v>
+        <v>149.6309601850286</v>
       </c>
       <c r="E22">
-        <v>9.612181834729199</v>
+        <v>11.11627888808195</v>
       </c>
       <c r="F22">
-        <v>149.9185674182124</v>
+        <v>150.7122188316408</v>
       </c>
       <c r="G22">
-        <v>9.55736529423592</v>
+        <v>9.81260875991739</v>
       </c>
       <c r="H22">
-        <v>44.99300319517067</v>
+        <v>45.16384414210624</v>
       </c>
       <c r="I22">
-        <v>3.188375597053951</v>
+        <v>3.382135936228701</v>
       </c>
       <c r="J22">
-        <v>45.06355373271059</v>
+        <v>45.36525052589753</v>
       </c>
       <c r="K22">
-        <v>3.950254871425605</v>
+        <v>3.313697723831983</v>
       </c>
       <c r="L22">
-        <v>14.95152594849346</v>
+        <v>15.18677631212014</v>
       </c>
       <c r="M22">
-        <v>1.335303450681969</v>
+        <v>1.467066946376302</v>
       </c>
       <c r="N22">
-        <v>29.89850498574395</v>
+        <v>29.95402318501982</v>
       </c>
       <c r="O22">
-        <v>2.483217568319241</v>
+        <v>2.518679638227309</v>
       </c>
       <c r="P22">
-        <v>15.01197955609378</v>
+        <v>15.04232466649709</v>
       </c>
       <c r="Q22">
-        <v>1.21574938566417</v>
+        <v>1.458054523353026</v>
       </c>
       <c r="R22">
-        <v>44.99300319517067</v>
+        <v>45.16384414210624</v>
       </c>
       <c r="S22">
-        <v>3.188375597053951</v>
+        <v>3.382135936228701</v>
       </c>
       <c r="T22">
-        <v>31.66771353857739</v>
+        <v>31.81228215479011</v>
       </c>
       <c r="U22">
-        <v>3.154106474003203</v>
+        <v>2.736731449797407</v>
       </c>
       <c r="V22">
-        <v>6.684084558887183</v>
+        <v>6.739112569650174</v>
       </c>
       <c r="W22">
-        <v>0.7364117473154573</v>
+        <v>0.7979414889739638</v>
       </c>
       <c r="X22">
-        <v>6.711755635246006</v>
+        <v>6.81385580145724</v>
       </c>
       <c r="Y22">
-        <v>0.7361296304860564</v>
+        <v>0.7398791915519396</v>
       </c>
       <c r="Z22">
-        <v>14.95152594849346</v>
+        <v>15.18677631212014</v>
       </c>
       <c r="AA22">
-        <v>1.335303450681969</v>
+        <v>1.467066946376302</v>
       </c>
       <c r="AB22">
-        <v>29.89850498574395</v>
+        <v>29.95402318501982</v>
       </c>
       <c r="AC22">
-        <v>2.483217568319241</v>
+        <v>2.518679638227309</v>
       </c>
       <c r="AD22">
-        <v>36.21545968558442</v>
+        <v>35.9622227058607</v>
       </c>
       <c r="AE22">
-        <v>1.287213366046899</v>
+        <v>2.002671071566923</v>
       </c>
     </row>
   </sheetData>
@@ -2700,64 +2700,64 @@
         <v>2020</v>
       </c>
       <c r="B2">
-        <v>50.01829104151307</v>
+        <v>50.0336253681736</v>
       </c>
       <c r="C2">
-        <v>3.440149426168108</v>
+        <v>2.584793726329579</v>
       </c>
       <c r="D2">
-        <v>50.01829104151307</v>
+        <v>50.0336253681736</v>
       </c>
       <c r="E2">
-        <v>3.440149426168108</v>
+        <v>2.584793726329579</v>
       </c>
       <c r="F2">
-        <v>4.94613215193266</v>
+        <v>5.070429605468534</v>
       </c>
       <c r="G2">
-        <v>0.5186043960364086</v>
+        <v>0.4313717702867806</v>
       </c>
       <c r="H2">
-        <v>4.94613215193266</v>
+        <v>5.070429605468534</v>
       </c>
       <c r="I2">
-        <v>0.5186043960364086</v>
+        <v>0.4313717702867806</v>
       </c>
       <c r="J2">
-        <v>25.361593552497</v>
+        <v>25.7179772492961</v>
       </c>
       <c r="K2">
-        <v>1.745591687326106</v>
+        <v>1.439310435570558</v>
       </c>
       <c r="L2">
-        <v>25.361593552497</v>
+        <v>25.7179772492961</v>
       </c>
       <c r="M2">
-        <v>1.745591687326106</v>
+        <v>1.439310435570558</v>
       </c>
       <c r="N2">
-        <v>17.10067104264711</v>
+        <v>17.54552101399409</v>
       </c>
       <c r="O2">
-        <v>1.333893302296489</v>
+        <v>1.041564990890891</v>
       </c>
       <c r="P2">
-        <v>17.10067104264711</v>
+        <v>17.54552101399409</v>
       </c>
       <c r="Q2">
-        <v>1.333893302296489</v>
+        <v>1.041564990890891</v>
       </c>
       <c r="R2">
-        <v>2.232603562169483</v>
+        <v>2.272833331896503</v>
       </c>
       <c r="S2">
-        <v>0.2821736521231317</v>
+        <v>0.2592255986680573</v>
       </c>
       <c r="T2">
-        <v>2.232603562169483</v>
+        <v>2.272833331896503</v>
       </c>
       <c r="U2">
-        <v>0.2821736521231317</v>
+        <v>0.2592255986680573</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -2765,64 +2765,64 @@
         <v>2021</v>
       </c>
       <c r="B3">
-        <v>55.8881713556068</v>
+        <v>54.88528218102728</v>
       </c>
       <c r="C3">
-        <v>3.779937685649497</v>
+        <v>3.814345276896495</v>
       </c>
       <c r="D3">
-        <v>105.9064623971199</v>
+        <v>104.9189075492009</v>
       </c>
       <c r="E3">
-        <v>4.545333102161855</v>
+        <v>4.441884366710648</v>
       </c>
       <c r="F3">
-        <v>5.635935442887479</v>
+        <v>5.478252316188206</v>
       </c>
       <c r="G3">
-        <v>0.4457024004850813</v>
+        <v>0.4238342256434968</v>
       </c>
       <c r="H3">
-        <v>10.58206759482014</v>
+        <v>10.54868192165674</v>
       </c>
       <c r="I3">
-        <v>0.6204201593804717</v>
+        <v>0.5591689692416502</v>
       </c>
       <c r="J3">
-        <v>19.46730951868257</v>
+        <v>19.80848524622133</v>
       </c>
       <c r="K3">
-        <v>1.63692423488424</v>
+        <v>2.090006087703874</v>
       </c>
       <c r="L3">
-        <v>44.82890307117957</v>
+        <v>45.52646249551743</v>
       </c>
       <c r="M3">
-        <v>2.526363487768487</v>
+        <v>2.443723809720753</v>
       </c>
       <c r="N3">
-        <v>27.50019602134769</v>
+        <v>27.06171790269768</v>
       </c>
       <c r="O3">
-        <v>1.229827736904243</v>
+        <v>1.318339172594312</v>
       </c>
       <c r="P3">
-        <v>44.60086706399482</v>
+        <v>44.60723891669177</v>
       </c>
       <c r="Q3">
-        <v>1.687155858822626</v>
+        <v>1.640660958929644</v>
       </c>
       <c r="R3">
-        <v>2.519222385253921</v>
+        <v>2.473460302117485</v>
       </c>
       <c r="S3">
-        <v>0.301669293607653</v>
+        <v>0.2705255710472279</v>
       </c>
       <c r="T3">
-        <v>4.751825947423404</v>
+        <v>4.746293634013987</v>
       </c>
       <c r="U3">
-        <v>0.3913536408493216</v>
+        <v>0.3914839743864463</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -2830,64 +2830,64 @@
         <v>2022</v>
       </c>
       <c r="B4">
-        <v>60.13697746945844</v>
+        <v>60.39157475059026</v>
       </c>
       <c r="C4">
-        <v>3.588374917452811</v>
+        <v>3.08948858569708</v>
       </c>
       <c r="D4">
-        <v>166.0434398665783</v>
+        <v>165.3104822997911</v>
       </c>
       <c r="E4">
-        <v>5.348268910061016</v>
+        <v>5.632496431813572</v>
       </c>
       <c r="F4">
-        <v>5.92866560588659</v>
+        <v>6.043360889847785</v>
       </c>
       <c r="G4">
-        <v>0.5900786522873195</v>
+        <v>0.5353084161761348</v>
       </c>
       <c r="H4">
-        <v>16.51073320070673</v>
+        <v>16.59204281150452</v>
       </c>
       <c r="I4">
-        <v>0.7989522882577175</v>
+        <v>0.7205241366432036</v>
       </c>
       <c r="J4">
-        <v>18.89330632472895</v>
+        <v>19.58512968620792</v>
       </c>
       <c r="K4">
-        <v>2.209404949297495</v>
+        <v>2.136781914006488</v>
       </c>
       <c r="L4">
-        <v>63.72220939590851</v>
+        <v>65.11159218172534</v>
       </c>
       <c r="M4">
-        <v>3.846200137039964</v>
+        <v>3.350998032764519</v>
       </c>
       <c r="N4">
-        <v>32.65617527672989</v>
+        <v>32.51196789635061</v>
       </c>
       <c r="O4">
-        <v>1.427718333091253</v>
+        <v>1.254773093533074</v>
       </c>
       <c r="P4">
-        <v>77.25704234072468</v>
+        <v>77.1192068130424</v>
       </c>
       <c r="Q4">
-        <v>2.296136212559972</v>
+        <v>2.143399094025114</v>
       </c>
       <c r="R4">
-        <v>2.770965504498378</v>
+        <v>2.643163290269645</v>
       </c>
       <c r="S4">
-        <v>0.3115786942876588</v>
+        <v>0.3186622331203489</v>
       </c>
       <c r="T4">
-        <v>7.522791451921782</v>
+        <v>7.389456924283628</v>
       </c>
       <c r="U4">
-        <v>0.5304093141449929</v>
+        <v>0.5201165326425944</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -2895,64 +2895,64 @@
         <v>2023</v>
       </c>
       <c r="B5">
-        <v>65.35264196351619</v>
+        <v>65.37674470455526</v>
       </c>
       <c r="C5">
-        <v>4.421814173181794</v>
+        <v>4.383919590805982</v>
       </c>
       <c r="D5">
-        <v>231.3960818300945</v>
+        <v>230.6872270043464</v>
       </c>
       <c r="E5">
-        <v>6.134735777219997</v>
+        <v>6.726284056123465</v>
       </c>
       <c r="F5">
-        <v>6.52269436443217</v>
+        <v>6.613509858810958</v>
       </c>
       <c r="G5">
-        <v>0.5334991507131777</v>
+        <v>0.6497249480812332</v>
       </c>
       <c r="H5">
-        <v>23.0334275651389</v>
+        <v>23.20555267031549</v>
       </c>
       <c r="I5">
-        <v>1.028136644249209</v>
+        <v>1.035639557348036</v>
       </c>
       <c r="J5">
-        <v>19.65256174105154</v>
+        <v>19.56565486480785</v>
       </c>
       <c r="K5">
-        <v>2.302629920333013</v>
+        <v>3.174396218383766</v>
       </c>
       <c r="L5">
-        <v>83.37477113696012</v>
+        <v>84.6772470465332</v>
       </c>
       <c r="M5">
-        <v>4.897890955436102</v>
+        <v>4.401836859227135</v>
       </c>
       <c r="N5">
-        <v>36.84094677062138</v>
+        <v>36.6521596816042</v>
       </c>
       <c r="O5">
-        <v>1.673599357355773</v>
+        <v>1.791718059454783</v>
       </c>
       <c r="P5">
-        <v>114.0979891113461</v>
+        <v>113.7713664946466</v>
       </c>
       <c r="Q5">
-        <v>3.243008132001016</v>
+        <v>2.768479850396493</v>
       </c>
       <c r="R5">
-        <v>3.009049290003767</v>
+        <v>2.997340920756467</v>
       </c>
       <c r="S5">
-        <v>0.347677936798344</v>
+        <v>0.3057035537517128</v>
       </c>
       <c r="T5">
-        <v>10.53184074192555</v>
+        <v>10.3867978450401</v>
       </c>
       <c r="U5">
-        <v>0.6004083079243445</v>
+        <v>0.6128791537441828</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -2960,64 +2960,64 @@
         <v>2024</v>
       </c>
       <c r="B6">
-        <v>69.97096129877912</v>
+        <v>69.22265045851476</v>
       </c>
       <c r="C6">
-        <v>4.131067040066861</v>
+        <v>3.861725991315873</v>
       </c>
       <c r="D6">
-        <v>301.3670431288737</v>
+        <v>299.9098774628612</v>
       </c>
       <c r="E6">
-        <v>7.261600315708174</v>
+        <v>6.929733264629414</v>
       </c>
       <c r="F6">
-        <v>7.152039602769468</v>
+        <v>6.9335029277647</v>
       </c>
       <c r="G6">
-        <v>0.7123056696959089</v>
+        <v>0.6194686978181358</v>
       </c>
       <c r="H6">
-        <v>30.18546716790836</v>
+        <v>30.13905559808018</v>
       </c>
       <c r="I6">
-        <v>1.346684639749718</v>
+        <v>1.225638544830604</v>
       </c>
       <c r="J6">
-        <v>20.34234272586056</v>
+        <v>19.81573078911387</v>
       </c>
       <c r="K6">
-        <v>2.49045035450229</v>
+        <v>2.621646207157242</v>
       </c>
       <c r="L6">
-        <v>103.7171138628206</v>
+        <v>104.492977835647</v>
       </c>
       <c r="M6">
-        <v>5.989754501742443</v>
+        <v>5.210652874996104</v>
       </c>
       <c r="N6">
-        <v>40.08501274261368</v>
+        <v>39.43262456341371</v>
       </c>
       <c r="O6">
-        <v>1.74991966310347</v>
+        <v>1.622670594048049</v>
       </c>
       <c r="P6">
-        <v>154.1830018539597</v>
+        <v>153.2039910580603</v>
       </c>
       <c r="Q6">
-        <v>3.903997377579883</v>
+        <v>3.189747669016322</v>
       </c>
       <c r="R6">
-        <v>3.201357806590762</v>
+        <v>3.07367214562526</v>
       </c>
       <c r="S6">
-        <v>0.3854500132017702</v>
+        <v>0.3624294001673468</v>
       </c>
       <c r="T6">
-        <v>13.73319854851632</v>
+        <v>13.46046999066536</v>
       </c>
       <c r="U6">
-        <v>0.7397326548857852</v>
+        <v>0.6776169420101651</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -3025,64 +3025,64 @@
         <v>2025</v>
       </c>
       <c r="B7">
-        <v>75.5021616446129</v>
+        <v>74.823240145325</v>
       </c>
       <c r="C7">
-        <v>4.321379384286475</v>
+        <v>4.561285773060686</v>
       </c>
       <c r="D7">
-        <v>376.8692047734866</v>
+        <v>374.7331176081862</v>
       </c>
       <c r="E7">
-        <v>8.812079790956176</v>
+        <v>8.38591506525527</v>
       </c>
       <c r="F7">
-        <v>7.422084145932107</v>
+        <v>7.446763692820443</v>
       </c>
       <c r="G7">
-        <v>0.7385067320001737</v>
+        <v>0.648819439345996</v>
       </c>
       <c r="H7">
-        <v>37.60755131384047</v>
+        <v>37.58581929090062</v>
       </c>
       <c r="I7">
-        <v>1.601197025395721</v>
+        <v>1.347739241548284</v>
       </c>
       <c r="J7">
-        <v>20.77273641145304</v>
+        <v>20.95158678253589</v>
       </c>
       <c r="K7">
-        <v>2.910465799090502</v>
+        <v>2.580118111349082</v>
       </c>
       <c r="L7">
-        <v>124.4898502742737</v>
+        <v>125.4445646181829</v>
       </c>
       <c r="M7">
-        <v>6.944517400019384</v>
+        <v>5.88594542212585</v>
       </c>
       <c r="N7">
-        <v>42.81776502986141</v>
+        <v>42.96711035253136</v>
       </c>
       <c r="O7">
-        <v>2.288077872633058</v>
+        <v>2.072186176845936</v>
       </c>
       <c r="P7">
-        <v>197.0007668838212</v>
+        <v>196.1711014105916</v>
       </c>
       <c r="Q7">
-        <v>5.101038904912412</v>
+        <v>4.207005339343267</v>
       </c>
       <c r="R7">
-        <v>3.392313886832446</v>
+        <v>3.36924549722484</v>
       </c>
       <c r="S7">
-        <v>0.344340229146733</v>
+        <v>0.4262868247239823</v>
       </c>
       <c r="T7">
-        <v>17.12551243534876</v>
+        <v>16.8297154878902</v>
       </c>
       <c r="U7">
-        <v>0.8755860650727741</v>
+        <v>0.7638937489848806</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -3090,64 +3090,64 @@
         <v>2026</v>
       </c>
       <c r="B8">
-        <v>80.74585004836531</v>
+        <v>79.60134766598752</v>
       </c>
       <c r="C8">
-        <v>4.403476841683715</v>
+        <v>4.317286795918008</v>
       </c>
       <c r="D8">
-        <v>457.6150548218517</v>
+        <v>454.3344652741736</v>
       </c>
       <c r="E8">
-        <v>9.838531407454052</v>
+        <v>9.130281221032865</v>
       </c>
       <c r="F8">
-        <v>7.970485685730497</v>
+        <v>8.137474386801449</v>
       </c>
       <c r="G8">
-        <v>0.6044464662983786</v>
+        <v>0.6179138987464504</v>
       </c>
       <c r="H8">
-        <v>45.57803699957095</v>
+        <v>45.72329367770207</v>
       </c>
       <c r="I8">
-        <v>1.684135581216519</v>
+        <v>1.470672485716542</v>
       </c>
       <c r="J8">
-        <v>22.53954371341956</v>
+        <v>22.41387179863164</v>
       </c>
       <c r="K8">
-        <v>3.059897040629056</v>
+        <v>2.584897599376977</v>
       </c>
       <c r="L8">
-        <v>147.0293939876932</v>
+        <v>147.8584364168146</v>
       </c>
       <c r="M8">
-        <v>7.55235450274463</v>
+        <v>5.784909601084522</v>
       </c>
       <c r="N8">
-        <v>46.35407019747942</v>
+        <v>46.05433311652032</v>
       </c>
       <c r="O8">
-        <v>1.971039946647277</v>
+        <v>2.370678036952516</v>
       </c>
       <c r="P8">
-        <v>243.3548370813005</v>
+        <v>242.225434527112</v>
       </c>
       <c r="Q8">
-        <v>4.595626128626193</v>
+        <v>4.902034290697125</v>
       </c>
       <c r="R8">
-        <v>3.740894162071686</v>
+        <v>3.543110094193791</v>
       </c>
       <c r="S8">
-        <v>0.427375410799588</v>
+        <v>0.471740909670426</v>
       </c>
       <c r="T8">
-        <v>20.86640659742045</v>
+        <v>20.37282558208399</v>
       </c>
       <c r="U8">
-        <v>0.9516795714422439</v>
+        <v>0.827867189054576</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -3155,64 +3155,64 @@
         <v>2027</v>
       </c>
       <c r="B9">
-        <v>86.24183332126397</v>
+        <v>84.79233301725377</v>
       </c>
       <c r="C9">
-        <v>4.586001308598784</v>
+        <v>5.35509961237626</v>
       </c>
       <c r="D9">
-        <v>543.856888143116</v>
+        <v>539.1267982914273</v>
       </c>
       <c r="E9">
-        <v>10.47984231052791</v>
+        <v>10.45624200093057</v>
       </c>
       <c r="F9">
-        <v>8.671055425289774</v>
+        <v>8.491675865601144</v>
       </c>
       <c r="G9">
-        <v>0.7161060926805919</v>
+        <v>0.735242053870342</v>
       </c>
       <c r="H9">
-        <v>54.24909242486076</v>
+        <v>54.21496954330321</v>
       </c>
       <c r="I9">
-        <v>1.814441634241127</v>
+        <v>1.658077929334075</v>
       </c>
       <c r="J9">
-        <v>23.53060432574395</v>
+        <v>23.50092112945403</v>
       </c>
       <c r="K9">
-        <v>2.748918573970201</v>
+        <v>2.833672042518555</v>
       </c>
       <c r="L9">
-        <v>170.5599983134372</v>
+        <v>171.3593575462685</v>
       </c>
       <c r="M9">
-        <v>8.748494560428192</v>
+        <v>6.896901959636407</v>
       </c>
       <c r="N9">
-        <v>49.41758946398627</v>
+        <v>48.91985964564018</v>
       </c>
       <c r="O9">
-        <v>2.155141018149456</v>
+        <v>1.790101230797801</v>
       </c>
       <c r="P9">
-        <v>292.7724265452869</v>
+        <v>291.1452941727521</v>
       </c>
       <c r="Q9">
-        <v>4.670915701647785</v>
+        <v>5.525998123949819</v>
       </c>
       <c r="R9">
-        <v>3.89868342351734</v>
+        <v>3.83119667310576</v>
       </c>
       <c r="S9">
-        <v>0.312653510220951</v>
+        <v>0.4549782963768986</v>
       </c>
       <c r="T9">
-        <v>24.76509002093779</v>
+        <v>24.20402225518976</v>
       </c>
       <c r="U9">
-        <v>1.021995269371323</v>
+        <v>1.028644023430529</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -3220,64 +3220,64 @@
         <v>2028</v>
       </c>
       <c r="B10">
-        <v>89.64766067452625</v>
+        <v>89.99151951960113</v>
       </c>
       <c r="C10">
-        <v>6.376371245979247</v>
+        <v>5.592691907133609</v>
       </c>
       <c r="D10">
-        <v>633.5045488176421</v>
+        <v>629.1183178110285</v>
       </c>
       <c r="E10">
-        <v>12.71844608229222</v>
+        <v>11.65714452387685</v>
       </c>
       <c r="F10">
-        <v>8.947043198010958</v>
+        <v>8.909833186054932</v>
       </c>
       <c r="G10">
-        <v>0.909847459665953</v>
+        <v>0.6427649747902198</v>
       </c>
       <c r="H10">
-        <v>63.19613562287174</v>
+        <v>63.12480272935814</v>
       </c>
       <c r="I10">
-        <v>2.185195978690271</v>
+        <v>1.730828885580657</v>
       </c>
       <c r="J10">
-        <v>24.90369003134081</v>
+        <v>25.15923379654071</v>
       </c>
       <c r="K10">
-        <v>3.485061096716237</v>
+        <v>3.012771809192495</v>
       </c>
       <c r="L10">
-        <v>195.463688344778</v>
+        <v>196.5185913428093</v>
       </c>
       <c r="M10">
-        <v>10.13494330341044</v>
+        <v>7.760716053665978</v>
       </c>
       <c r="N10">
-        <v>51.75174609493043</v>
+        <v>51.58508000104987</v>
       </c>
       <c r="O10">
-        <v>2.085030137254415</v>
+        <v>1.855191115052647</v>
       </c>
       <c r="P10">
-        <v>344.5241726402172</v>
+        <v>342.730374173802</v>
       </c>
       <c r="Q10">
-        <v>5.331851482284523</v>
+        <v>5.645697449393573</v>
       </c>
       <c r="R10">
-        <v>4.003897271897484</v>
+        <v>3.947189715503322</v>
       </c>
       <c r="S10">
-        <v>0.4295108135839393</v>
+        <v>0.4577298977062312</v>
       </c>
       <c r="T10">
-        <v>28.76898729283526</v>
+        <v>28.15121197069307</v>
       </c>
       <c r="U10">
-        <v>1.103780119290714</v>
+        <v>1.212365728360612</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -3285,64 +3285,64 @@
         <v>2029</v>
       </c>
       <c r="B11">
-        <v>96.5482921813462</v>
+        <v>96.20086273848023</v>
       </c>
       <c r="C11">
-        <v>6.786374106708037</v>
+        <v>6.307482570279485</v>
       </c>
       <c r="D11">
-        <v>730.0528409989884</v>
+        <v>725.3191805495089</v>
       </c>
       <c r="E11">
-        <v>14.69417817010416</v>
+        <v>13.81446470871512</v>
       </c>
       <c r="F11">
-        <v>9.593951293514131</v>
+        <v>9.422647751762211</v>
       </c>
       <c r="G11">
-        <v>0.8175905165446359</v>
+        <v>1.026958380259368</v>
       </c>
       <c r="H11">
-        <v>72.79008691638585</v>
+        <v>72.54745048112038</v>
       </c>
       <c r="I11">
-        <v>2.245224770096184</v>
+        <v>2.040406771134653</v>
       </c>
       <c r="J11">
-        <v>27.53299147883016</v>
+        <v>25.82224973728584</v>
       </c>
       <c r="K11">
-        <v>3.076860630488339</v>
+        <v>3.088419040592255</v>
       </c>
       <c r="L11">
-        <v>222.9966798236081</v>
+        <v>222.3408410800952</v>
       </c>
       <c r="M11">
-        <v>10.3960855074618</v>
+        <v>8.170085347770872</v>
       </c>
       <c r="N11">
-        <v>54.83115439281475</v>
+        <v>54.69152825840616</v>
       </c>
       <c r="O11">
-        <v>2.705492224480921</v>
+        <v>2.532866978470969</v>
       </c>
       <c r="P11">
-        <v>399.3553270330319</v>
+        <v>397.4219024322081</v>
       </c>
       <c r="Q11">
-        <v>6.220521848491533</v>
+        <v>5.955482442457446</v>
       </c>
       <c r="R11">
-        <v>4.377131458720441</v>
+        <v>4.380990771279371</v>
       </c>
       <c r="S11">
-        <v>0.4943279805493067</v>
+        <v>0.454098511441366</v>
       </c>
       <c r="T11">
-        <v>33.1461187515557</v>
+        <v>32.53220274197245</v>
       </c>
       <c r="U11">
-        <v>1.104438995935254</v>
+        <v>1.284671891911388</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -3350,64 +3350,64 @@
         <v>2030</v>
       </c>
       <c r="B12">
-        <v>100.5365971061737</v>
+        <v>99.49319704361611</v>
       </c>
       <c r="C12">
-        <v>5.51019054207956</v>
+        <v>4.651662286092257</v>
       </c>
       <c r="D12">
-        <v>830.5894381051621</v>
+        <v>824.812377593125</v>
       </c>
       <c r="E12">
-        <v>14.63430832870725</v>
+        <v>14.96217728664171</v>
       </c>
       <c r="F12">
-        <v>10.28970833928713</v>
+        <v>10.17252913743659</v>
       </c>
       <c r="G12">
-        <v>0.9209066096450853</v>
+        <v>0.7512832979047136</v>
       </c>
       <c r="H12">
-        <v>83.07979525567298</v>
+        <v>82.71997961855693</v>
       </c>
       <c r="I12">
-        <v>2.21335232954246</v>
+        <v>2.24868896324348</v>
       </c>
       <c r="J12">
-        <v>28.21654286501281</v>
+        <v>27.75238422696063</v>
       </c>
       <c r="K12">
-        <v>3.414633398855992</v>
+        <v>3.504216695103415</v>
       </c>
       <c r="L12">
-        <v>251.2132226886209</v>
+        <v>250.0932253070558</v>
       </c>
       <c r="M12">
-        <v>10.89288338947542</v>
+        <v>9.521484763062675</v>
       </c>
       <c r="N12">
-        <v>58.37419718163251</v>
+        <v>57.99773013712204</v>
       </c>
       <c r="O12">
-        <v>2.323042680692596</v>
+        <v>2.326198942388799</v>
       </c>
       <c r="P12">
-        <v>457.7295242146645</v>
+        <v>455.4196325693302</v>
       </c>
       <c r="Q12">
-        <v>6.419113427295243</v>
+        <v>6.819226109570339</v>
       </c>
       <c r="R12">
-        <v>4.482066149495769</v>
+        <v>4.467768908305294</v>
       </c>
       <c r="S12">
-        <v>0.5214101156522724</v>
+        <v>0.5188156163577634</v>
       </c>
       <c r="T12">
-        <v>37.62818490105148</v>
+        <v>36.99997165027775</v>
       </c>
       <c r="U12">
-        <v>1.168357951226373</v>
+        <v>1.521957539457721</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -3415,64 +3415,64 @@
         <v>2031</v>
       </c>
       <c r="B13">
-        <v>4.96306769192384</v>
+        <v>5.034852664688315</v>
       </c>
       <c r="C13">
-        <v>0.3575408954078905</v>
+        <v>0.3215102335926248</v>
       </c>
       <c r="D13">
-        <v>835.5525057970858</v>
+        <v>829.8472302578134</v>
       </c>
       <c r="E13">
-        <v>14.68795042583962</v>
+        <v>14.93481226545649</v>
       </c>
       <c r="F13">
-        <v>0.4938409508961342</v>
+        <v>0.488634129918365</v>
       </c>
       <c r="G13">
-        <v>0.04351263995507974</v>
+        <v>0.04022006517907811</v>
       </c>
       <c r="H13">
-        <v>83.57363620656911</v>
+        <v>83.20861374847533</v>
       </c>
       <c r="I13">
-        <v>2.219015525531967</v>
+        <v>2.245876549250243</v>
       </c>
       <c r="J13">
-        <v>-22.38276587093704</v>
+        <v>-22.21744361845234</v>
       </c>
       <c r="K13">
-        <v>1.07179850436561</v>
+        <v>1.121016707083125</v>
       </c>
       <c r="L13">
-        <v>228.830456817684</v>
+        <v>227.8757816886035</v>
       </c>
       <c r="M13">
-        <v>11.2041162144057</v>
+        <v>9.453718018167713</v>
       </c>
       <c r="N13">
-        <v>26.61114164375449</v>
+        <v>26.49287186543965</v>
       </c>
       <c r="O13">
-        <v>1.079234670919509</v>
+        <v>1.149558905130166</v>
       </c>
       <c r="P13">
-        <v>484.340665858419</v>
+        <v>481.9125044347697</v>
       </c>
       <c r="Q13">
-        <v>6.548717087827585</v>
+        <v>6.882850475017121</v>
       </c>
       <c r="R13">
-        <v>0.2294336802307498</v>
+        <v>0.232107828571531</v>
       </c>
       <c r="S13">
-        <v>0.02655896142331275</v>
+        <v>0.02474247993098665</v>
       </c>
       <c r="T13">
-        <v>37.85761858128222</v>
+        <v>37.23207947884926</v>
       </c>
       <c r="U13">
-        <v>1.171579922914737</v>
+        <v>1.525468578520147</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -3480,64 +3480,64 @@
         <v>2032</v>
       </c>
       <c r="B14">
-        <v>109.94408266929</v>
+        <v>110.1881756583443</v>
       </c>
       <c r="C14">
-        <v>7.568462038282229</v>
+        <v>6.574460869264921</v>
       </c>
       <c r="D14">
-        <v>945.496588466376</v>
+        <v>940.0354059161577</v>
       </c>
       <c r="E14">
-        <v>17.38828262712262</v>
+        <v>16.5184135063484</v>
       </c>
       <c r="F14">
-        <v>11.00988323819557</v>
+        <v>11.02686540346899</v>
       </c>
       <c r="G14">
-        <v>0.8589248754794996</v>
+        <v>0.7655752384803146</v>
       </c>
       <c r="H14">
-        <v>94.58351944476468</v>
+        <v>94.23547915194429</v>
       </c>
       <c r="I14">
-        <v>2.343129794424324</v>
+        <v>2.44248654190118</v>
       </c>
       <c r="J14">
-        <v>46.93383236918077</v>
+        <v>46.07857607556789</v>
       </c>
       <c r="K14">
-        <v>3.573272801781011</v>
+        <v>4.013998452338887</v>
       </c>
       <c r="L14">
-        <v>275.7642891868646</v>
+        <v>273.9543577641713</v>
       </c>
       <c r="M14">
-        <v>12.22897688933398</v>
+        <v>9.904128924359311</v>
       </c>
       <c r="N14">
-        <v>47.33531900971998</v>
+        <v>47.18485157843545</v>
       </c>
       <c r="O14">
-        <v>2.525744315155611</v>
+        <v>2.510007412038156</v>
       </c>
       <c r="P14">
-        <v>531.675984868139</v>
+        <v>529.0973560132053</v>
       </c>
       <c r="Q14">
-        <v>7.167438437489137</v>
+        <v>7.719189841688086</v>
       </c>
       <c r="R14">
-        <v>4.844707357959497</v>
+        <v>4.846666047482144</v>
       </c>
       <c r="S14">
-        <v>0.5006528146953788</v>
+        <v>0.528172138871399</v>
       </c>
       <c r="T14">
-        <v>42.70232593924172</v>
+        <v>42.0787455263314</v>
       </c>
       <c r="U14">
-        <v>1.139188549663417</v>
+        <v>1.616926139828833</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -3545,64 +3545,64 @@
         <v>2033</v>
       </c>
       <c r="B15">
-        <v>115.0690247835456</v>
+        <v>114.1698285244135</v>
       </c>
       <c r="C15">
-        <v>7.473711825895886</v>
+        <v>6.115110142787806</v>
       </c>
       <c r="D15">
-        <v>1060.565613249922</v>
+        <v>1054.205234440571</v>
       </c>
       <c r="E15">
-        <v>19.34712804446976</v>
+        <v>18.62930344606055</v>
       </c>
       <c r="F15">
-        <v>11.61390468085213</v>
+        <v>11.38775720760655</v>
       </c>
       <c r="G15">
-        <v>0.9583488220063886</v>
+        <v>1.179878481142806</v>
       </c>
       <c r="H15">
-        <v>106.1974241256168</v>
+        <v>105.6232363595509</v>
       </c>
       <c r="I15">
-        <v>2.468523871532108</v>
+        <v>2.684244921536594</v>
       </c>
       <c r="J15">
-        <v>37.01891387408514</v>
+        <v>37.22325865944843</v>
       </c>
       <c r="K15">
-        <v>3.815372023993573</v>
+        <v>3.51881642054896</v>
       </c>
       <c r="L15">
-        <v>312.7832030609497</v>
+        <v>311.1776164236198</v>
       </c>
       <c r="M15">
-        <v>12.83668244407194</v>
+        <v>10.76790653804124</v>
       </c>
       <c r="N15">
-        <v>61.74470785302859</v>
+        <v>60.63742472078577</v>
       </c>
       <c r="O15">
-        <v>3.00870976158528</v>
+        <v>3.153998878065759</v>
       </c>
       <c r="P15">
-        <v>593.4206927211676</v>
+        <v>589.7347807339912</v>
       </c>
       <c r="Q15">
-        <v>7.749035703555225</v>
+        <v>9.321762869015616</v>
       </c>
       <c r="R15">
-        <v>5.034018965305209</v>
+        <v>5.168647304309602</v>
       </c>
       <c r="S15">
-        <v>0.5829366723677003</v>
+        <v>0.6661360380584068</v>
       </c>
       <c r="T15">
-        <v>47.73634490454694</v>
+        <v>47.24739283064102</v>
       </c>
       <c r="U15">
-        <v>1.243403447234189</v>
+        <v>1.767718930570887</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -3610,64 +3610,64 @@
         <v>2034</v>
       </c>
       <c r="B16">
-        <v>121.4945412313238</v>
+        <v>120.9115785252184</v>
       </c>
       <c r="C16">
-        <v>7.995843448649803</v>
+        <v>6.292735000800104</v>
       </c>
       <c r="D16">
-        <v>1182.060154481245</v>
+        <v>1175.11681296579</v>
       </c>
       <c r="E16">
-        <v>19.90421973511231</v>
+        <v>18.95376866996054</v>
       </c>
       <c r="F16">
-        <v>11.95203965471728</v>
+        <v>11.90734008782399</v>
       </c>
       <c r="G16">
-        <v>1.258372681407443</v>
+        <v>1.040214907440805</v>
       </c>
       <c r="H16">
-        <v>118.149463780334</v>
+        <v>117.5305764473748</v>
       </c>
       <c r="I16">
-        <v>2.632459647645569</v>
+        <v>3.070436385152675</v>
       </c>
       <c r="J16">
-        <v>34.59804593111185</v>
+        <v>35.60051235859834</v>
       </c>
       <c r="K16">
-        <v>4.303928588898661</v>
+        <v>4.375155213745185</v>
       </c>
       <c r="L16">
-        <v>347.3812489920616</v>
+        <v>346.7781287822182</v>
       </c>
       <c r="M16">
-        <v>14.28027649388266</v>
+        <v>11.67469007708417</v>
       </c>
       <c r="N16">
-        <v>67.85596938868719</v>
+        <v>67.27865478286921</v>
       </c>
       <c r="O16">
-        <v>3.719351032314043</v>
+        <v>3.06624607534494</v>
       </c>
       <c r="P16">
-        <v>661.2766621098547</v>
+        <v>657.0134355168602</v>
       </c>
       <c r="Q16">
-        <v>7.934441824895567</v>
+        <v>9.504096750854798</v>
       </c>
       <c r="R16">
-        <v>5.549124782107046</v>
+        <v>5.505440851204591</v>
       </c>
       <c r="S16">
-        <v>0.6168418189922523</v>
+        <v>0.6973164814900846</v>
       </c>
       <c r="T16">
-        <v>53.28546968665397</v>
+        <v>52.75283368184559</v>
       </c>
       <c r="U16">
-        <v>1.367041743932463</v>
+        <v>1.831121213037622</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -3675,64 +3675,64 @@
         <v>2035</v>
       </c>
       <c r="B17">
-        <v>123.7462191688878</v>
+        <v>126.6854902733556</v>
       </c>
       <c r="C17">
-        <v>7.671069770159747</v>
+        <v>7.212554576954148</v>
       </c>
       <c r="D17">
-        <v>1305.806373650133</v>
+        <v>1301.802303239145</v>
       </c>
       <c r="E17">
-        <v>20.26976288707607</v>
+        <v>20.11695562950943</v>
       </c>
       <c r="F17">
-        <v>12.93690883118416</v>
+        <v>12.51313894133322</v>
       </c>
       <c r="G17">
-        <v>1.036343703103887</v>
+        <v>1.04841199997707</v>
       </c>
       <c r="H17">
-        <v>131.0863726115182</v>
+        <v>130.0437153887081</v>
       </c>
       <c r="I17">
-        <v>2.767957400887186</v>
+        <v>3.043574618530857</v>
       </c>
       <c r="J17">
-        <v>35.68829175917131</v>
+        <v>35.5045593433412</v>
       </c>
       <c r="K17">
-        <v>4.475563532138921</v>
+        <v>5.317928991418042</v>
       </c>
       <c r="L17">
-        <v>383.0695407512329</v>
+        <v>382.2826881255594</v>
       </c>
       <c r="M17">
-        <v>14.46459318990157</v>
+        <v>13.215969363325</v>
       </c>
       <c r="N17">
-        <v>73.46678048419344</v>
+        <v>71.88756452801712</v>
       </c>
       <c r="O17">
-        <v>2.871488551974271</v>
+        <v>3.591247736315078</v>
       </c>
       <c r="P17">
-        <v>734.7434425940482</v>
+        <v>728.9010000448773</v>
       </c>
       <c r="Q17">
-        <v>7.484333879750534</v>
+        <v>10.16760953738855</v>
       </c>
       <c r="R17">
-        <v>5.731804700475699</v>
+        <v>5.801875508220352</v>
       </c>
       <c r="S17">
-        <v>0.6168648116551047</v>
+        <v>0.7943681588744124</v>
       </c>
       <c r="T17">
-        <v>59.01727438712967</v>
+        <v>58.55470919006597</v>
       </c>
       <c r="U17">
-        <v>1.36261104958242</v>
+        <v>2.116330757332569</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -3740,64 +3740,64 @@
         <v>2036</v>
       </c>
       <c r="B18">
-        <v>128.4848720019804</v>
+        <v>128.0364649514355</v>
       </c>
       <c r="C18">
-        <v>7.166212240204943</v>
+        <v>8.133443447914372</v>
       </c>
       <c r="D18">
-        <v>1434.291245652114</v>
+        <v>1429.838768190581</v>
       </c>
       <c r="E18">
-        <v>21.58949277017355</v>
+        <v>21.28479208070671</v>
       </c>
       <c r="F18">
-        <v>12.78072152842234</v>
+        <v>13.11087051231128</v>
       </c>
       <c r="G18">
-        <v>1.035583712788841</v>
+        <v>1.102299422209987</v>
       </c>
       <c r="H18">
-        <v>143.8670941399405</v>
+        <v>143.1545859010193</v>
       </c>
       <c r="I18">
-        <v>3.031923805064269</v>
+        <v>3.387042106566853</v>
       </c>
       <c r="J18">
-        <v>35.71909895179787</v>
+        <v>35.50564099994132</v>
       </c>
       <c r="K18">
-        <v>4.612173152546778</v>
+        <v>5.004648593882504</v>
       </c>
       <c r="L18">
-        <v>418.7886397030309</v>
+        <v>417.7883291255008</v>
       </c>
       <c r="M18">
-        <v>15.90694612083122</v>
+        <v>15.14496692518865</v>
       </c>
       <c r="N18">
-        <v>75.36526018711021</v>
+        <v>76.03699793894157</v>
       </c>
       <c r="O18">
-        <v>2.714599407154843</v>
+        <v>3.399811550306125</v>
       </c>
       <c r="P18">
-        <v>810.1087027811585</v>
+        <v>804.9379979838188</v>
       </c>
       <c r="Q18">
-        <v>7.897581438900831</v>
+        <v>11.68162784966407</v>
       </c>
       <c r="R18">
-        <v>5.684981247227537</v>
+        <v>5.968131407300851</v>
       </c>
       <c r="S18">
-        <v>0.6237727741670931</v>
+        <v>0.5786656214747021</v>
       </c>
       <c r="T18">
-        <v>64.7022556343572</v>
+        <v>64.52284059736679</v>
       </c>
       <c r="U18">
-        <v>1.520032833444774</v>
+        <v>2.2683901074746</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -3805,64 +3805,64 @@
         <v>2037</v>
       </c>
       <c r="B19">
-        <v>135.6187486293811</v>
+        <v>135.2202483110052</v>
       </c>
       <c r="C19">
-        <v>8.289130160632219</v>
+        <v>8.642332270980875</v>
       </c>
       <c r="D19">
-        <v>1569.909994281495</v>
+        <v>1565.059016501585</v>
       </c>
       <c r="E19">
-        <v>23.77936539311888</v>
+        <v>23.38660301719108</v>
       </c>
       <c r="F19">
-        <v>13.37103189510567</v>
+        <v>13.38876202875087</v>
       </c>
       <c r="G19">
-        <v>1.211337871939661</v>
+        <v>1.141340987644304</v>
       </c>
       <c r="H19">
-        <v>157.2381260350463</v>
+        <v>156.5433479297702</v>
       </c>
       <c r="I19">
-        <v>3.273165163395022</v>
+        <v>3.37044248231498</v>
       </c>
       <c r="J19">
-        <v>36.95462661551844</v>
+        <v>36.1652207952095</v>
       </c>
       <c r="K19">
-        <v>6.057763965700129</v>
+        <v>4.301566135288085</v>
       </c>
       <c r="L19">
-        <v>455.7432663185495</v>
+        <v>453.9535499207102</v>
       </c>
       <c r="M19">
-        <v>16.24381209770313</v>
+        <v>15.60134663003281</v>
       </c>
       <c r="N19">
-        <v>79.54025752517821</v>
+        <v>78.6094734713939</v>
       </c>
       <c r="O19">
-        <v>3.332863237552302</v>
+        <v>2.976396084130595</v>
       </c>
       <c r="P19">
-        <v>889.6489603063367</v>
+        <v>883.5474714552126</v>
       </c>
       <c r="Q19">
-        <v>9.153371185777411</v>
+        <v>12.32513162718145</v>
       </c>
       <c r="R19">
-        <v>6.03777245503243</v>
+        <v>6.091984750886077</v>
       </c>
       <c r="S19">
-        <v>0.6143716167438155</v>
+        <v>0.4799532532772439</v>
       </c>
       <c r="T19">
-        <v>70.74002808938965</v>
+        <v>70.61482534825286</v>
       </c>
       <c r="U19">
-        <v>1.729181481053401</v>
+        <v>2.309658179016924</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -3870,64 +3870,64 @@
         <v>2038</v>
       </c>
       <c r="B20">
-        <v>140.0071567166134</v>
+        <v>141.0461372254723</v>
       </c>
       <c r="C20">
-        <v>7.647462801756485</v>
+        <v>9.756221514738273</v>
       </c>
       <c r="D20">
-        <v>1709.917150998108</v>
+        <v>1706.105153727059</v>
       </c>
       <c r="E20">
-        <v>26.10320641360433</v>
+        <v>28.48021201367469</v>
       </c>
       <c r="F20">
-        <v>13.88158178215427</v>
+        <v>13.74309957318855</v>
       </c>
       <c r="G20">
-        <v>1.070939599701074</v>
+        <v>1.265231554255073</v>
       </c>
       <c r="H20">
-        <v>171.1197078172005</v>
+        <v>170.2864475029588</v>
       </c>
       <c r="I20">
-        <v>3.430955892723521</v>
+        <v>3.860997386952461</v>
       </c>
       <c r="J20">
-        <v>36.34431411365119</v>
+        <v>37.45599975666367</v>
       </c>
       <c r="K20">
-        <v>4.347895706524719</v>
+        <v>5.204076384401596</v>
       </c>
       <c r="L20">
-        <v>492.0875804322006</v>
+        <v>491.4095496773739</v>
       </c>
       <c r="M20">
-        <v>17.60982771718689</v>
+        <v>16.45694106575012</v>
       </c>
       <c r="N20">
-        <v>81.65069295070001</v>
+        <v>80.80392141554485</v>
       </c>
       <c r="O20">
-        <v>3.619799483328964</v>
+        <v>3.867774560388998</v>
       </c>
       <c r="P20">
-        <v>971.299653257037</v>
+        <v>964.351392870758</v>
       </c>
       <c r="Q20">
-        <v>10.41000762752269</v>
+        <v>13.9435334985089</v>
       </c>
       <c r="R20">
-        <v>6.242892604810628</v>
+        <v>6.288184130853799</v>
       </c>
       <c r="S20">
-        <v>0.7277447522080653</v>
+        <v>0.723867837872305</v>
       </c>
       <c r="T20">
-        <v>76.98292069420026</v>
+        <v>76.90300947910667</v>
       </c>
       <c r="U20">
-        <v>1.917600394804106</v>
+        <v>2.598816632717811</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -3935,64 +3935,64 @@
         <v>2039</v>
       </c>
       <c r="B21">
-        <v>145.9589959137425</v>
+        <v>144.3851681554447</v>
       </c>
       <c r="C21">
-        <v>9.378734230831009</v>
+        <v>7.545617962740461</v>
       </c>
       <c r="D21">
-        <v>1855.876146911851</v>
+        <v>1850.490321882502</v>
       </c>
       <c r="E21">
-        <v>30.32309924492946</v>
+        <v>28.11558877130384</v>
       </c>
       <c r="F21">
-        <v>14.34963111267409</v>
+        <v>14.40439629256414</v>
       </c>
       <c r="G21">
-        <v>1.250361129848153</v>
+        <v>1.224225835812796</v>
       </c>
       <c r="H21">
-        <v>185.4693389298746</v>
+        <v>184.6908437955229</v>
       </c>
       <c r="I21">
-        <v>3.638096171396279</v>
+        <v>3.903465659648022</v>
       </c>
       <c r="J21">
-        <v>39.51731723672244</v>
+        <v>38.68288107042201</v>
       </c>
       <c r="K21">
-        <v>6.374387694429575</v>
+        <v>5.250807578953673</v>
       </c>
       <c r="L21">
-        <v>531.6048976689231</v>
+        <v>530.092430747796</v>
       </c>
       <c r="M21">
-        <v>18.57421948593164</v>
+        <v>17.31142051287903</v>
       </c>
       <c r="N21">
-        <v>84.59010357689613</v>
+        <v>84.55880382401594</v>
       </c>
       <c r="O21">
-        <v>3.549384798045285</v>
+        <v>3.283951621661219</v>
       </c>
       <c r="P21">
-        <v>1055.889756833933</v>
+        <v>1048.910196694774</v>
       </c>
       <c r="Q21">
-        <v>11.81666898233022</v>
+        <v>14.51169701889111</v>
       </c>
       <c r="R21">
-        <v>6.375742706484647</v>
+        <v>6.541281747931266</v>
       </c>
       <c r="S21">
-        <v>0.9028712732922046</v>
+        <v>0.7837316587308233</v>
       </c>
       <c r="T21">
-        <v>83.35866340068493</v>
+        <v>83.44429122703795</v>
       </c>
       <c r="U21">
-        <v>2.093546208161964</v>
+        <v>2.71121241925157</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -4000,64 +4000,64 @@
         <v>2040</v>
       </c>
       <c r="B22">
-        <v>149.3750372937881</v>
+        <v>149.6309601850286</v>
       </c>
       <c r="C22">
-        <v>9.612181834729199</v>
+        <v>11.11627888808195</v>
       </c>
       <c r="D22">
-        <v>2005.251184205638</v>
+        <v>2000.121282067532</v>
       </c>
       <c r="E22">
-        <v>31.5835913681644</v>
+        <v>32.45321495189157</v>
       </c>
       <c r="F22">
-        <v>15.01197955609378</v>
+        <v>15.04232466649709</v>
       </c>
       <c r="G22">
-        <v>1.21574938566417</v>
+        <v>1.458054523353026</v>
       </c>
       <c r="H22">
-        <v>200.4813184859684</v>
+        <v>199.73316846202</v>
       </c>
       <c r="I22">
-        <v>3.911599322643212</v>
+        <v>4.509062876031763</v>
       </c>
       <c r="J22">
-        <v>40.44525704816366</v>
+        <v>41.01390359103568</v>
       </c>
       <c r="K22">
-        <v>5.733972167590987</v>
+        <v>5.902873946957387</v>
       </c>
       <c r="L22">
-        <v>572.0501547170866</v>
+        <v>571.1063343388316</v>
       </c>
       <c r="M22">
-        <v>19.09913484118263</v>
+        <v>18.72304570819672</v>
       </c>
       <c r="N22">
-        <v>87.74957517870904</v>
+        <v>87.84213477265084</v>
       </c>
       <c r="O22">
-        <v>3.803114691723235</v>
+        <v>4.257577177721902</v>
       </c>
       <c r="P22">
-        <v>1143.639332012642</v>
+        <v>1136.752331467424</v>
       </c>
       <c r="Q22">
-        <v>11.8844019598394</v>
+        <v>15.57188788580021</v>
       </c>
       <c r="R22">
-        <v>6.711755635246006</v>
+        <v>6.81385580145724</v>
       </c>
       <c r="S22">
-        <v>0.7361296304860564</v>
+        <v>0.7398791915519396</v>
       </c>
       <c r="T22">
-        <v>90.07041903593094</v>
+        <v>90.2581470284952</v>
       </c>
       <c r="U22">
-        <v>2.403297023876302</v>
+        <v>2.726091535039786</v>
       </c>
     </row>
   </sheetData>
@@ -4170,88 +4170,88 @@
         <v>2020</v>
       </c>
       <c r="B2">
-        <v>50.52090660970934</v>
+        <v>50.15709659747338</v>
       </c>
       <c r="C2">
-        <v>2.442730839690111</v>
+        <v>2.298016927555033</v>
       </c>
       <c r="D2">
-        <v>25.35411340129717</v>
+        <v>25.24457228895476</v>
       </c>
       <c r="E2">
-        <v>1.540564839277451</v>
+        <v>1.292897462832222</v>
       </c>
       <c r="F2">
-        <v>25.16679320841217</v>
+        <v>24.91252430851864</v>
       </c>
       <c r="G2">
-        <v>1.512309187087165</v>
+        <v>1.612979688921338</v>
       </c>
       <c r="H2">
-        <v>7.553095832432629</v>
+        <v>7.482989052508585</v>
       </c>
       <c r="I2">
-        <v>0.6180404843571209</v>
+        <v>0.6049954505556686</v>
       </c>
       <c r="J2">
-        <v>7.559032952264459</v>
+        <v>7.490055196866603</v>
       </c>
       <c r="K2">
-        <v>0.5706240929109944</v>
+        <v>0.5556095259693711</v>
       </c>
       <c r="L2">
-        <v>2.488464995840658</v>
+        <v>2.501863619362353</v>
       </c>
       <c r="M2">
-        <v>0.2231091030356355</v>
+        <v>0.2366183359445581</v>
       </c>
       <c r="N2">
-        <v>5.038067084437897</v>
+        <v>4.952744923622959</v>
       </c>
       <c r="O2">
-        <v>0.369934143794329</v>
+        <v>0.3833465705222328</v>
       </c>
       <c r="P2">
-        <v>2.528132343436519</v>
+        <v>2.484871516158154</v>
       </c>
       <c r="Q2">
-        <v>0.2222482511852688</v>
+        <v>0.2097810819799739</v>
       </c>
       <c r="R2">
-        <v>7.553095832432629</v>
+        <v>7.482989052508585</v>
       </c>
       <c r="S2">
-        <v>0.6180404843571209</v>
+        <v>0.6049954505556686</v>
       </c>
       <c r="T2">
-        <v>5.297143711060072</v>
+        <v>5.1760405519452</v>
       </c>
       <c r="U2">
-        <v>0.4084651296644295</v>
+        <v>0.4389695190626279</v>
       </c>
       <c r="V2">
-        <v>1.126555336008219</v>
+        <v>1.145562339575095</v>
       </c>
       <c r="W2">
-        <v>0.1326552180274501</v>
+        <v>0.1104824354414678</v>
       </c>
       <c r="X2">
-        <v>1.135333905196172</v>
+        <v>1.168452305346305</v>
       </c>
       <c r="Y2">
-        <v>0.1364416762387468</v>
+        <v>0.114166934431957</v>
       </c>
       <c r="Z2">
-        <v>2.488464995840658</v>
+        <v>2.501863619362353</v>
       </c>
       <c r="AA2">
-        <v>0.2231091030356355</v>
+        <v>0.2366183359445581</v>
       </c>
       <c r="AB2">
-        <v>5.038067084437897</v>
+        <v>4.952744923622959</v>
       </c>
       <c r="AC2">
-        <v>0.369934143794329</v>
+        <v>0.3833465705222328</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -4265,94 +4265,94 @@
         <v>2021</v>
       </c>
       <c r="B3">
-        <v>55.35754554107311</v>
+        <v>54.5749989591418</v>
       </c>
       <c r="C3">
-        <v>2.822824177817124</v>
+        <v>2.763180797607538</v>
       </c>
       <c r="D3">
-        <v>27.6887940990326</v>
+        <v>27.25683682824483</v>
       </c>
       <c r="E3">
-        <v>1.826930315970957</v>
+        <v>1.694331535370261</v>
       </c>
       <c r="F3">
-        <v>27.66875144204049</v>
+        <v>27.31816213089696</v>
       </c>
       <c r="G3">
-        <v>1.532263572042919</v>
+        <v>1.795154030645533</v>
       </c>
       <c r="H3">
-        <v>8.251373211243013</v>
+        <v>8.121812845747307</v>
       </c>
       <c r="I3">
-        <v>0.5947432511206791</v>
+        <v>0.5187672539780153</v>
       </c>
       <c r="J3">
-        <v>8.298103790135549</v>
+        <v>8.282444477884937</v>
       </c>
       <c r="K3">
-        <v>0.496884625125131</v>
+        <v>0.695643543160096</v>
       </c>
       <c r="L3">
-        <v>2.791823920865422</v>
+        <v>2.742180556989529</v>
       </c>
       <c r="M3">
-        <v>0.2348117057505</v>
+        <v>0.2503635720142078</v>
       </c>
       <c r="N3">
-        <v>5.585581842364908</v>
+        <v>5.448302090930329</v>
       </c>
       <c r="O3">
-        <v>0.4373522021562828</v>
+        <v>0.4224908053716967</v>
       </c>
       <c r="P3">
-        <v>2.741868677431609</v>
+        <v>2.723422159344876</v>
       </c>
       <c r="Q3">
-        <v>0.246024078556095</v>
+        <v>0.2450846217271386</v>
       </c>
       <c r="R3">
-        <v>8.251373211243013</v>
+        <v>8.121812845747307</v>
       </c>
       <c r="S3">
-        <v>0.5947432511206791</v>
+        <v>0.5187672539780153</v>
       </c>
       <c r="T3">
-        <v>5.817685607491807</v>
+        <v>5.822299292722159</v>
       </c>
       <c r="U3">
-        <v>0.3740676576515737</v>
+        <v>0.5224386465180186</v>
       </c>
       <c r="V3">
-        <v>1.23462787805169</v>
+        <v>1.22427042875409</v>
       </c>
       <c r="W3">
-        <v>0.1147456384382336</v>
+        <v>0.1387831678231171</v>
       </c>
       <c r="X3">
-        <v>1.245790304592054</v>
+        <v>1.235874756408689</v>
       </c>
       <c r="Y3">
-        <v>0.1262950988268673</v>
+        <v>0.1321268927049191</v>
       </c>
       <c r="Z3">
-        <v>2.791823920865422</v>
+        <v>2.742180556989529</v>
       </c>
       <c r="AA3">
-        <v>0.2348117057505</v>
+        <v>0.2503635720142078</v>
       </c>
       <c r="AB3">
-        <v>5.585581842364908</v>
+        <v>5.448302090930329</v>
       </c>
       <c r="AC3">
-        <v>0.4373522021562828</v>
+        <v>0.4224908053716967</v>
       </c>
       <c r="AD3">
-        <v>8.432478015182891</v>
+        <v>8.145441325734485</v>
       </c>
       <c r="AE3">
-        <v>0.732956966255864</v>
+        <v>0.6854890023616238</v>
       </c>
     </row>
     <row r="4" spans="1:31">
@@ -4360,94 +4360,94 @@
         <v>2022</v>
       </c>
       <c r="B4">
-        <v>59.8373730303021</v>
+        <v>59.97962593672386</v>
       </c>
       <c r="C4">
-        <v>2.327699940557668</v>
+        <v>3.162922518716615</v>
       </c>
       <c r="D4">
-        <v>29.79250135683034</v>
+        <v>30.03334825807666</v>
       </c>
       <c r="E4">
-        <v>1.692769173129575</v>
+        <v>1.948460192300637</v>
       </c>
       <c r="F4">
-        <v>30.04487167347177</v>
+        <v>29.9462776786472</v>
       </c>
       <c r="G4">
-        <v>1.580587729867778</v>
+        <v>1.878936611593927</v>
       </c>
       <c r="H4">
-        <v>8.996454036861371</v>
+        <v>8.919046222012186</v>
       </c>
       <c r="I4">
-        <v>0.5584122430428481</v>
+        <v>0.7106214800027341</v>
       </c>
       <c r="J4">
-        <v>9.042543039441078</v>
+        <v>9.000600770379579</v>
       </c>
       <c r="K4">
-        <v>0.5756387642504043</v>
+        <v>0.6298395447107982</v>
       </c>
       <c r="L4">
-        <v>3.012446731939148</v>
+        <v>2.995195106497945</v>
       </c>
       <c r="M4">
-        <v>0.2325472532566834</v>
+        <v>0.2170454228292127</v>
       </c>
       <c r="N4">
-        <v>5.97334056959089</v>
+        <v>6.024547632248227</v>
       </c>
       <c r="O4">
-        <v>0.3902827220186278</v>
+        <v>0.5039268752554852</v>
       </c>
       <c r="P4">
-        <v>3.020087295639284</v>
+        <v>3.006887947509259</v>
       </c>
       <c r="Q4">
-        <v>0.2530141099849345</v>
+        <v>0.2389280696980747</v>
       </c>
       <c r="R4">
-        <v>8.996454036861371</v>
+        <v>8.919046222012186</v>
       </c>
       <c r="S4">
-        <v>0.5584122430428481</v>
+        <v>0.7106214800027341</v>
       </c>
       <c r="T4">
-        <v>6.341993413113522</v>
+        <v>6.255897888587533</v>
       </c>
       <c r="U4">
-        <v>0.4656524768159477</v>
+        <v>0.4897548966620001</v>
       </c>
       <c r="V4">
-        <v>1.346711124462645</v>
+        <v>1.374751935239492</v>
       </c>
       <c r="W4">
-        <v>0.1503619751683794</v>
+        <v>0.1518780908890732</v>
       </c>
       <c r="X4">
-        <v>1.353838501864912</v>
+        <v>1.369950946552552</v>
       </c>
       <c r="Y4">
-        <v>0.1392381788131636</v>
+        <v>0.1225055319518751</v>
       </c>
       <c r="Z4">
-        <v>3.012446731939148</v>
+        <v>2.995195106497945</v>
       </c>
       <c r="AA4">
-        <v>0.2325472532566834</v>
+        <v>0.2170454228292127</v>
       </c>
       <c r="AB4">
-        <v>5.97334056959089</v>
+        <v>6.024547632248227</v>
       </c>
       <c r="AC4">
-        <v>0.3902827220186278</v>
+        <v>0.5039268752554852</v>
       </c>
       <c r="AD4">
-        <v>12.03977937623752</v>
+        <v>11.78263359053208</v>
       </c>
       <c r="AE4">
-        <v>0.6911221910382833</v>
+        <v>0.6910499037910857</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -4455,94 +4455,94 @@
         <v>2023</v>
       </c>
       <c r="B5">
-        <v>64.73968505739589</v>
+        <v>65.29576091856751</v>
       </c>
       <c r="C5">
-        <v>3.13867341463577</v>
+        <v>3.238463163353375</v>
       </c>
       <c r="D5">
-        <v>32.111708924642</v>
+        <v>32.85914439918344</v>
       </c>
       <c r="E5">
-        <v>2.139732613913315</v>
+        <v>2.117106146119645</v>
       </c>
       <c r="F5">
-        <v>32.62797613275391</v>
+        <v>32.43661651938409</v>
       </c>
       <c r="G5">
-        <v>2.036789634038068</v>
+        <v>1.836002902059692</v>
       </c>
       <c r="H5">
-        <v>9.765749976741814</v>
+        <v>9.659863826896551</v>
       </c>
       <c r="I5">
-        <v>0.7181020363474675</v>
+        <v>0.7167527963599297</v>
       </c>
       <c r="J5">
-        <v>9.784274676135773</v>
+        <v>9.768130723568456</v>
       </c>
       <c r="K5">
-        <v>0.7933058545351842</v>
+        <v>0.6372721982188062</v>
       </c>
       <c r="L5">
-        <v>3.291870320077736</v>
+        <v>3.261317649747267</v>
       </c>
       <c r="M5">
-        <v>0.2640714144696224</v>
+        <v>0.266035036231522</v>
       </c>
       <c r="N5">
-        <v>6.495149676341238</v>
+        <v>6.47715535425588</v>
       </c>
       <c r="O5">
-        <v>0.5291524972779191</v>
+        <v>0.3934374528609071</v>
       </c>
       <c r="P5">
-        <v>3.29093148345734</v>
+        <v>3.270148964915929</v>
       </c>
       <c r="Q5">
-        <v>0.2640790623363066</v>
+        <v>0.2989070823864001</v>
       </c>
       <c r="R5">
-        <v>9.765749976741814</v>
+        <v>9.659863826896551</v>
       </c>
       <c r="S5">
-        <v>0.7181020363474675</v>
+        <v>0.7167527963599297</v>
       </c>
       <c r="T5">
-        <v>6.841876219405629</v>
+        <v>6.849517615297292</v>
       </c>
       <c r="U5">
-        <v>0.6352916273723332</v>
+        <v>0.5278478836707232</v>
       </c>
       <c r="V5">
-        <v>1.48232392009869</v>
+        <v>1.452474739474561</v>
       </c>
       <c r="W5">
-        <v>0.189748867716381</v>
+        <v>0.1455870724882923</v>
       </c>
       <c r="X5">
-        <v>1.460074536631456</v>
+        <v>1.466138368796604</v>
       </c>
       <c r="Y5">
-        <v>0.1778105724863899</v>
+        <v>0.1321272348826124</v>
       </c>
       <c r="Z5">
-        <v>3.291870320077736</v>
+        <v>3.261317649747267</v>
       </c>
       <c r="AA5">
-        <v>0.2640714144696224</v>
+        <v>0.266035036231522</v>
       </c>
       <c r="AB5">
-        <v>6.495149676341238</v>
+        <v>6.47715535425588</v>
       </c>
       <c r="AC5">
-        <v>0.5291524972779191</v>
+        <v>0.3934374528609071</v>
       </c>
       <c r="AD5">
-        <v>14.16159562427607</v>
+        <v>13.92010459445073</v>
       </c>
       <c r="AE5">
-        <v>0.7471464226910715</v>
+        <v>0.8105229448820823</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -4550,94 +4550,94 @@
         <v>2024</v>
       </c>
       <c r="B6">
-        <v>69.7843419035318</v>
+        <v>70.22223061637173</v>
       </c>
       <c r="C6">
-        <v>3.319291661905137</v>
+        <v>3.799543900878309</v>
       </c>
       <c r="D6">
-        <v>34.71381765369868</v>
+        <v>35.16400611814424</v>
       </c>
       <c r="E6">
-        <v>1.965837361517666</v>
+        <v>2.508619216375895</v>
       </c>
       <c r="F6">
-        <v>35.0705242498331</v>
+        <v>35.05822449822749</v>
       </c>
       <c r="G6">
-        <v>2.017147140460041</v>
+        <v>2.134504764707378</v>
       </c>
       <c r="H6">
-        <v>10.56279633376504</v>
+        <v>10.50960898198848</v>
       </c>
       <c r="I6">
-        <v>0.8213521753828292</v>
+        <v>0.8629018622395902</v>
       </c>
       <c r="J6">
-        <v>10.49264953171036</v>
+        <v>10.49714691871095</v>
       </c>
       <c r="K6">
-        <v>0.67408934075884</v>
+        <v>0.6281528099203586</v>
       </c>
       <c r="L6">
-        <v>3.523018611752656</v>
+        <v>3.521308134344119</v>
       </c>
       <c r="M6">
-        <v>0.3268062098722219</v>
+        <v>0.3085747156153228</v>
       </c>
       <c r="N6">
-        <v>7.005875583506475</v>
+        <v>7.016789717346946</v>
       </c>
       <c r="O6">
-        <v>0.4785690770845249</v>
+        <v>0.50933708092061</v>
       </c>
       <c r="P6">
-        <v>3.486184189098558</v>
+        <v>3.513370745836997</v>
       </c>
       <c r="Q6">
-        <v>0.2997092704883336</v>
+        <v>0.3112305609813006</v>
       </c>
       <c r="R6">
-        <v>10.56279633376504</v>
+        <v>10.50960898198848</v>
       </c>
       <c r="S6">
-        <v>0.8213521753828292</v>
+        <v>0.8629018622395902</v>
       </c>
       <c r="T6">
-        <v>7.388233409806048</v>
+        <v>7.37073631488117</v>
       </c>
       <c r="U6">
-        <v>0.5127307636534105</v>
+        <v>0.521067874041966</v>
       </c>
       <c r="V6">
-        <v>1.56166611684522</v>
+        <v>1.560167495665252</v>
       </c>
       <c r="W6">
-        <v>0.1880483290740939</v>
+        <v>0.1537878421940386</v>
       </c>
       <c r="X6">
-        <v>1.542750005059093</v>
+        <v>1.566243108164528</v>
       </c>
       <c r="Y6">
-        <v>0.164569242508421</v>
+        <v>0.1712629689624998</v>
       </c>
       <c r="Z6">
-        <v>3.523018611752656</v>
+        <v>3.521308134344119</v>
       </c>
       <c r="AA6">
-        <v>0.3268062098722219</v>
+        <v>0.3085747156153228</v>
       </c>
       <c r="AB6">
-        <v>7.005875583506475</v>
+        <v>7.016789717346946</v>
       </c>
       <c r="AC6">
-        <v>0.4785690770845249</v>
+        <v>0.50933708092061</v>
       </c>
       <c r="AD6">
-        <v>15.71994171008613</v>
+        <v>15.54900028584319</v>
       </c>
       <c r="AE6">
-        <v>0.7530791221794212</v>
+        <v>0.6958198363738696</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -4645,94 +4645,94 @@
         <v>2025</v>
       </c>
       <c r="B7">
-        <v>75.19280694903691</v>
+        <v>76.1619614880874</v>
       </c>
       <c r="C7">
-        <v>3.711434635283078</v>
+        <v>3.326452386358314</v>
       </c>
       <c r="D7">
-        <v>37.31580199425409</v>
+        <v>38.18852699382029</v>
       </c>
       <c r="E7">
-        <v>1.957225648652124</v>
+        <v>2.057279295579067</v>
       </c>
       <c r="F7">
-        <v>37.87700495478281</v>
+        <v>37.9734344942671</v>
       </c>
       <c r="G7">
-        <v>2.384741284211917</v>
+        <v>1.901416060030986</v>
       </c>
       <c r="H7">
-        <v>11.29436610465755</v>
+        <v>11.34889819480181</v>
       </c>
       <c r="I7">
-        <v>0.8014525509893937</v>
+        <v>0.6839170658316788</v>
       </c>
       <c r="J7">
-        <v>11.327488326179</v>
+        <v>11.38561160510879</v>
       </c>
       <c r="K7">
-        <v>0.9397681828129872</v>
+        <v>0.7480448053630848</v>
       </c>
       <c r="L7">
-        <v>3.849223477670934</v>
+        <v>3.824776681926193</v>
       </c>
       <c r="M7">
-        <v>0.3191244484033933</v>
+        <v>0.294802036711854</v>
       </c>
       <c r="N7">
-        <v>7.598818641870898</v>
+        <v>7.557797818808463</v>
       </c>
       <c r="O7">
-        <v>0.60494901554659</v>
+        <v>0.5335924919835664</v>
       </c>
       <c r="P7">
-        <v>3.80710840440442</v>
+        <v>3.856350193621868</v>
       </c>
       <c r="Q7">
-        <v>0.3195085141119338</v>
+        <v>0.341385204407016</v>
       </c>
       <c r="R7">
-        <v>11.29436610465755</v>
+        <v>11.34889819480181</v>
       </c>
       <c r="S7">
-        <v>0.8014525509893937</v>
+        <v>0.6839170658316788</v>
       </c>
       <c r="T7">
-        <v>7.935536733771644</v>
+        <v>7.986163204886675</v>
       </c>
       <c r="U7">
-        <v>0.7124403689286876</v>
+        <v>0.5244050962440174</v>
       </c>
       <c r="V7">
-        <v>1.683051149880833</v>
+        <v>1.699401933979777</v>
       </c>
       <c r="W7">
-        <v>0.2036870007926397</v>
+        <v>0.1959502676748929</v>
       </c>
       <c r="X7">
-        <v>1.708900442526517</v>
+        <v>1.700046466242333</v>
       </c>
       <c r="Y7">
-        <v>0.2027450272972777</v>
+        <v>0.1932168817230498</v>
       </c>
       <c r="Z7">
-        <v>3.849223477670934</v>
+        <v>3.824776681926193</v>
       </c>
       <c r="AA7">
-        <v>0.3191244484033933</v>
+        <v>0.294802036711854</v>
       </c>
       <c r="AB7">
-        <v>7.598818641870898</v>
+        <v>7.557797818808463</v>
       </c>
       <c r="AC7">
-        <v>0.60494901554659</v>
+        <v>0.5335924919835664</v>
       </c>
       <c r="AD7">
-        <v>17.1618417115429</v>
+        <v>17.03407692948743</v>
       </c>
       <c r="AE7">
-        <v>0.8072314226524555</v>
+        <v>0.8602674710753158</v>
       </c>
     </row>
     <row r="8" spans="1:31">
@@ -4740,94 +4740,94 @@
         <v>2026</v>
       </c>
       <c r="B8">
-        <v>80.44405637604996</v>
+        <v>80.07042977155169</v>
       </c>
       <c r="C8">
-        <v>2.991297567380144</v>
+        <v>3.747325721521246</v>
       </c>
       <c r="D8">
-        <v>40.23260431677053</v>
+        <v>39.93354781927816</v>
       </c>
       <c r="E8">
-        <v>1.876096985927994</v>
+        <v>2.336288837900946</v>
       </c>
       <c r="F8">
-        <v>40.21145205927942</v>
+        <v>40.13688195227352</v>
       </c>
       <c r="G8">
-        <v>1.874471242456806</v>
+        <v>2.330546742316618</v>
       </c>
       <c r="H8">
-        <v>12.10700527706276</v>
+        <v>12.04475827419671</v>
       </c>
       <c r="I8">
-        <v>0.6643986088680779</v>
+        <v>0.8751815005506595</v>
       </c>
       <c r="J8">
-        <v>12.0328343217299</v>
+        <v>12.1410259086794</v>
       </c>
       <c r="K8">
-        <v>0.7351159531562182</v>
+        <v>0.8654491649177317</v>
       </c>
       <c r="L8">
-        <v>3.992154648253638</v>
+        <v>3.917327279925857</v>
       </c>
       <c r="M8">
-        <v>0.3412196143447861</v>
+        <v>0.2783852035883699</v>
       </c>
       <c r="N8">
-        <v>8.045586896870217</v>
+        <v>8.025237632086203</v>
       </c>
       <c r="O8">
-        <v>0.4866898084827793</v>
+        <v>0.6373719428663206</v>
       </c>
       <c r="P8">
-        <v>4.033870915362913</v>
+        <v>4.008532857385351</v>
       </c>
       <c r="Q8">
-        <v>0.3606525040353185</v>
+        <v>0.308942617972202</v>
       </c>
       <c r="R8">
-        <v>12.10700527706276</v>
+        <v>12.04475827419671</v>
       </c>
       <c r="S8">
-        <v>0.6643986088680779</v>
+        <v>0.8751815005506595</v>
       </c>
       <c r="T8">
-        <v>8.43180395603548</v>
+        <v>8.466988725706047</v>
       </c>
       <c r="U8">
-        <v>0.5876578682758692</v>
+        <v>0.6744095847421422</v>
       </c>
       <c r="V8">
-        <v>1.790871473604051</v>
+        <v>1.824728761839668</v>
       </c>
       <c r="W8">
-        <v>0.1941526091218132</v>
+        <v>0.1966614146984621</v>
       </c>
       <c r="X8">
-        <v>1.810158892090379</v>
+        <v>1.849308421133686</v>
       </c>
       <c r="Y8">
-        <v>0.2106979429676362</v>
+        <v>0.1766462304681818</v>
       </c>
       <c r="Z8">
-        <v>3.992154648253638</v>
+        <v>3.917327279925857</v>
       </c>
       <c r="AA8">
-        <v>0.3412196143447861</v>
+        <v>0.2783852035883699</v>
       </c>
       <c r="AB8">
-        <v>8.045586896870217</v>
+        <v>8.025237632086203</v>
       </c>
       <c r="AC8">
-        <v>0.4866898084827793</v>
+        <v>0.6373719428663206</v>
       </c>
       <c r="AD8">
-        <v>18.49086229811295</v>
+        <v>18.49376550815364</v>
       </c>
       <c r="AE8">
-        <v>0.8866091548176133</v>
+        <v>0.7392438033404323</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -4835,94 +4835,94 @@
         <v>2027</v>
       </c>
       <c r="B9">
-        <v>84.08044314914201</v>
+        <v>84.52714394902355</v>
       </c>
       <c r="C9">
-        <v>4.995800980245157</v>
+        <v>3.76344834935833</v>
       </c>
       <c r="D9">
-        <v>41.81336105700422</v>
+        <v>42.23744549290257</v>
       </c>
       <c r="E9">
-        <v>3.038705819809163</v>
+        <v>2.121935275849374</v>
       </c>
       <c r="F9">
-        <v>42.26708209213778</v>
+        <v>42.28969845612102</v>
       </c>
       <c r="G9">
-        <v>2.963451863139413</v>
+        <v>2.373571036439651</v>
       </c>
       <c r="H9">
-        <v>12.64645417937491</v>
+        <v>12.64831049181471</v>
       </c>
       <c r="I9">
-        <v>0.9958141115626056</v>
+        <v>0.9200883684962664</v>
       </c>
       <c r="J9">
-        <v>12.57402600073655</v>
+        <v>12.89856572486099</v>
       </c>
       <c r="K9">
-        <v>1.034138234428508</v>
+        <v>0.8334499426325832</v>
       </c>
       <c r="L9">
-        <v>4.225709861103726</v>
+        <v>4.189957719288737</v>
       </c>
       <c r="M9">
-        <v>0.3327169350989573</v>
+        <v>0.3642925354396193</v>
       </c>
       <c r="N9">
-        <v>8.539113304657628</v>
+        <v>8.350961841446074</v>
       </c>
       <c r="O9">
-        <v>0.6228606647511271</v>
+        <v>0.6210356278618581</v>
       </c>
       <c r="P9">
-        <v>4.281778746264959</v>
+        <v>4.201902678710495</v>
       </c>
       <c r="Q9">
-        <v>0.3936909152132196</v>
+        <v>0.3705299609679102</v>
       </c>
       <c r="R9">
-        <v>12.64645417937491</v>
+        <v>12.64831049181471</v>
       </c>
       <c r="S9">
-        <v>0.9958141115626056</v>
+        <v>0.9200883684962664</v>
       </c>
       <c r="T9">
-        <v>8.76385856292868</v>
+        <v>8.988417149989237</v>
       </c>
       <c r="U9">
-        <v>0.8579518387990895</v>
+        <v>0.6362561075671742</v>
       </c>
       <c r="V9">
-        <v>1.889531911431077</v>
+        <v>1.968476450284495</v>
       </c>
       <c r="W9">
-        <v>0.1959454108355855</v>
+        <v>0.19401227011084</v>
       </c>
       <c r="X9">
-        <v>1.920635526376794</v>
+        <v>1.941672124587264</v>
       </c>
       <c r="Y9">
-        <v>0.1965298688510005</v>
+        <v>0.2274952249894093</v>
       </c>
       <c r="Z9">
-        <v>4.225709861103726</v>
+        <v>4.189957719288737</v>
       </c>
       <c r="AA9">
-        <v>0.3327169350989573</v>
+        <v>0.3642925354396193</v>
       </c>
       <c r="AB9">
-        <v>8.539113304657628</v>
+        <v>8.350961841446074</v>
       </c>
       <c r="AC9">
-        <v>0.6228606647511271</v>
+        <v>0.6210356278618581</v>
       </c>
       <c r="AD9">
-        <v>19.83105514796485</v>
+        <v>19.78024101673869</v>
       </c>
       <c r="AE9">
-        <v>0.7962594059248428</v>
+        <v>0.9821075683319498</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -4930,94 +4930,94 @@
         <v>2028</v>
       </c>
       <c r="B10">
-        <v>88.94261540332258</v>
+        <v>90.23045228268819</v>
       </c>
       <c r="C10">
-        <v>4.438567848147736</v>
+        <v>4.485520429864262</v>
       </c>
       <c r="D10">
-        <v>44.76620243003374</v>
+        <v>44.92700299847004</v>
       </c>
       <c r="E10">
-        <v>2.878841971130918</v>
+        <v>2.688700176913707</v>
       </c>
       <c r="F10">
-        <v>44.17641297328883</v>
+        <v>45.30344928421816</v>
       </c>
       <c r="G10">
-        <v>2.897398986591192</v>
+        <v>2.784287454913319</v>
       </c>
       <c r="H10">
-        <v>13.12731617582293</v>
+        <v>13.63295290508933</v>
       </c>
       <c r="I10">
-        <v>1.050334177005866</v>
+        <v>1.01253120690945</v>
       </c>
       <c r="J10">
-        <v>13.3008443579482</v>
+        <v>13.59314046785313</v>
       </c>
       <c r="K10">
-        <v>1.032902901829404</v>
+        <v>1.052036106457539</v>
       </c>
       <c r="L10">
-        <v>4.423890833141999</v>
+        <v>4.496284112588188</v>
       </c>
       <c r="M10">
-        <v>0.360736654373199</v>
+        <v>0.3756466144609517</v>
       </c>
       <c r="N10">
-        <v>8.876020467892635</v>
+        <v>9.033633500022813</v>
       </c>
       <c r="O10">
-        <v>0.7197577516224009</v>
+        <v>0.6890781402312799</v>
       </c>
       <c r="P10">
-        <v>4.44834113848306</v>
+        <v>4.547438298664695</v>
       </c>
       <c r="Q10">
-        <v>0.4450693669384551</v>
+        <v>0.3468465818112295</v>
       </c>
       <c r="R10">
-        <v>13.12731617582293</v>
+        <v>13.63295290508933</v>
       </c>
       <c r="S10">
-        <v>1.050334177005866</v>
+        <v>1.01253120690945</v>
       </c>
       <c r="T10">
-        <v>9.204789523131462</v>
+        <v>9.557451610352333</v>
       </c>
       <c r="U10">
-        <v>0.7689413746101726</v>
+        <v>0.8043303814493752</v>
       </c>
       <c r="V10">
-        <v>2.052037906454212</v>
+        <v>2.016919600947907</v>
       </c>
       <c r="W10">
-        <v>0.2342036900214832</v>
+        <v>0.2303055881628594</v>
       </c>
       <c r="X10">
-        <v>2.044016928362528</v>
+        <v>2.018769256552894</v>
       </c>
       <c r="Y10">
-        <v>0.2450258132819976</v>
+        <v>0.2023385714083736</v>
       </c>
       <c r="Z10">
-        <v>4.423890833141999</v>
+        <v>4.496284112588188</v>
       </c>
       <c r="AA10">
-        <v>0.360736654373199</v>
+        <v>0.3756466144609517</v>
       </c>
       <c r="AB10">
-        <v>8.876020467892635</v>
+        <v>9.033633500022813</v>
       </c>
       <c r="AC10">
-        <v>0.7197577516224009</v>
+        <v>0.6890781402312799</v>
       </c>
       <c r="AD10">
-        <v>20.85317276364365</v>
+        <v>20.94292490947764</v>
       </c>
       <c r="AE10">
-        <v>1.115793186809303</v>
+        <v>0.8497780303697596</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -5025,94 +5025,94 @@
         <v>2029</v>
       </c>
       <c r="B11">
-        <v>94.10464946588495</v>
+        <v>95.01838190940835</v>
       </c>
       <c r="C11">
-        <v>4.448688813417729</v>
+        <v>5.208394711938013</v>
       </c>
       <c r="D11">
-        <v>46.77118206313334</v>
+        <v>47.18696589869393</v>
       </c>
       <c r="E11">
-        <v>2.566967504397573</v>
+        <v>3.226150977677583</v>
       </c>
       <c r="F11">
-        <v>47.33346740275165</v>
+        <v>47.83141601071441</v>
       </c>
       <c r="G11">
-        <v>2.860853573112124</v>
+        <v>3.082449061314084</v>
       </c>
       <c r="H11">
-        <v>14.29136969146751</v>
+        <v>14.32110139271151</v>
       </c>
       <c r="I11">
-        <v>1.044067650417732</v>
+        <v>1.091146217177604</v>
       </c>
       <c r="J11">
-        <v>14.17574908225194</v>
+        <v>14.23894240734701</v>
       </c>
       <c r="K11">
-        <v>1.053437654339393</v>
+        <v>1.062801087705537</v>
       </c>
       <c r="L11">
-        <v>4.735852288916917</v>
+        <v>4.885219859425988</v>
       </c>
       <c r="M11">
-        <v>0.443223461518908</v>
+        <v>0.4567578190125983</v>
       </c>
       <c r="N11">
-        <v>9.398103451507298</v>
+        <v>9.552830200393817</v>
       </c>
       <c r="O11">
-        <v>0.7822208270217252</v>
+        <v>0.7691787493552715</v>
       </c>
       <c r="P11">
-        <v>4.732392888607971</v>
+        <v>4.833322150836089</v>
       </c>
       <c r="Q11">
-        <v>0.3277141247366481</v>
+        <v>0.4891600201634535</v>
       </c>
       <c r="R11">
-        <v>14.29136969146751</v>
+        <v>14.32110139271151</v>
       </c>
       <c r="S11">
-        <v>1.044067650417732</v>
+        <v>1.091146217177604</v>
       </c>
       <c r="T11">
-        <v>9.957488291486504</v>
+        <v>9.924052845216686</v>
       </c>
       <c r="U11">
-        <v>0.8432492497323716</v>
+        <v>0.7225426685285243</v>
       </c>
       <c r="V11">
-        <v>2.096142068874329</v>
+        <v>2.149164308645058</v>
       </c>
       <c r="W11">
-        <v>0.2152058526611432</v>
+        <v>0.2603933473688148</v>
       </c>
       <c r="X11">
-        <v>2.122118721891106</v>
+        <v>2.165725253485271</v>
       </c>
       <c r="Y11">
-        <v>0.2372465141665232</v>
+        <v>0.2373158726812129</v>
       </c>
       <c r="Z11">
-        <v>4.735852288916917</v>
+        <v>4.885219859425988</v>
       </c>
       <c r="AA11">
-        <v>0.443223461518908</v>
+        <v>0.4567578190125983</v>
       </c>
       <c r="AB11">
-        <v>9.398103451507298</v>
+        <v>9.552830200393817</v>
       </c>
       <c r="AC11">
-        <v>0.7822208270217252</v>
+        <v>0.7691787493552715</v>
       </c>
       <c r="AD11">
-        <v>21.80297806371473</v>
+        <v>22.38405371969056</v>
       </c>
       <c r="AE11">
-        <v>1.177844564609393</v>
+        <v>1.028057269222813</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -5120,94 +5120,94 @@
         <v>2030</v>
       </c>
       <c r="B12">
-        <v>100.6821487974258</v>
+        <v>99.42235283871709</v>
       </c>
       <c r="C12">
-        <v>4.190578274687474</v>
+        <v>5.08324786003172</v>
       </c>
       <c r="D12">
-        <v>50.21828680991764</v>
+        <v>49.4927125039103</v>
       </c>
       <c r="E12">
-        <v>2.869098935780423</v>
+        <v>3.154942025807223</v>
       </c>
       <c r="F12">
-        <v>50.46386198750816</v>
+        <v>49.92964033480677</v>
       </c>
       <c r="G12">
-        <v>2.998975438280455</v>
+        <v>2.961295963602595</v>
       </c>
       <c r="H12">
-        <v>15.19628710603252</v>
+        <v>15.00639394352056</v>
       </c>
       <c r="I12">
-        <v>1.066319428869327</v>
+        <v>1.154018429648017</v>
       </c>
       <c r="J12">
-        <v>15.04873315604318</v>
+        <v>14.85424203783409</v>
       </c>
       <c r="K12">
-        <v>1.098908105509623</v>
+        <v>0.9540327555423793</v>
       </c>
       <c r="L12">
-        <v>5.087615862135056</v>
+        <v>5.044998987881861</v>
       </c>
       <c r="M12">
-        <v>0.4591527653109682</v>
+        <v>0.4710481037418239</v>
       </c>
       <c r="N12">
-        <v>10.13353562680425</v>
+        <v>9.999709909429322</v>
       </c>
       <c r="O12">
-        <v>0.8382827791435168</v>
+        <v>0.7020366838355512</v>
       </c>
       <c r="P12">
-        <v>4.997690236493138</v>
+        <v>5.024295456140931</v>
       </c>
       <c r="Q12">
-        <v>0.4805181785626039</v>
+        <v>0.4228737567025853</v>
       </c>
       <c r="R12">
-        <v>15.19628710603252</v>
+        <v>15.00639394352056</v>
       </c>
       <c r="S12">
-        <v>1.066319428869327</v>
+        <v>1.154018429648017</v>
       </c>
       <c r="T12">
-        <v>10.53689623582767</v>
+        <v>10.45691026148424</v>
       </c>
       <c r="U12">
-        <v>0.8844216020508346</v>
+        <v>0.787209932848938</v>
       </c>
       <c r="V12">
-        <v>2.263830525199548</v>
+        <v>2.196450260462893</v>
       </c>
       <c r="W12">
-        <v>0.2242600336702701</v>
+        <v>0.2502311133378295</v>
       </c>
       <c r="X12">
-        <v>2.248006395015966</v>
+        <v>2.200881515886955</v>
       </c>
       <c r="Y12">
-        <v>0.2066968632274332</v>
+        <v>0.2175809994576081</v>
       </c>
       <c r="Z12">
-        <v>5.087615862135056</v>
+        <v>5.044998987881861</v>
       </c>
       <c r="AA12">
-        <v>0.4591527653109682</v>
+        <v>0.4710481037418239</v>
       </c>
       <c r="AB12">
-        <v>10.13353562680425</v>
+        <v>9.999709909429322</v>
       </c>
       <c r="AC12">
-        <v>0.8382827791435168</v>
+        <v>0.7020366838355512</v>
       </c>
       <c r="AD12">
-        <v>23.40444621885204</v>
+        <v>23.54953965161856</v>
       </c>
       <c r="AE12">
-        <v>1.21515423962389</v>
+        <v>0.9122841611698583</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -5215,94 +5215,94 @@
         <v>2031</v>
       </c>
       <c r="B13">
-        <v>4.997411262237688</v>
+        <v>5.011216553464253</v>
       </c>
       <c r="C13">
-        <v>0.2399524727633623</v>
+        <v>0.2292841370770076</v>
       </c>
       <c r="D13">
-        <v>2.496280389584476</v>
+        <v>2.509172638871949</v>
       </c>
       <c r="E13">
-        <v>0.1462934176143341</v>
+        <v>0.1381153215691751</v>
       </c>
       <c r="F13">
-        <v>2.501130872653213</v>
+        <v>2.502043914592303</v>
       </c>
       <c r="G13">
-        <v>0.1429104626683209</v>
+        <v>0.158576794664126</v>
       </c>
       <c r="H13">
-        <v>0.7577669622849355</v>
+        <v>0.7596366597052966</v>
       </c>
       <c r="I13">
-        <v>0.05524658723938817</v>
+        <v>0.05550176946161853</v>
       </c>
       <c r="J13">
-        <v>0.7411291892128092</v>
+        <v>0.7415795730217256</v>
       </c>
       <c r="K13">
-        <v>0.04818107564266008</v>
+        <v>0.05442132136665763</v>
       </c>
       <c r="L13">
-        <v>0.252670431580985</v>
+        <v>0.2518854168942823</v>
       </c>
       <c r="M13">
-        <v>0.01982399446950794</v>
+        <v>0.02303882422572827</v>
       </c>
       <c r="N13">
-        <v>0.5010271904497023</v>
+        <v>0.4957067588384166</v>
       </c>
       <c r="O13">
-        <v>0.03828085877976316</v>
+        <v>0.0384418760006444</v>
       </c>
       <c r="P13">
-        <v>0.2485370991247804</v>
+        <v>0.2532355061325826</v>
       </c>
       <c r="Q13">
-        <v>0.01811326843005469</v>
+        <v>0.02502909919430259</v>
       </c>
       <c r="R13">
-        <v>0.7577669622849355</v>
+        <v>0.7596366597052966</v>
       </c>
       <c r="S13">
-        <v>0.05524658723938817</v>
+        <v>0.05550176946161853</v>
       </c>
       <c r="T13">
-        <v>0.5188015617979268</v>
+        <v>0.5177255640845507</v>
       </c>
       <c r="U13">
-        <v>0.03529021366383167</v>
+        <v>0.04091577914927617</v>
       </c>
       <c r="V13">
-        <v>0.1108410632262543</v>
+        <v>0.1114267663795013</v>
       </c>
       <c r="W13">
-        <v>0.01371844388858372</v>
+        <v>0.0107148479271449</v>
       </c>
       <c r="X13">
-        <v>0.111486564188628</v>
+        <v>0.1124272425576737</v>
       </c>
       <c r="Y13">
-        <v>0.01464753725628035</v>
+        <v>0.0141665915831577</v>
       </c>
       <c r="Z13">
-        <v>0.252670431580985</v>
+        <v>0.2518854168942823</v>
       </c>
       <c r="AA13">
-        <v>0.01982399446950794</v>
+        <v>0.02303882422572827</v>
       </c>
       <c r="AB13">
-        <v>0.5010271904497023</v>
+        <v>0.4957067588384166</v>
       </c>
       <c r="AC13">
-        <v>0.03828085877976316</v>
+        <v>0.0384418760006444</v>
       </c>
       <c r="AD13">
-        <v>24.91056139256165</v>
+        <v>24.77010441214048</v>
       </c>
       <c r="AE13">
-        <v>1.059228629637211</v>
+        <v>1.134343656537446</v>
       </c>
     </row>
     <row r="14" spans="1:31">
@@ -5310,94 +5310,94 @@
         <v>2032</v>
       </c>
       <c r="B14">
-        <v>109.3131992764112</v>
+        <v>108.8945978523869</v>
       </c>
       <c r="C14">
-        <v>6.042845893634488</v>
+        <v>5.486443721008545</v>
       </c>
       <c r="D14">
-        <v>54.99122579397785</v>
+        <v>54.61388932534805</v>
       </c>
       <c r="E14">
-        <v>3.945122079568969</v>
+        <v>3.55681132794463</v>
       </c>
       <c r="F14">
-        <v>54.32197348243335</v>
+        <v>54.28070852703883</v>
       </c>
       <c r="G14">
-        <v>3.186051807473589</v>
+        <v>3.023335094827607</v>
       </c>
       <c r="H14">
-        <v>16.46374876509838</v>
+        <v>16.19748663512407</v>
       </c>
       <c r="I14">
-        <v>1.225799997679217</v>
+        <v>1.066421802495912</v>
       </c>
       <c r="J14">
-        <v>16.28810636185069</v>
+        <v>16.31275156394348</v>
       </c>
       <c r="K14">
-        <v>1.150811421938635</v>
+        <v>1.033137036081139</v>
       </c>
       <c r="L14">
-        <v>5.366760417220839</v>
+        <v>5.471908413386766</v>
       </c>
       <c r="M14">
-        <v>0.4317271252204554</v>
+        <v>0.5002676378574867</v>
       </c>
       <c r="N14">
-        <v>10.70659147316318</v>
+        <v>10.86919406525164</v>
       </c>
       <c r="O14">
-        <v>0.8100443142710142</v>
+        <v>0.7631495141572844</v>
       </c>
       <c r="P14">
-        <v>5.496766465100251</v>
+        <v>5.429367849332878</v>
       </c>
       <c r="Q14">
-        <v>0.5172854510242976</v>
+        <v>0.4965650860185318</v>
       </c>
       <c r="R14">
-        <v>16.46374876509838</v>
+        <v>16.19748663512407</v>
       </c>
       <c r="S14">
-        <v>1.225799997679217</v>
+        <v>1.066421802495912</v>
       </c>
       <c r="T14">
-        <v>11.4133777553878</v>
+        <v>11.38832483379432</v>
       </c>
       <c r="U14">
-        <v>0.8216265149845284</v>
+        <v>0.869066432132623</v>
       </c>
       <c r="V14">
-        <v>2.444268783020623</v>
+        <v>2.488967277320244</v>
       </c>
       <c r="W14">
-        <v>0.295669933472182</v>
+        <v>0.2253689059864823</v>
       </c>
       <c r="X14">
-        <v>2.43045982344227</v>
+        <v>2.435459452828916</v>
       </c>
       <c r="Y14">
-        <v>0.3016574586973632</v>
+        <v>0.2378165329115204</v>
       </c>
       <c r="Z14">
-        <v>5.366760417220839</v>
+        <v>5.471908413386766</v>
       </c>
       <c r="AA14">
-        <v>0.4317271252204554</v>
+        <v>0.5002676378574867</v>
       </c>
       <c r="AB14">
-        <v>10.70659147316318</v>
+        <v>10.86919406525164</v>
       </c>
       <c r="AC14">
-        <v>0.8100443142710142</v>
+        <v>0.7631495141572844</v>
       </c>
       <c r="AD14">
-        <v>9.381436585081444</v>
+        <v>9.636244132684487</v>
       </c>
       <c r="AE14">
-        <v>0.8964178838194994</v>
+        <v>0.8403565304243213</v>
       </c>
     </row>
     <row r="15" spans="1:31">
@@ -5405,94 +5405,94 @@
         <v>2033</v>
       </c>
       <c r="B15">
-        <v>113.9570506107022</v>
+        <v>115.2276053223648</v>
       </c>
       <c r="C15">
-        <v>5.911909751628091</v>
+        <v>5.950913196551721</v>
       </c>
       <c r="D15">
-        <v>56.97923876744524</v>
+        <v>57.70835169746343</v>
       </c>
       <c r="E15">
-        <v>3.981928383560119</v>
+        <v>3.03327306737529</v>
       </c>
       <c r="F15">
-        <v>56.9778118432569</v>
+        <v>57.51925362490137</v>
       </c>
       <c r="G15">
-        <v>3.062756306886873</v>
+        <v>3.776472326109317</v>
       </c>
       <c r="H15">
-        <v>17.08898848430093</v>
+        <v>17.07812554744611</v>
       </c>
       <c r="I15">
-        <v>1.101571133887194</v>
+        <v>1.145740404285225</v>
       </c>
       <c r="J15">
-        <v>16.97830511032727</v>
+        <v>17.33402857623943</v>
       </c>
       <c r="K15">
-        <v>1.23880530643497</v>
+        <v>1.358733111345778</v>
       </c>
       <c r="L15">
-        <v>5.687535827863537</v>
+        <v>5.836008386525083</v>
       </c>
       <c r="M15">
-        <v>0.4127689859426495</v>
+        <v>0.5726760377121558</v>
       </c>
       <c r="N15">
-        <v>11.48911086629274</v>
+        <v>11.45412924122571</v>
       </c>
       <c r="O15">
-        <v>0.8769476059818503</v>
+        <v>1.042727985648523</v>
       </c>
       <c r="P15">
-        <v>5.733871554472446</v>
+        <v>5.816961873465037</v>
       </c>
       <c r="Q15">
-        <v>0.4459217615775258</v>
+        <v>0.5103953710973063</v>
       </c>
       <c r="R15">
-        <v>17.08898848430093</v>
+        <v>17.07812554744611</v>
       </c>
       <c r="S15">
-        <v>1.101571133887194</v>
+        <v>1.145740404285225</v>
       </c>
       <c r="T15">
-        <v>11.87344460718868</v>
+        <v>12.13138484586523</v>
       </c>
       <c r="U15">
-        <v>0.9887767527550471</v>
+        <v>1.025109145798196</v>
       </c>
       <c r="V15">
-        <v>2.576108462636643</v>
+        <v>2.607947817412902</v>
       </c>
       <c r="W15">
-        <v>0.2892276258700878</v>
+        <v>0.3079220637891067</v>
       </c>
       <c r="X15">
-        <v>2.528752040501939</v>
+        <v>2.594695912961299</v>
       </c>
       <c r="Y15">
-        <v>0.2661718029762631</v>
+        <v>0.2938952839513732</v>
       </c>
       <c r="Z15">
-        <v>5.687535827863537</v>
+        <v>5.836008386525083</v>
       </c>
       <c r="AA15">
-        <v>0.4127689859426495</v>
+        <v>0.5726760377121558</v>
       </c>
       <c r="AB15">
-        <v>11.48911086629274</v>
+        <v>11.45412924122571</v>
       </c>
       <c r="AC15">
-        <v>0.8769476059818503</v>
+        <v>1.042727985648523</v>
       </c>
       <c r="AD15">
-        <v>21.68048299247199</v>
+        <v>21.35404435493049</v>
       </c>
       <c r="AE15">
-        <v>1.17139616875477</v>
+        <v>1.056338940331217</v>
       </c>
     </row>
     <row r="16" spans="1:31">
@@ -5500,94 +5500,94 @@
         <v>2034</v>
       </c>
       <c r="B16">
-        <v>119.2693908618029</v>
+        <v>119.525315350423</v>
       </c>
       <c r="C16">
-        <v>6.377642944865957</v>
+        <v>6.341866247963319</v>
       </c>
       <c r="D16">
-        <v>59.76009299885563</v>
+        <v>60.59413585314783</v>
       </c>
       <c r="E16">
-        <v>4.198500184313873</v>
+        <v>3.64567695935763</v>
       </c>
       <c r="F16">
-        <v>59.50929786294725</v>
+        <v>58.93117949727523</v>
       </c>
       <c r="G16">
-        <v>3.675498657859237</v>
+        <v>3.683269102803629</v>
       </c>
       <c r="H16">
-        <v>17.86914639176626</v>
+        <v>17.68203759953254</v>
       </c>
       <c r="I16">
-        <v>1.365578945658799</v>
+        <v>1.210491913240147</v>
       </c>
       <c r="J16">
-        <v>17.87267741784789</v>
+        <v>17.69331581335859</v>
       </c>
       <c r="K16">
-        <v>1.186644418221912</v>
+        <v>1.488477296703509</v>
       </c>
       <c r="L16">
-        <v>5.98299770686193</v>
+        <v>5.902300389519151</v>
       </c>
       <c r="M16">
-        <v>0.5506519901739779</v>
+        <v>0.5247597275483888</v>
       </c>
       <c r="N16">
-        <v>11.78451936717748</v>
+        <v>11.82369597497599</v>
       </c>
       <c r="O16">
-        <v>0.916243505094064</v>
+        <v>0.8371129651663353</v>
       </c>
       <c r="P16">
-        <v>5.9999569792937</v>
+        <v>5.829829719888949</v>
       </c>
       <c r="Q16">
-        <v>0.541491290142503</v>
+        <v>0.4487976328858077</v>
       </c>
       <c r="R16">
-        <v>17.86914639176626</v>
+        <v>17.68203759953254</v>
       </c>
       <c r="S16">
-        <v>1.365578945658799</v>
+        <v>1.210491913240147</v>
       </c>
       <c r="T16">
-        <v>12.61257305204732</v>
+        <v>12.37642998580819</v>
       </c>
       <c r="U16">
-        <v>0.9751292915886217</v>
+        <v>1.146211295379303</v>
       </c>
       <c r="V16">
-        <v>2.616683397350985</v>
+        <v>2.667299057990749</v>
       </c>
       <c r="W16">
-        <v>0.2671796429726854</v>
+        <v>0.3197802160407173</v>
       </c>
       <c r="X16">
-        <v>2.64342096844958</v>
+        <v>2.649586769559653</v>
       </c>
       <c r="Y16">
-        <v>0.2666984023954043</v>
+        <v>0.3116585625189456</v>
       </c>
       <c r="Z16">
-        <v>5.98299770686193</v>
+        <v>5.902300389519151</v>
       </c>
       <c r="AA16">
-        <v>0.5506519901739779</v>
+        <v>0.5247597275483888</v>
       </c>
       <c r="AB16">
-        <v>11.78451936717748</v>
+        <v>11.82369597497599</v>
       </c>
       <c r="AC16">
-        <v>0.916243505094064</v>
+        <v>0.8371129651663353</v>
       </c>
       <c r="AD16">
-        <v>26.35205300897196</v>
+        <v>26.28136179859146</v>
       </c>
       <c r="AE16">
-        <v>1.366240998383971</v>
+        <v>1.26625716955997</v>
       </c>
     </row>
     <row r="17" spans="1:31">
@@ -5595,94 +5595,94 @@
         <v>2035</v>
       </c>
       <c r="B17">
-        <v>124.4061099483742</v>
+        <v>124.8467785100477</v>
       </c>
       <c r="C17">
-        <v>5.490760942947163</v>
+        <v>5.387063913470782</v>
       </c>
       <c r="D17">
-        <v>61.87323637002957</v>
+        <v>62.34629623956686</v>
       </c>
       <c r="E17">
-        <v>3.420524267069234</v>
+        <v>3.389225800036392</v>
       </c>
       <c r="F17">
-        <v>62.53287357834457</v>
+        <v>62.50048227048083</v>
       </c>
       <c r="G17">
-        <v>3.484179630033834</v>
+        <v>3.829274790756971</v>
       </c>
       <c r="H17">
-        <v>18.82760407215578</v>
+        <v>18.96787917100703</v>
       </c>
       <c r="I17">
-        <v>1.097481896515077</v>
+        <v>1.365846639359742</v>
       </c>
       <c r="J17">
-        <v>18.63246590437945</v>
+        <v>18.67836163377644</v>
       </c>
       <c r="K17">
-        <v>1.596416905504344</v>
+        <v>1.425483016147012</v>
       </c>
       <c r="L17">
-        <v>6.247858635446898</v>
+        <v>6.208974410742561</v>
       </c>
       <c r="M17">
-        <v>0.5012366081174449</v>
+        <v>0.4980283967701086</v>
       </c>
       <c r="N17">
-        <v>12.52840399944222</v>
+        <v>12.42424857798092</v>
       </c>
       <c r="O17">
-        <v>0.8482827294733407</v>
+        <v>0.9259788029891967</v>
       </c>
       <c r="P17">
-        <v>6.296540966920216</v>
+        <v>6.221018476973866</v>
       </c>
       <c r="Q17">
-        <v>0.4891879611770578</v>
+        <v>0.6118553339773527</v>
       </c>
       <c r="R17">
-        <v>18.82760407215578</v>
+        <v>18.96787917100703</v>
       </c>
       <c r="S17">
-        <v>1.097481896515077</v>
+        <v>1.365846639359742</v>
       </c>
       <c r="T17">
-        <v>13.11206818616776</v>
+        <v>13.06851123812248</v>
       </c>
       <c r="U17">
-        <v>1.243528902335659</v>
+        <v>1.054508935269745</v>
       </c>
       <c r="V17">
-        <v>2.744079237178159</v>
+        <v>2.783641807698909</v>
       </c>
       <c r="W17">
-        <v>0.3135366773322854</v>
+        <v>0.3317547570811415</v>
       </c>
       <c r="X17">
-        <v>2.776318834252079</v>
+        <v>2.82620858795506</v>
       </c>
       <c r="Y17">
-        <v>0.3184588869714053</v>
+        <v>0.3359021360652148</v>
       </c>
       <c r="Z17">
-        <v>6.247858635446898</v>
+        <v>6.208974410742561</v>
       </c>
       <c r="AA17">
-        <v>0.5012366081174449</v>
+        <v>0.4980283967701086</v>
       </c>
       <c r="AB17">
-        <v>12.52840399944222</v>
+        <v>12.42424857798092</v>
       </c>
       <c r="AC17">
-        <v>0.8482827294733407</v>
+        <v>0.9259788029891967</v>
       </c>
       <c r="AD17">
-        <v>29.00433816646633</v>
+        <v>28.66069954198206</v>
       </c>
       <c r="AE17">
-        <v>1.393243059515049</v>
+        <v>1.381818955101963</v>
       </c>
     </row>
     <row r="18" spans="1:31">
@@ -5690,94 +5690,94 @@
         <v>2036</v>
       </c>
       <c r="B18">
-        <v>130.6799983663137</v>
+        <v>129.8456555818816</v>
       </c>
       <c r="C18">
-        <v>7.605555676144028</v>
+        <v>7.421724308938145</v>
       </c>
       <c r="D18">
-        <v>65.00454599520381</v>
+        <v>64.97696354430258</v>
       </c>
       <c r="E18">
-        <v>4.564797160917442</v>
+        <v>4.522666147531498</v>
       </c>
       <c r="F18">
-        <v>65.6754523711099</v>
+        <v>64.868692037579</v>
       </c>
       <c r="G18">
-        <v>4.731292585628295</v>
+        <v>4.055416558434745</v>
       </c>
       <c r="H18">
-        <v>19.78652169208449</v>
+        <v>19.34889361359264</v>
       </c>
       <c r="I18">
-        <v>1.665625694340052</v>
+        <v>1.486803210049731</v>
       </c>
       <c r="J18">
-        <v>19.56512460626335</v>
+        <v>19.42812072948646</v>
       </c>
       <c r="K18">
-        <v>1.532793597843386</v>
+        <v>1.474702064200804</v>
       </c>
       <c r="L18">
-        <v>6.520808136566601</v>
+        <v>6.473640939545785</v>
       </c>
       <c r="M18">
-        <v>0.6893164887426141</v>
+        <v>0.5756625500856003</v>
       </c>
       <c r="N18">
-        <v>13.24072064376811</v>
+        <v>13.09285726948059</v>
       </c>
       <c r="O18">
-        <v>1.115567074681591</v>
+        <v>0.9106740387387529</v>
       </c>
       <c r="P18">
-        <v>6.56227729242735</v>
+        <v>6.525179485473545</v>
       </c>
       <c r="Q18">
-        <v>0.6447826587086298</v>
+        <v>0.6008785195124396</v>
       </c>
       <c r="R18">
-        <v>19.78652169208449</v>
+        <v>19.34889361359264</v>
       </c>
       <c r="S18">
-        <v>1.665625694340052</v>
+        <v>1.486803210049731</v>
       </c>
       <c r="T18">
-        <v>13.69724408783728</v>
+        <v>13.54507262076005</v>
       </c>
       <c r="U18">
-        <v>1.244703331698765</v>
+        <v>1.158780303292815</v>
       </c>
       <c r="V18">
-        <v>2.921550933348107</v>
+        <v>2.95600625396453</v>
       </c>
       <c r="W18">
-        <v>0.2908780122820028</v>
+        <v>0.3556241383114043</v>
       </c>
       <c r="X18">
-        <v>2.94632958507797</v>
+        <v>2.927041854761871</v>
       </c>
       <c r="Y18">
-        <v>0.3235847263759942</v>
+        <v>0.3266798266281889</v>
       </c>
       <c r="Z18">
-        <v>6.520808136566601</v>
+        <v>6.473640939545785</v>
       </c>
       <c r="AA18">
-        <v>0.6893164887426141</v>
+        <v>0.5756625500856003</v>
       </c>
       <c r="AB18">
-        <v>13.24072064376811</v>
+        <v>13.09285726948059</v>
       </c>
       <c r="AC18">
-        <v>1.115567074681591</v>
+        <v>0.9106740387387529</v>
       </c>
       <c r="AD18">
-        <v>30.87800932907932</v>
+        <v>30.80132938749169</v>
       </c>
       <c r="AE18">
-        <v>1.265739246065167</v>
+        <v>1.492468402434688</v>
       </c>
     </row>
     <row r="19" spans="1:31">
@@ -5785,94 +5785,94 @@
         <v>2037</v>
       </c>
       <c r="B19">
-        <v>134.9551819381051</v>
+        <v>133.6315862893624</v>
       </c>
       <c r="C19">
-        <v>6.852534162910002</v>
+        <v>7.309829009149282</v>
       </c>
       <c r="D19">
-        <v>67.22839358072355</v>
+        <v>66.66550133085474</v>
       </c>
       <c r="E19">
-        <v>4.095712450785647</v>
+        <v>4.474557492046713</v>
       </c>
       <c r="F19">
-        <v>67.72678835738148</v>
+        <v>66.96608495850759</v>
       </c>
       <c r="G19">
-        <v>4.382761807872472</v>
+        <v>4.309312388907045</v>
       </c>
       <c r="H19">
-        <v>20.32383477551202</v>
+        <v>20.206483699169</v>
       </c>
       <c r="I19">
-        <v>1.592357237702848</v>
+        <v>1.612010998945121</v>
       </c>
       <c r="J19">
-        <v>20.40042793303243</v>
+        <v>20.18490372557429</v>
       </c>
       <c r="K19">
-        <v>1.683019502166264</v>
+        <v>1.731354454488202</v>
       </c>
       <c r="L19">
-        <v>6.761078453010647</v>
+        <v>6.614976079943837</v>
       </c>
       <c r="M19">
-        <v>0.5604113377951232</v>
+        <v>0.6262386980270339</v>
       </c>
       <c r="N19">
-        <v>13.373117960256</v>
+        <v>13.27670635545043</v>
       </c>
       <c r="O19">
-        <v>1.175464291100162</v>
+        <v>0.9516826965879958</v>
       </c>
       <c r="P19">
-        <v>6.868329235570416</v>
+        <v>6.683015098370034</v>
       </c>
       <c r="Q19">
-        <v>0.5677138054653907</v>
+        <v>0.4852461349431368</v>
       </c>
       <c r="R19">
-        <v>20.32383477551202</v>
+        <v>20.206483699169</v>
       </c>
       <c r="S19">
-        <v>1.592357237702848</v>
+        <v>1.612010998945121</v>
       </c>
       <c r="T19">
-        <v>14.22086988366263</v>
+        <v>14.05299836375852</v>
       </c>
       <c r="U19">
-        <v>1.239119301598846</v>
+        <v>1.241789809440645</v>
       </c>
       <c r="V19">
-        <v>3.102223499070406</v>
+        <v>3.059300321470742</v>
       </c>
       <c r="W19">
-        <v>0.3997820551540992</v>
+        <v>0.3807767003956389</v>
       </c>
       <c r="X19">
-        <v>3.077334550299385</v>
+        <v>3.072605040345029</v>
       </c>
       <c r="Y19">
-        <v>0.3855142998352674</v>
+        <v>0.3625083255067754</v>
       </c>
       <c r="Z19">
-        <v>6.761078453010647</v>
+        <v>6.614976079943837</v>
       </c>
       <c r="AA19">
-        <v>0.5604113377951232</v>
+        <v>0.6262386980270339</v>
       </c>
       <c r="AB19">
-        <v>13.373117960256</v>
+        <v>13.27670635545043</v>
       </c>
       <c r="AC19">
-        <v>1.175464291100162</v>
+        <v>0.9516826965879958</v>
       </c>
       <c r="AD19">
-        <v>32.54598185927996</v>
+        <v>32.1114711158643</v>
       </c>
       <c r="AE19">
-        <v>1.664570175522567</v>
+        <v>1.586697590581737</v>
       </c>
     </row>
     <row r="20" spans="1:31">
@@ -5880,94 +5880,94 @@
         <v>2038</v>
       </c>
       <c r="B20">
-        <v>138.8044405366794</v>
+        <v>139.9198337620148</v>
       </c>
       <c r="C20">
-        <v>7.051569622044727</v>
+        <v>6.792866796915363</v>
       </c>
       <c r="D20">
-        <v>69.3927189291058</v>
+        <v>70.25897728758328</v>
       </c>
       <c r="E20">
-        <v>4.656907830469154</v>
+        <v>4.796714109142961</v>
       </c>
       <c r="F20">
-        <v>69.41172160757353</v>
+        <v>69.66085647443154</v>
       </c>
       <c r="G20">
-        <v>4.008847052361724</v>
+        <v>3.855469135934479</v>
       </c>
       <c r="H20">
-        <v>20.76568849689173</v>
+        <v>20.93807319596776</v>
       </c>
       <c r="I20">
-        <v>1.673502216140248</v>
+        <v>1.420620298552668</v>
       </c>
       <c r="J20">
-        <v>21.03680223747478</v>
+        <v>21.00410544100226</v>
       </c>
       <c r="K20">
-        <v>1.437633680300243</v>
+        <v>1.35653909318722</v>
       </c>
       <c r="L20">
-        <v>6.926219009240835</v>
+        <v>6.853928406813221</v>
       </c>
       <c r="M20">
-        <v>0.528003749956341</v>
+        <v>0.6918275100891028</v>
       </c>
       <c r="N20">
-        <v>13.84238890584263</v>
+        <v>13.95322761352638</v>
       </c>
       <c r="O20">
-        <v>0.8621208827230981</v>
+        <v>0.9709227651063269</v>
       </c>
       <c r="P20">
-        <v>6.840622958123563</v>
+        <v>6.911521817121931</v>
       </c>
       <c r="Q20">
-        <v>0.5671327538588843</v>
+        <v>0.6545884466046961</v>
       </c>
       <c r="R20">
-        <v>20.76568849689173</v>
+        <v>20.93807319596776</v>
       </c>
       <c r="S20">
-        <v>1.673502216140248</v>
+        <v>1.420620298552668</v>
       </c>
       <c r="T20">
-        <v>14.78626267905429</v>
+        <v>14.67886142602912</v>
       </c>
       <c r="U20">
-        <v>1.147088201717779</v>
+        <v>1.040463820746219</v>
       </c>
       <c r="V20">
-        <v>3.128574029671533</v>
+        <v>3.168430878558727</v>
       </c>
       <c r="W20">
-        <v>0.3421054468621769</v>
+        <v>0.3597452266627261</v>
       </c>
       <c r="X20">
-        <v>3.121965528748954</v>
+        <v>3.156813136414413</v>
       </c>
       <c r="Y20">
-        <v>0.3578537583046217</v>
+        <v>0.3388605286829787</v>
       </c>
       <c r="Z20">
-        <v>6.926219009240835</v>
+        <v>6.853928406813221</v>
       </c>
       <c r="AA20">
-        <v>0.528003749956341</v>
+        <v>0.6918275100891028</v>
       </c>
       <c r="AB20">
-        <v>13.84238890584263</v>
+        <v>13.95322761352638</v>
       </c>
       <c r="AC20">
-        <v>0.8621208827230981</v>
+        <v>0.9709227651063269</v>
       </c>
       <c r="AD20">
-        <v>33.8602150594628</v>
+        <v>33.47266392190529</v>
       </c>
       <c r="AE20">
-        <v>1.675637486094809</v>
+        <v>1.767156864419818</v>
       </c>
     </row>
     <row r="21" spans="1:31">
@@ -5975,94 +5975,94 @@
         <v>2039</v>
       </c>
       <c r="B21">
-        <v>144.0825185142694</v>
+        <v>144.1950076340099</v>
       </c>
       <c r="C21">
-        <v>6.423802556460242</v>
+        <v>9.088156132107665</v>
       </c>
       <c r="D21">
-        <v>71.46085666810582</v>
+        <v>72.11686628040013</v>
       </c>
       <c r="E21">
-        <v>4.145693210252559</v>
+        <v>5.375929011230484</v>
       </c>
       <c r="F21">
-        <v>72.62166184616359</v>
+        <v>72.07814135360975</v>
       </c>
       <c r="G21">
-        <v>3.820939440609191</v>
+        <v>5.221392837656436</v>
       </c>
       <c r="H21">
-        <v>21.74801382653628</v>
+        <v>21.48712660000849</v>
       </c>
       <c r="I21">
-        <v>1.426411125948617</v>
+        <v>1.894327262716648</v>
       </c>
       <c r="J21">
-        <v>21.72873148997822</v>
+        <v>21.59075588428399</v>
       </c>
       <c r="K21">
-        <v>1.31019857804856</v>
+        <v>1.707689616405746</v>
       </c>
       <c r="L21">
-        <v>7.24317551325502</v>
+        <v>7.328498253362774</v>
       </c>
       <c r="M21">
-        <v>0.6152873168782448</v>
+        <v>0.7270408256098997</v>
       </c>
       <c r="N21">
-        <v>14.53346897361103</v>
+        <v>14.45880202822606</v>
       </c>
       <c r="O21">
-        <v>1.067610119725944</v>
+        <v>1.366373221736296</v>
       </c>
       <c r="P21">
-        <v>7.368272042783034</v>
+        <v>7.212958587728428</v>
       </c>
       <c r="Q21">
-        <v>0.5812020523862538</v>
+        <v>0.6746588708901174</v>
       </c>
       <c r="R21">
-        <v>21.74801382653628</v>
+        <v>21.48712660000849</v>
       </c>
       <c r="S21">
-        <v>1.426411125948617</v>
+        <v>1.894327262716648</v>
       </c>
       <c r="T21">
-        <v>15.15353326522519</v>
+        <v>15.10726325510366</v>
       </c>
       <c r="U21">
-        <v>1.033133593901622</v>
+        <v>1.39990355711588</v>
       </c>
       <c r="V21">
-        <v>3.280154957869623</v>
+        <v>3.245246497677166</v>
       </c>
       <c r="W21">
-        <v>0.3418379521802449</v>
+        <v>0.3764392730526144</v>
       </c>
       <c r="X21">
-        <v>3.295043266883406</v>
+        <v>3.238246131503166</v>
       </c>
       <c r="Y21">
-        <v>0.329032409824808</v>
+        <v>0.3755698910833398</v>
       </c>
       <c r="Z21">
-        <v>7.24317551325502</v>
+        <v>7.328498253362774</v>
       </c>
       <c r="AA21">
-        <v>0.6152873168782448</v>
+        <v>0.7270408256098997</v>
       </c>
       <c r="AB21">
-        <v>14.53346897361103</v>
+        <v>14.45880202822606</v>
       </c>
       <c r="AC21">
-        <v>1.067610119725944</v>
+        <v>1.366373221736296</v>
       </c>
       <c r="AD21">
-        <v>34.9499018165866</v>
+        <v>34.84934155448439</v>
       </c>
       <c r="AE21">
-        <v>1.628650568763459</v>
+        <v>1.558374448772369</v>
       </c>
     </row>
     <row r="22" spans="1:31">
@@ -6070,94 +6070,94 @@
         <v>2040</v>
       </c>
       <c r="B22">
-        <v>147.6277319126625</v>
+        <v>149.0854072357391</v>
       </c>
       <c r="C22">
-        <v>7.238893658155416</v>
+        <v>7.538872662458288</v>
       </c>
       <c r="D22">
-        <v>73.34447360002353</v>
+        <v>73.78692225142612</v>
       </c>
       <c r="E22">
-        <v>4.45331822297246</v>
+        <v>4.610673252253872</v>
       </c>
       <c r="F22">
-        <v>74.28325831263908</v>
+        <v>75.29848498431296</v>
       </c>
       <c r="G22">
-        <v>4.297820163759537</v>
+        <v>4.672333035244393</v>
       </c>
       <c r="H22">
-        <v>22.49588174533105</v>
+        <v>22.55574344660516</v>
       </c>
       <c r="I22">
-        <v>1.465366644866051</v>
+        <v>1.793148131430177</v>
       </c>
       <c r="J22">
-        <v>22.20523795894077</v>
+        <v>22.50354001626601</v>
       </c>
       <c r="K22">
-        <v>1.392006672143422</v>
+        <v>1.717126532837474</v>
       </c>
       <c r="L22">
-        <v>7.405382823031811</v>
+        <v>7.610605911612124</v>
       </c>
       <c r="M22">
-        <v>0.7360885409594459</v>
+        <v>0.5486833799733757</v>
       </c>
       <c r="N22">
-        <v>14.82455285023766</v>
+        <v>15.16492612887253</v>
       </c>
       <c r="O22">
-        <v>0.9195605074109842</v>
+        <v>1.270124344695937</v>
       </c>
       <c r="P22">
-        <v>7.352202935097779</v>
+        <v>7.463669480957143</v>
       </c>
       <c r="Q22">
-        <v>0.6517551313542057</v>
+        <v>0.6256049088259888</v>
       </c>
       <c r="R22">
-        <v>22.49588174533105</v>
+        <v>22.55574344660516</v>
       </c>
       <c r="S22">
-        <v>1.465366644866051</v>
+        <v>1.793148131430177</v>
       </c>
       <c r="T22">
-        <v>15.37458550065847</v>
+        <v>15.82750202336664</v>
       </c>
       <c r="U22">
-        <v>1.079440791522133</v>
+        <v>1.226116296305393</v>
       </c>
       <c r="V22">
-        <v>3.412707598218708</v>
+        <v>3.358266002334761</v>
       </c>
       <c r="W22">
-        <v>0.351395036953125</v>
+        <v>0.4051478894702281</v>
       </c>
       <c r="X22">
-        <v>3.417944860063586</v>
+        <v>3.317771990564613</v>
       </c>
       <c r="Y22">
-        <v>0.3859950034421889</v>
+        <v>0.4098642837762938</v>
       </c>
       <c r="Z22">
-        <v>7.405382823031811</v>
+        <v>7.610605911612124</v>
       </c>
       <c r="AA22">
-        <v>0.7360885409594459</v>
+        <v>0.5486833799733757</v>
       </c>
       <c r="AB22">
-        <v>14.82455285023766</v>
+        <v>15.16492612887253</v>
       </c>
       <c r="AC22">
-        <v>0.9195605074109842</v>
+        <v>1.270124344695937</v>
       </c>
       <c r="AD22">
-        <v>36.21545968558442</v>
+        <v>35.9622227058607</v>
       </c>
       <c r="AE22">
-        <v>1.287213366046899</v>
+        <v>2.002671071566923</v>
       </c>
     </row>
   </sheetData>
@@ -6240,64 +6240,64 @@
         <v>2020</v>
       </c>
       <c r="B2">
-        <v>25.35411340129717</v>
+        <v>25.24457228895476</v>
       </c>
       <c r="C2">
-        <v>1.540564839277451</v>
+        <v>1.292897462832222</v>
       </c>
       <c r="D2">
-        <v>25.35411340129717</v>
+        <v>25.24457228895476</v>
       </c>
       <c r="E2">
-        <v>1.540564839277451</v>
+        <v>1.292897462832222</v>
       </c>
       <c r="F2">
-        <v>2.528132343436519</v>
+        <v>2.484871516158154</v>
       </c>
       <c r="G2">
-        <v>0.2222482511852688</v>
+        <v>0.2097810819799739</v>
       </c>
       <c r="H2">
-        <v>2.528132343436519</v>
+        <v>2.484871516158154</v>
       </c>
       <c r="I2">
-        <v>0.2222482511852688</v>
+        <v>0.2097810819799739</v>
       </c>
       <c r="J2">
-        <v>12.85023954349271</v>
+        <v>12.65902960445379</v>
       </c>
       <c r="K2">
-        <v>0.8516137291373908</v>
+        <v>0.9036777241148544</v>
       </c>
       <c r="L2">
-        <v>12.85023954349271</v>
+        <v>12.65902960445379</v>
       </c>
       <c r="M2">
-        <v>0.8516137291373908</v>
+        <v>0.9036777241148544</v>
       </c>
       <c r="N2">
-        <v>8.653087416286773</v>
+        <v>8.600170882560404</v>
       </c>
       <c r="O2">
-        <v>0.5764025297029057</v>
+        <v>0.6127156752418262</v>
       </c>
       <c r="P2">
-        <v>8.653087416286773</v>
+        <v>8.600170882560404</v>
       </c>
       <c r="Q2">
-        <v>0.5764025297029057</v>
+        <v>0.6127156752418262</v>
       </c>
       <c r="R2">
-        <v>1.135333905196172</v>
+        <v>1.168452305346305</v>
       </c>
       <c r="S2">
-        <v>0.1364416762387468</v>
+        <v>0.114166934431957</v>
       </c>
       <c r="T2">
-        <v>1.135333905196172</v>
+        <v>1.168452305346305</v>
       </c>
       <c r="U2">
-        <v>0.1364416762387468</v>
+        <v>0.114166934431957</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -6305,64 +6305,64 @@
         <v>2021</v>
       </c>
       <c r="B3">
-        <v>27.6887940990326</v>
+        <v>27.25683682824483</v>
       </c>
       <c r="C3">
-        <v>1.826930315970957</v>
+        <v>1.694331535370261</v>
       </c>
       <c r="D3">
-        <v>53.04290750032975</v>
+        <v>52.50140911719959</v>
       </c>
       <c r="E3">
-        <v>2.289289470446939</v>
+        <v>2.137426836779183</v>
       </c>
       <c r="F3">
-        <v>2.741868677431609</v>
+        <v>2.723422159344876</v>
       </c>
       <c r="G3">
-        <v>0.246024078556095</v>
+        <v>0.2450846217271386</v>
       </c>
       <c r="H3">
-        <v>5.270001020868127</v>
+        <v>5.20829367550303</v>
       </c>
       <c r="I3">
-        <v>0.3621106868537332</v>
+        <v>0.3433263798282535</v>
       </c>
       <c r="J3">
-        <v>5.636580803551929</v>
+        <v>5.798670812734977</v>
       </c>
       <c r="K3">
-        <v>1.096716407509592</v>
+        <v>1.183380027709805</v>
       </c>
       <c r="L3">
-        <v>18.48682034704463</v>
+        <v>18.45770041718877</v>
       </c>
       <c r="M3">
-        <v>0.9446019761708098</v>
+        <v>1.073054149109127</v>
       </c>
       <c r="N3">
-        <v>18.04451165646491</v>
+        <v>17.56019440240843</v>
       </c>
       <c r="O3">
-        <v>1.010325528238096</v>
+        <v>1.047111425868614</v>
       </c>
       <c r="P3">
-        <v>26.69759907275167</v>
+        <v>26.16036528496883</v>
       </c>
       <c r="Q3">
-        <v>1.395367384412128</v>
+        <v>1.488984270479633</v>
       </c>
       <c r="R3">
-        <v>1.245790304592054</v>
+        <v>1.235874756408689</v>
       </c>
       <c r="S3">
-        <v>0.1262950988268673</v>
+        <v>0.1321268927049191</v>
       </c>
       <c r="T3">
-        <v>2.381124209788226</v>
+        <v>2.404327061754993</v>
       </c>
       <c r="U3">
-        <v>0.1888767098310767</v>
+        <v>0.1921453479923979</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -6370,64 +6370,64 @@
         <v>2022</v>
       </c>
       <c r="B4">
-        <v>29.79250135683034</v>
+        <v>30.03334825807666</v>
       </c>
       <c r="C4">
-        <v>1.692769173129575</v>
+        <v>1.948460192300637</v>
       </c>
       <c r="D4">
-        <v>82.8354088571601</v>
+        <v>82.53475737527624</v>
       </c>
       <c r="E4">
-        <v>3.060086870766806</v>
+        <v>2.978717555729351</v>
       </c>
       <c r="F4">
-        <v>3.020087295639284</v>
+        <v>3.006887947509259</v>
       </c>
       <c r="G4">
-        <v>0.2530141099849345</v>
+        <v>0.2389280696980747</v>
       </c>
       <c r="H4">
-        <v>8.290088316507415</v>
+        <v>8.21518162301229</v>
       </c>
       <c r="I4">
-        <v>0.3884282419790746</v>
+        <v>0.481818146979107</v>
       </c>
       <c r="J4">
-        <v>3.298668073737379</v>
+        <v>3.392310520067643</v>
       </c>
       <c r="K4">
-        <v>1.01297973086352</v>
+        <v>1.197680223287449</v>
       </c>
       <c r="L4">
-        <v>21.78548842078201</v>
+        <v>21.85001093725641</v>
       </c>
       <c r="M4">
-        <v>1.142608046905871</v>
+        <v>1.357304790758269</v>
       </c>
       <c r="N4">
-        <v>22.3722778022302</v>
+        <v>22.17712826451774</v>
       </c>
       <c r="O4">
-        <v>0.9448506720554135</v>
+        <v>1.136403777944439</v>
       </c>
       <c r="P4">
-        <v>49.0698768749819</v>
+        <v>48.33749354948657</v>
       </c>
       <c r="Q4">
-        <v>1.894290047348387</v>
+        <v>2.310013604497542</v>
       </c>
       <c r="R4">
-        <v>1.353838501864912</v>
+        <v>1.369950946552552</v>
       </c>
       <c r="S4">
-        <v>0.1392381788131636</v>
+        <v>0.1225055319518751</v>
       </c>
       <c r="T4">
-        <v>3.734962711653137</v>
+        <v>3.774278008307546</v>
       </c>
       <c r="U4">
-        <v>0.2229048383976761</v>
+        <v>0.250247048862179</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -6435,64 +6435,64 @@
         <v>2023</v>
       </c>
       <c r="B5">
-        <v>32.111708924642</v>
+        <v>32.85914439918344</v>
       </c>
       <c r="C5">
-        <v>2.139732613913315</v>
+        <v>2.117106146119645</v>
       </c>
       <c r="D5">
-        <v>114.9471177818021</v>
+        <v>115.3939017744597</v>
       </c>
       <c r="E5">
-        <v>2.992442127721824</v>
+        <v>3.853754562162668</v>
       </c>
       <c r="F5">
-        <v>3.29093148345734</v>
+        <v>3.270148964915929</v>
       </c>
       <c r="G5">
-        <v>0.2640790623363066</v>
+        <v>0.2989070823864001</v>
       </c>
       <c r="H5">
-        <v>11.58101979996475</v>
+        <v>11.48533058792822</v>
       </c>
       <c r="I5">
-        <v>0.4231834803632731</v>
+        <v>0.6342903803349277</v>
       </c>
       <c r="J5">
-        <v>2.446030571871376</v>
+        <v>2.589276847743114</v>
       </c>
       <c r="K5">
-        <v>1.419152542263047</v>
+        <v>1.41790394267414</v>
       </c>
       <c r="L5">
-        <v>24.23151899265339</v>
+        <v>24.43928778499951</v>
       </c>
       <c r="M5">
-        <v>1.763848368745322</v>
+        <v>1.553603729856215</v>
       </c>
       <c r="N5">
-        <v>25.43093954079374</v>
+        <v>25.11105233792843</v>
       </c>
       <c r="O5">
-        <v>0.9959034520460445</v>
+        <v>1.117311953352604</v>
       </c>
       <c r="P5">
-        <v>74.5008164157756</v>
+        <v>73.44854588741504</v>
       </c>
       <c r="Q5">
-        <v>2.300212867527906</v>
+        <v>3.078154208284171</v>
       </c>
       <c r="R5">
-        <v>1.460074536631456</v>
+        <v>1.466138368796604</v>
       </c>
       <c r="S5">
-        <v>0.1778105724863899</v>
+        <v>0.1321272348826124</v>
       </c>
       <c r="T5">
-        <v>5.195037248284592</v>
+        <v>5.240416377104151</v>
       </c>
       <c r="U5">
-        <v>0.282277219623961</v>
+        <v>0.2786315563742572</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -6500,64 +6500,64 @@
         <v>2024</v>
       </c>
       <c r="B6">
-        <v>34.71381765369868</v>
+        <v>35.16400611814424</v>
       </c>
       <c r="C6">
-        <v>1.965837361517666</v>
+        <v>2.508619216375895</v>
       </c>
       <c r="D6">
-        <v>149.6609354355008</v>
+        <v>150.5579078926039</v>
       </c>
       <c r="E6">
-        <v>3.105849353882925</v>
+        <v>4.350836892430388</v>
       </c>
       <c r="F6">
-        <v>3.486184189098558</v>
+        <v>3.513370745836997</v>
       </c>
       <c r="G6">
-        <v>0.2997092704883336</v>
+        <v>0.3112305609813006</v>
       </c>
       <c r="H6">
-        <v>15.06720398906331</v>
+        <v>14.99870133376521</v>
       </c>
       <c r="I6">
-        <v>0.5333320606397075</v>
+        <v>0.7137001008290718</v>
       </c>
       <c r="J6">
-        <v>2.231088033484968</v>
+        <v>2.331345011026452</v>
       </c>
       <c r="K6">
-        <v>1.364311715001386</v>
+        <v>1.393117223040397</v>
       </c>
       <c r="L6">
-        <v>26.46260702613835</v>
+        <v>26.77063279602598</v>
       </c>
       <c r="M6">
-        <v>1.966879036701577</v>
+        <v>1.6588593612711</v>
       </c>
       <c r="N6">
-        <v>27.81050202219046</v>
+        <v>27.64726563319951</v>
       </c>
       <c r="O6">
-        <v>1.058546190530263</v>
+        <v>1.021096865480792</v>
       </c>
       <c r="P6">
-        <v>102.3113184379661</v>
+        <v>101.0958115206145</v>
       </c>
       <c r="Q6">
-        <v>2.812930735151675</v>
+        <v>3.636067991203257</v>
       </c>
       <c r="R6">
-        <v>1.542750005059093</v>
+        <v>1.566243108164528</v>
       </c>
       <c r="S6">
-        <v>0.164569242508421</v>
+        <v>0.1712629689624998</v>
       </c>
       <c r="T6">
-        <v>6.737787253343684</v>
+        <v>6.806659485268675</v>
       </c>
       <c r="U6">
-        <v>0.2942312776395929</v>
+        <v>0.3248192131494401</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -6565,64 +6565,64 @@
         <v>2025</v>
       </c>
       <c r="B7">
-        <v>37.31580199425409</v>
+        <v>38.18852699382029</v>
       </c>
       <c r="C7">
-        <v>1.957225648652124</v>
+        <v>2.057279295579067</v>
       </c>
       <c r="D7">
-        <v>186.9767374297549</v>
+        <v>188.7464348864242</v>
       </c>
       <c r="E7">
-        <v>3.562138760216569</v>
+        <v>4.263798288179835</v>
       </c>
       <c r="F7">
-        <v>3.80710840440442</v>
+        <v>3.856350193621868</v>
       </c>
       <c r="G7">
-        <v>0.3195085141119338</v>
+        <v>0.341385204407016</v>
       </c>
       <c r="H7">
-        <v>18.87431239346773</v>
+        <v>18.85505152738708</v>
       </c>
       <c r="I7">
-        <v>0.5828767084516765</v>
+        <v>0.7278201291612036</v>
       </c>
       <c r="J7">
-        <v>2.068061126886303</v>
+        <v>2.300984470201051</v>
       </c>
       <c r="K7">
-        <v>1.493886868633633</v>
+        <v>1.27032106223554</v>
       </c>
       <c r="L7">
-        <v>28.53066815302466</v>
+        <v>29.07161726622702</v>
       </c>
       <c r="M7">
-        <v>2.310375607959555</v>
+        <v>1.673015554005384</v>
       </c>
       <c r="N7">
-        <v>30.29293498096555</v>
+        <v>30.11605336420187</v>
       </c>
       <c r="O7">
-        <v>1.305363893360112</v>
+        <v>1.260094323425523</v>
       </c>
       <c r="P7">
-        <v>132.6042534189316</v>
+        <v>131.2118648848164</v>
       </c>
       <c r="Q7">
-        <v>3.261177344970188</v>
+        <v>4.252444730329182</v>
       </c>
       <c r="R7">
-        <v>1.708900442526517</v>
+        <v>1.700046466242333</v>
       </c>
       <c r="S7">
-        <v>0.2027450272972777</v>
+        <v>0.1932168817230498</v>
       </c>
       <c r="T7">
-        <v>8.446687695870203</v>
+        <v>8.506705951511011</v>
       </c>
       <c r="U7">
-        <v>0.3188214784140723</v>
+        <v>0.3294757657681614</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -6630,64 +6630,64 @@
         <v>2026</v>
       </c>
       <c r="B8">
-        <v>40.23260431677053</v>
+        <v>39.93354781927816</v>
       </c>
       <c r="C8">
-        <v>1.876096985927994</v>
+        <v>2.336288837900946</v>
       </c>
       <c r="D8">
-        <v>227.2093417465254</v>
+        <v>228.6799827057023</v>
       </c>
       <c r="E8">
-        <v>3.906731629123991</v>
+        <v>5.269964830073368</v>
       </c>
       <c r="F8">
-        <v>4.033870915362913</v>
+        <v>4.008532857385351</v>
       </c>
       <c r="G8">
-        <v>0.3606525040353185</v>
+        <v>0.308942617972202</v>
       </c>
       <c r="H8">
-        <v>22.90818330883064</v>
+        <v>22.86358438477243</v>
       </c>
       <c r="I8">
-        <v>0.6939954164910528</v>
+        <v>0.8143232171988247</v>
       </c>
       <c r="J8">
-        <v>2.047946934985292</v>
+        <v>2.01798149174912</v>
       </c>
       <c r="K8">
-        <v>1.29063319575198</v>
+        <v>1.447416680069343</v>
       </c>
       <c r="L8">
-        <v>30.57861508800995</v>
+        <v>31.08959875797614</v>
       </c>
       <c r="M8">
-        <v>2.029932406052901</v>
+        <v>1.83606869759148</v>
       </c>
       <c r="N8">
-        <v>32.31947531684085</v>
+        <v>32.26105918200535</v>
       </c>
       <c r="O8">
-        <v>1.265269682568188</v>
+        <v>1.305648083240188</v>
       </c>
       <c r="P8">
-        <v>164.9237287357725</v>
+        <v>163.4729240668217</v>
       </c>
       <c r="Q8">
-        <v>3.686337108525274</v>
+        <v>4.8930846237492</v>
       </c>
       <c r="R8">
-        <v>1.810158892090379</v>
+        <v>1.849308421133686</v>
       </c>
       <c r="S8">
-        <v>0.2106979429676362</v>
+        <v>0.1766462304681818</v>
       </c>
       <c r="T8">
-        <v>10.25684658796058</v>
+        <v>10.3560143726447</v>
       </c>
       <c r="U8">
-        <v>0.3555821602941067</v>
+        <v>0.3636654606755941</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -6695,64 +6695,64 @@
         <v>2027</v>
       </c>
       <c r="B9">
-        <v>41.81336105700422</v>
+        <v>42.23744549290257</v>
       </c>
       <c r="C9">
-        <v>3.038705819809163</v>
+        <v>2.121935275849374</v>
       </c>
       <c r="D9">
-        <v>269.0227028035296</v>
+        <v>270.9174281986049</v>
       </c>
       <c r="E9">
-        <v>4.925618988701924</v>
+        <v>5.818093958805822</v>
       </c>
       <c r="F9">
-        <v>4.281778746264959</v>
+        <v>4.201902678710495</v>
       </c>
       <c r="G9">
-        <v>0.3936909152132196</v>
+        <v>0.3705299609679102</v>
       </c>
       <c r="H9">
-        <v>27.1899620550956</v>
+        <v>27.06548706348293</v>
       </c>
       <c r="I9">
-        <v>0.7283653655202869</v>
+        <v>0.9715334219775682</v>
       </c>
       <c r="J9">
-        <v>1.579257594338735</v>
+        <v>1.856486625065263</v>
       </c>
       <c r="K9">
-        <v>2.074305555867626</v>
+        <v>1.821937480836472</v>
       </c>
       <c r="L9">
-        <v>32.15787268234868</v>
+        <v>32.94608538304142</v>
       </c>
       <c r="M9">
-        <v>2.407962364427816</v>
+        <v>2.177532727728843</v>
       </c>
       <c r="N9">
-        <v>34.48541022515728</v>
+        <v>34.289637027758</v>
       </c>
       <c r="O9">
-        <v>1.068389379960367</v>
+        <v>1.308287338770345</v>
       </c>
       <c r="P9">
-        <v>199.4091389609298</v>
+        <v>197.7625610945797</v>
       </c>
       <c r="Q9">
-        <v>3.976995683130872</v>
+        <v>5.477195729934168</v>
       </c>
       <c r="R9">
-        <v>1.920635526376794</v>
+        <v>1.941672124587264</v>
       </c>
       <c r="S9">
-        <v>0.1965298688510005</v>
+        <v>0.2274952249894093</v>
       </c>
       <c r="T9">
-        <v>12.17748211433737</v>
+        <v>12.29768649723196</v>
       </c>
       <c r="U9">
-        <v>0.4185648657063649</v>
+        <v>0.4442235432170952</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -6760,64 +6760,64 @@
         <v>2028</v>
       </c>
       <c r="B10">
-        <v>44.76620243003374</v>
+        <v>44.92700299847004</v>
       </c>
       <c r="C10">
-        <v>2.878841971130918</v>
+        <v>2.688700176913707</v>
       </c>
       <c r="D10">
-        <v>313.7889052335634</v>
+        <v>315.844431197075</v>
       </c>
       <c r="E10">
-        <v>5.769407248614187</v>
+        <v>6.237018415632991</v>
       </c>
       <c r="F10">
-        <v>4.44834113848306</v>
+        <v>4.547438298664695</v>
       </c>
       <c r="G10">
-        <v>0.4450693669384551</v>
+        <v>0.3468465818112295</v>
       </c>
       <c r="H10">
-        <v>31.63830319357866</v>
+        <v>31.61292536214762</v>
       </c>
       <c r="I10">
-        <v>0.8784005933431751</v>
+        <v>1.080167684580152</v>
       </c>
       <c r="J10">
-        <v>1.478932935310747</v>
+        <v>2.247479605964027</v>
       </c>
       <c r="K10">
-        <v>1.777386877933623</v>
+        <v>1.951357431763098</v>
       </c>
       <c r="L10">
-        <v>33.63680561765943</v>
+        <v>35.19356498900544</v>
       </c>
       <c r="M10">
-        <v>2.695229217002255</v>
+        <v>2.156079949423262</v>
       </c>
       <c r="N10">
-        <v>36.20512197113249</v>
+        <v>36.48976212303654</v>
       </c>
       <c r="O10">
-        <v>1.693891894111745</v>
+        <v>1.235850215823681</v>
       </c>
       <c r="P10">
-        <v>235.6142609320623</v>
+        <v>234.2523232176162</v>
       </c>
       <c r="Q10">
-        <v>4.478654327557717</v>
+        <v>5.999560886789039</v>
       </c>
       <c r="R10">
-        <v>2.044016928362528</v>
+        <v>2.018769256552894</v>
       </c>
       <c r="S10">
-        <v>0.2450258132819976</v>
+        <v>0.2023385714083736</v>
       </c>
       <c r="T10">
-        <v>14.2214990426999</v>
+        <v>14.31645575378486</v>
       </c>
       <c r="U10">
-        <v>0.4740499034841165</v>
+        <v>0.4889984974859284</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -6825,64 +6825,64 @@
         <v>2029</v>
       </c>
       <c r="B11">
-        <v>46.77118206313334</v>
+        <v>47.18696589869393</v>
       </c>
       <c r="C11">
-        <v>2.566967504397573</v>
+        <v>3.226150977677583</v>
       </c>
       <c r="D11">
-        <v>360.5600872966967</v>
+        <v>363.0313970957687</v>
       </c>
       <c r="E11">
-        <v>6.244955513282802</v>
+        <v>6.735047338091514</v>
       </c>
       <c r="F11">
-        <v>4.732392888607971</v>
+        <v>4.833322150836089</v>
       </c>
       <c r="G11">
-        <v>0.3277141247366481</v>
+        <v>0.4891600201634535</v>
       </c>
       <c r="H11">
-        <v>36.37069608218663</v>
+        <v>36.44624751298371</v>
       </c>
       <c r="I11">
-        <v>0.9914607000761884</v>
+        <v>1.09556463792634</v>
       </c>
       <c r="J11">
-        <v>2.445879919239293</v>
+        <v>1.861100518237636</v>
       </c>
       <c r="K11">
-        <v>1.913583556728713</v>
+        <v>2.121876001201401</v>
       </c>
       <c r="L11">
-        <v>36.08268553689872</v>
+        <v>37.05466550724307</v>
       </c>
       <c r="M11">
-        <v>2.641107343548329</v>
+        <v>2.526239935748113</v>
       </c>
       <c r="N11">
-        <v>38.03307587301327</v>
+        <v>38.97126808815541</v>
       </c>
       <c r="O11">
-        <v>1.710320229400963</v>
+        <v>1.553986320949175</v>
       </c>
       <c r="P11">
-        <v>273.6473368050756</v>
+        <v>273.2235913057717</v>
       </c>
       <c r="Q11">
-        <v>5.005806922256943</v>
+        <v>6.508320366763047</v>
       </c>
       <c r="R11">
-        <v>2.122118721891106</v>
+        <v>2.165725253485271</v>
       </c>
       <c r="S11">
-        <v>0.2372465141665232</v>
+        <v>0.2373158726812129</v>
       </c>
       <c r="T11">
-        <v>16.34361776459101</v>
+        <v>16.48218100727012</v>
       </c>
       <c r="U11">
-        <v>0.5195673230293666</v>
+        <v>0.5657258298233565</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -6890,64 +6890,64 @@
         <v>2030</v>
       </c>
       <c r="B12">
-        <v>50.21828680991764</v>
+        <v>49.4927125039103</v>
       </c>
       <c r="C12">
-        <v>2.869098935780423</v>
+        <v>3.154942025807223</v>
       </c>
       <c r="D12">
-        <v>410.7783741066143</v>
+        <v>412.5241095996792</v>
       </c>
       <c r="E12">
-        <v>6.642264038519992</v>
+        <v>7.769755967285789</v>
       </c>
       <c r="F12">
-        <v>4.997690236493138</v>
+        <v>5.024295456140931</v>
       </c>
       <c r="G12">
-        <v>0.4805181785626039</v>
+        <v>0.4228737567025853</v>
       </c>
       <c r="H12">
-        <v>41.36838631867977</v>
+        <v>41.47054296912463</v>
       </c>
       <c r="I12">
-        <v>1.180813677851445</v>
+        <v>1.12856630102679</v>
       </c>
       <c r="J12">
-        <v>2.328737123008161</v>
+        <v>1.913764553386256</v>
       </c>
       <c r="K12">
-        <v>2.078002127015286</v>
+        <v>1.804144444674681</v>
       </c>
       <c r="L12">
-        <v>38.41142265990689</v>
+        <v>38.96843006062931</v>
       </c>
       <c r="M12">
-        <v>2.646390232632398</v>
+        <v>2.679458459930493</v>
       </c>
       <c r="N12">
-        <v>40.88942823299089</v>
+        <v>40.79069880939264</v>
       </c>
       <c r="O12">
-        <v>1.693596450369943</v>
+        <v>1.580284403500426</v>
       </c>
       <c r="P12">
-        <v>314.5367650380664</v>
+        <v>314.0142901151644</v>
       </c>
       <c r="Q12">
-        <v>5.712981988265286</v>
+        <v>6.564889246538141</v>
       </c>
       <c r="R12">
-        <v>2.248006395015966</v>
+        <v>2.200881515886955</v>
       </c>
       <c r="S12">
-        <v>0.2066968632274332</v>
+        <v>0.2175809994576081</v>
       </c>
       <c r="T12">
-        <v>18.59162415960698</v>
+        <v>18.68306252315708</v>
       </c>
       <c r="U12">
-        <v>0.5825675651365856</v>
+        <v>0.6219643092382943</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -6955,64 +6955,64 @@
         <v>2031</v>
       </c>
       <c r="B13">
-        <v>2.496280389584476</v>
+        <v>2.509172638871949</v>
       </c>
       <c r="C13">
-        <v>0.1462934176143341</v>
+        <v>0.1381153215691751</v>
       </c>
       <c r="D13">
-        <v>413.2746544961989</v>
+        <v>415.0332822385511</v>
       </c>
       <c r="E13">
-        <v>6.622703653865424</v>
+        <v>7.788108815971229</v>
       </c>
       <c r="F13">
-        <v>0.2485370991247804</v>
+        <v>0.2532355061325826</v>
       </c>
       <c r="G13">
-        <v>0.01811326843005469</v>
+        <v>0.02502909919430259</v>
       </c>
       <c r="H13">
-        <v>41.61692341780454</v>
+        <v>41.72377847525724</v>
       </c>
       <c r="I13">
-        <v>1.181799136939569</v>
+        <v>1.130184878902656</v>
       </c>
       <c r="J13">
-        <v>-23.63399286847879</v>
+        <v>-23.49274218835064</v>
       </c>
       <c r="K13">
-        <v>1.066507857321034</v>
+        <v>1.151917632073774</v>
       </c>
       <c r="L13">
-        <v>14.7774297914281</v>
+        <v>15.47568787227868</v>
       </c>
       <c r="M13">
-        <v>2.318801404110227</v>
+        <v>2.133958826608299</v>
       </c>
       <c r="N13">
-        <v>25.77510007781859</v>
+        <v>25.62912335425268</v>
       </c>
       <c r="O13">
-        <v>1.05603263591447</v>
+        <v>1.134171941615763</v>
       </c>
       <c r="P13">
-        <v>340.3118651158849</v>
+        <v>339.643413469417</v>
       </c>
       <c r="Q13">
-        <v>6.055634273172553</v>
+        <v>6.614785233415631</v>
       </c>
       <c r="R13">
-        <v>0.111486564188628</v>
+        <v>0.1124272425576737</v>
       </c>
       <c r="S13">
-        <v>0.01464753725628035</v>
+        <v>0.0141665915831577</v>
       </c>
       <c r="T13">
-        <v>18.7031107237956</v>
+        <v>18.79548976571475</v>
       </c>
       <c r="U13">
-        <v>0.5821792742274583</v>
+        <v>0.6221532454039098</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -7020,64 +7020,64 @@
         <v>2032</v>
       </c>
       <c r="B14">
-        <v>54.99122579397785</v>
+        <v>54.61388932534805</v>
       </c>
       <c r="C14">
-        <v>3.945122079568969</v>
+        <v>3.55681132794463</v>
       </c>
       <c r="D14">
-        <v>468.2658802901767</v>
+        <v>469.6471715638992</v>
       </c>
       <c r="E14">
-        <v>7.686869255657105</v>
+        <v>8.574419556604461</v>
       </c>
       <c r="F14">
-        <v>5.496766465100251</v>
+        <v>5.429367849332878</v>
       </c>
       <c r="G14">
-        <v>0.5172854510242976</v>
+        <v>0.4965650860185318</v>
       </c>
       <c r="H14">
-        <v>47.1136898829048</v>
+        <v>47.15314632459012</v>
       </c>
       <c r="I14">
-        <v>1.424417852054406</v>
+        <v>1.245894341862282</v>
       </c>
       <c r="J14">
-        <v>18.49568993540474</v>
+        <v>17.9495673362339</v>
       </c>
       <c r="K14">
-        <v>1.884987442133379</v>
+        <v>1.6879472040412</v>
       </c>
       <c r="L14">
-        <v>33.27311972683285</v>
+        <v>33.42525520851259</v>
       </c>
       <c r="M14">
-        <v>2.414571722847783</v>
+        <v>2.331640435186754</v>
       </c>
       <c r="N14">
-        <v>27.89905725848608</v>
+        <v>28.46631388864314</v>
       </c>
       <c r="O14">
-        <v>1.736323899512693</v>
+        <v>1.475696887960477</v>
       </c>
       <c r="P14">
-        <v>368.2109223743711</v>
+        <v>368.1097273580602</v>
       </c>
       <c r="Q14">
-        <v>6.635954358604528</v>
+        <v>6.601400383958803</v>
       </c>
       <c r="R14">
-        <v>2.43045982344227</v>
+        <v>2.435459452828916</v>
       </c>
       <c r="S14">
-        <v>0.3016574586973632</v>
+        <v>0.2378165329115204</v>
       </c>
       <c r="T14">
-        <v>21.13357054723788</v>
+        <v>21.23094921854367</v>
       </c>
       <c r="U14">
-        <v>0.7317748796922725</v>
+        <v>0.6692395718977807</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -7085,64 +7085,64 @@
         <v>2033</v>
       </c>
       <c r="B15">
-        <v>56.97923876744524</v>
+        <v>57.70835169746343</v>
       </c>
       <c r="C15">
-        <v>3.981928383560119</v>
+        <v>3.03327306737529</v>
       </c>
       <c r="D15">
-        <v>525.2451190576219</v>
+        <v>527.3555232613627</v>
       </c>
       <c r="E15">
-        <v>8.685420169335053</v>
+        <v>9.26308415965218</v>
       </c>
       <c r="F15">
-        <v>5.733871554472446</v>
+        <v>5.816961873465037</v>
       </c>
       <c r="G15">
-        <v>0.4459217615775258</v>
+        <v>0.5103953710973063</v>
       </c>
       <c r="H15">
-        <v>52.84756143737728</v>
+        <v>52.97010819805515</v>
       </c>
       <c r="I15">
-        <v>1.489363728070126</v>
+        <v>1.274134742558203</v>
       </c>
       <c r="J15">
-        <v>7.281950099017629</v>
+        <v>7.855466038380841</v>
       </c>
       <c r="K15">
-        <v>2.183085761491649</v>
+        <v>2.110636477826218</v>
       </c>
       <c r="L15">
-        <v>40.55506982585048</v>
+        <v>41.28072124689343</v>
       </c>
       <c r="M15">
-        <v>2.523847566818886</v>
+        <v>2.925462985952767</v>
       </c>
       <c r="N15">
-        <v>41.43323814926492</v>
+        <v>41.25212980009419</v>
       </c>
       <c r="O15">
-        <v>1.862675861265368</v>
+        <v>1.959430747416879</v>
       </c>
       <c r="P15">
-        <v>409.644160523636</v>
+        <v>409.3618571581545</v>
       </c>
       <c r="Q15">
-        <v>7.089814819383879</v>
+        <v>7.126330574841709</v>
       </c>
       <c r="R15">
-        <v>2.528752040501939</v>
+        <v>2.594695912961299</v>
       </c>
       <c r="S15">
-        <v>0.2661718029762631</v>
+        <v>0.2938952839513732</v>
       </c>
       <c r="T15">
-        <v>23.66232258773981</v>
+        <v>23.82564513150497</v>
       </c>
       <c r="U15">
-        <v>0.7274962742021639</v>
+        <v>0.7638321875652028</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -7150,64 +7150,64 @@
         <v>2034</v>
       </c>
       <c r="B16">
-        <v>59.76009299885563</v>
+        <v>60.59413585314783</v>
       </c>
       <c r="C16">
-        <v>4.198500184313873</v>
+        <v>3.64567695935763</v>
       </c>
       <c r="D16">
-        <v>585.0052120564776</v>
+        <v>587.9496591145104</v>
       </c>
       <c r="E16">
-        <v>9.154916619145231</v>
+        <v>10.20758415433445</v>
       </c>
       <c r="F16">
-        <v>5.9999569792937</v>
+        <v>5.829829719888949</v>
       </c>
       <c r="G16">
-        <v>0.541491290142503</v>
+        <v>0.4487976328858077</v>
       </c>
       <c r="H16">
-        <v>58.84751841667094</v>
+        <v>58.7999379179441</v>
       </c>
       <c r="I16">
-        <v>1.507523692509746</v>
+        <v>1.293874768745314</v>
       </c>
       <c r="J16">
-        <v>4.12966643484163</v>
+        <v>3.777105786749266</v>
       </c>
       <c r="K16">
-        <v>2.489969875720314</v>
+        <v>2.572353863091811</v>
       </c>
       <c r="L16">
-        <v>44.68473626069211</v>
+        <v>45.0578270336427</v>
       </c>
       <c r="M16">
-        <v>2.852495479545033</v>
+        <v>2.975657777584393</v>
       </c>
       <c r="N16">
-        <v>46.73625348036235</v>
+        <v>46.67465722107734</v>
       </c>
       <c r="O16">
-        <v>1.73885062988773</v>
+        <v>1.829859765562761</v>
       </c>
       <c r="P16">
-        <v>456.3804140039985</v>
+        <v>456.0365143792317</v>
       </c>
       <c r="Q16">
-        <v>7.244675767396304</v>
+        <v>7.511164942811011</v>
       </c>
       <c r="R16">
-        <v>2.64342096844958</v>
+        <v>2.649586769559653</v>
       </c>
       <c r="S16">
-        <v>0.2666984023954043</v>
+        <v>0.3116585625189456</v>
       </c>
       <c r="T16">
-        <v>26.30574355618939</v>
+        <v>26.47523190106463</v>
       </c>
       <c r="U16">
-        <v>0.7561698245911381</v>
+        <v>0.8056857930953938</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -7215,64 +7215,64 @@
         <v>2035</v>
       </c>
       <c r="B17">
-        <v>61.87323637002957</v>
+        <v>62.34629623956686</v>
       </c>
       <c r="C17">
-        <v>3.420524267069234</v>
+        <v>3.389225800036392</v>
       </c>
       <c r="D17">
-        <v>646.8784484265069</v>
+        <v>650.2959553540773</v>
       </c>
       <c r="E17">
-        <v>9.08374689459483</v>
+        <v>10.80055541159546</v>
       </c>
       <c r="F17">
-        <v>6.296540966920216</v>
+        <v>6.221018476973866</v>
       </c>
       <c r="G17">
-        <v>0.4891879611770578</v>
+        <v>0.6118553339773527</v>
       </c>
       <c r="H17">
-        <v>65.14405938359117</v>
+        <v>65.02095639491795</v>
       </c>
       <c r="I17">
-        <v>1.65394521786909</v>
+        <v>1.415780563776691</v>
       </c>
       <c r="J17">
-        <v>2.935334091857222</v>
+        <v>3.375690867147451</v>
       </c>
       <c r="K17">
-        <v>2.554502498626503</v>
+        <v>2.388085014489334</v>
       </c>
       <c r="L17">
-        <v>47.62007035254933</v>
+        <v>48.43351790079015</v>
       </c>
       <c r="M17">
-        <v>3.340576564174297</v>
+        <v>3.216277618926057</v>
       </c>
       <c r="N17">
-        <v>50.5246800385336</v>
+        <v>50.07756433840444</v>
       </c>
       <c r="O17">
-        <v>1.684745699666975</v>
+        <v>1.95958584284104</v>
       </c>
       <c r="P17">
-        <v>506.905094042532</v>
+        <v>506.114078717636</v>
       </c>
       <c r="Q17">
-        <v>7.674135905913167</v>
+        <v>7.949050558076616</v>
       </c>
       <c r="R17">
-        <v>2.776318834252079</v>
+        <v>2.82620858795506</v>
       </c>
       <c r="S17">
-        <v>0.3184588869714053</v>
+        <v>0.3359021360652148</v>
       </c>
       <c r="T17">
-        <v>29.08206239044148</v>
+        <v>29.30144048901967</v>
       </c>
       <c r="U17">
-        <v>0.8888707727304859</v>
+        <v>0.8589584377112051</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -7280,64 +7280,64 @@
         <v>2036</v>
       </c>
       <c r="B18">
-        <v>65.00454599520381</v>
+        <v>64.97696354430258</v>
       </c>
       <c r="C18">
-        <v>4.564797160917442</v>
+        <v>4.522666147531498</v>
       </c>
       <c r="D18">
-        <v>711.8829944217109</v>
+        <v>715.2729188983801</v>
       </c>
       <c r="E18">
-        <v>9.923300179226175</v>
+        <v>12.93107657026719</v>
       </c>
       <c r="F18">
-        <v>6.56227729242735</v>
+        <v>6.525179485473545</v>
       </c>
       <c r="G18">
-        <v>0.6447826587086298</v>
+        <v>0.6008785195124396</v>
       </c>
       <c r="H18">
-        <v>71.70633667601854</v>
+        <v>71.54613588039149</v>
       </c>
       <c r="I18">
-        <v>1.879385274180198</v>
+        <v>1.536610492041193</v>
       </c>
       <c r="J18">
-        <v>2.605756450842439</v>
+        <v>2.092636846860996</v>
       </c>
       <c r="K18">
-        <v>3.220553437407485</v>
+        <v>2.885445766551347</v>
       </c>
       <c r="L18">
-        <v>50.22582680339178</v>
+        <v>50.52615474765116</v>
       </c>
       <c r="M18">
-        <v>4.174320398176628</v>
+        <v>3.641777397779502</v>
       </c>
       <c r="N18">
-        <v>53.56108904276213</v>
+        <v>53.32383385048259</v>
       </c>
       <c r="O18">
-        <v>2.053662183782291</v>
+        <v>2.115960451861295</v>
       </c>
       <c r="P18">
-        <v>560.466183085294</v>
+        <v>559.4379125681186</v>
       </c>
       <c r="Q18">
-        <v>8.19787296208313</v>
+        <v>8.985878492849272</v>
       </c>
       <c r="R18">
-        <v>2.94632958507797</v>
+        <v>2.927041854761871</v>
       </c>
       <c r="S18">
-        <v>0.3235847263759942</v>
+        <v>0.3266798266281889</v>
       </c>
       <c r="T18">
-        <v>32.02839197551944</v>
+        <v>32.22848234378155</v>
       </c>
       <c r="U18">
-        <v>0.9346867694807015</v>
+        <v>0.9383782340451418</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -7345,64 +7345,64 @@
         <v>2037</v>
       </c>
       <c r="B19">
-        <v>67.22839358072355</v>
+        <v>66.66550133085474</v>
       </c>
       <c r="C19">
-        <v>4.095712450785647</v>
+        <v>4.474557492046713</v>
       </c>
       <c r="D19">
-        <v>779.1113880024341</v>
+        <v>781.9384202292343</v>
       </c>
       <c r="E19">
-        <v>10.19895085217739</v>
+        <v>12.99229139462749</v>
       </c>
       <c r="F19">
-        <v>6.868329235570416</v>
+        <v>6.683015098370034</v>
       </c>
       <c r="G19">
-        <v>0.5677138054653907</v>
+        <v>0.4852461349431368</v>
       </c>
       <c r="H19">
-        <v>78.57466591158895</v>
+        <v>78.22915097876152</v>
       </c>
       <c r="I19">
-        <v>1.882803841576173</v>
+        <v>1.531552128318842</v>
       </c>
       <c r="J19">
-        <v>1.998722799894684</v>
+        <v>2.148010947063213</v>
       </c>
       <c r="K19">
-        <v>3.012066869369503</v>
+        <v>3.007678438825952</v>
       </c>
       <c r="L19">
-        <v>52.22454960328644</v>
+        <v>52.67416569471435</v>
       </c>
       <c r="M19">
-        <v>3.788058145959087</v>
+        <v>4.028415645750123</v>
       </c>
       <c r="N19">
-        <v>55.782401771617</v>
+        <v>55.06245387272931</v>
       </c>
       <c r="O19">
-        <v>2.255297861895068</v>
+        <v>2.344993651833193</v>
       </c>
       <c r="P19">
-        <v>616.2485848569111</v>
+        <v>614.500366440848</v>
       </c>
       <c r="Q19">
-        <v>8.891215674686803</v>
+        <v>10.27319731793617</v>
       </c>
       <c r="R19">
-        <v>3.077334550299385</v>
+        <v>3.072605040345029</v>
       </c>
       <c r="S19">
-        <v>0.3855142998352674</v>
+        <v>0.3625083255067754</v>
       </c>
       <c r="T19">
-        <v>35.10572652581883</v>
+        <v>35.30108738412657</v>
       </c>
       <c r="U19">
-        <v>1.083910220902223</v>
+        <v>1.088129840816065</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -7410,64 +7410,64 @@
         <v>2038</v>
       </c>
       <c r="B20">
-        <v>69.3927189291058</v>
+        <v>70.25897728758328</v>
       </c>
       <c r="C20">
-        <v>4.656907830469154</v>
+        <v>4.796714109142961</v>
       </c>
       <c r="D20">
-        <v>848.5041069315403</v>
+        <v>852.197397516818</v>
       </c>
       <c r="E20">
-        <v>10.98643368807808</v>
+        <v>14.29930616279333</v>
       </c>
       <c r="F20">
-        <v>6.840622958123563</v>
+        <v>6.911521817121931</v>
       </c>
       <c r="G20">
-        <v>0.5671327538588843</v>
+        <v>0.6545884466046961</v>
       </c>
       <c r="H20">
-        <v>85.41528886971246</v>
+        <v>85.14067279588343</v>
       </c>
       <c r="I20">
-        <v>2.045082101450793</v>
+        <v>1.664126510829166</v>
       </c>
       <c r="J20">
-        <v>1.691736116483214</v>
+        <v>2.144270700091563</v>
       </c>
       <c r="K20">
-        <v>3.071680712324712</v>
+        <v>2.650833145526752</v>
       </c>
       <c r="L20">
-        <v>53.91628571976967</v>
+        <v>54.81843639480592</v>
       </c>
       <c r="M20">
-        <v>4.014392899490576</v>
+        <v>3.542311739604998</v>
       </c>
       <c r="N20">
-        <v>57.75739700421782</v>
+        <v>57.44825082080364</v>
       </c>
       <c r="O20">
-        <v>1.94007144142898</v>
+        <v>2.4297111108634</v>
       </c>
       <c r="P20">
-        <v>674.0059818611289</v>
+        <v>671.9486172616519</v>
       </c>
       <c r="Q20">
-        <v>9.574115427663822</v>
+        <v>11.50376666037205</v>
       </c>
       <c r="R20">
-        <v>3.121965528748954</v>
+        <v>3.156813136414413</v>
       </c>
       <c r="S20">
-        <v>0.3578537583046217</v>
+        <v>0.3388605286829787</v>
       </c>
       <c r="T20">
-        <v>38.22769205456778</v>
+        <v>38.45790052054099</v>
       </c>
       <c r="U20">
-        <v>1.162657329912663</v>
+        <v>1.188604542038078</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -7475,64 +7475,64 @@
         <v>2039</v>
       </c>
       <c r="B21">
-        <v>71.46085666810582</v>
+        <v>72.11686628040013</v>
       </c>
       <c r="C21">
-        <v>4.145693210252559</v>
+        <v>5.375929011230484</v>
       </c>
       <c r="D21">
-        <v>919.9649635996462</v>
+        <v>924.3142637972182</v>
       </c>
       <c r="E21">
-        <v>11.08714008994375</v>
+        <v>15.14872001704742</v>
       </c>
       <c r="F21">
-        <v>7.368272042783034</v>
+        <v>7.212958587728428</v>
       </c>
       <c r="G21">
-        <v>0.5812020523862538</v>
+        <v>0.6746588708901174</v>
       </c>
       <c r="H21">
-        <v>92.78356091249555</v>
+        <v>92.3536313836119</v>
       </c>
       <c r="I21">
-        <v>2.224377005219218</v>
+        <v>1.953030866011956</v>
       </c>
       <c r="J21">
-        <v>1.951645275174857</v>
+        <v>1.745048300627772</v>
       </c>
       <c r="K21">
-        <v>2.967019381298149</v>
+        <v>3.238669944709621</v>
       </c>
       <c r="L21">
-        <v>55.86793099494454</v>
+        <v>56.56348469543367</v>
       </c>
       <c r="M21">
-        <v>3.780829140915833</v>
+        <v>3.923107143283765</v>
       </c>
       <c r="N21">
-        <v>60.00670126132232</v>
+        <v>59.88188833375038</v>
       </c>
       <c r="O21">
-        <v>2.055983040338213</v>
+        <v>2.739736788279725</v>
       </c>
       <c r="P21">
-        <v>734.0126831224514</v>
+        <v>731.8305055954021</v>
       </c>
       <c r="Q21">
-        <v>10.38643692477492</v>
+        <v>12.7708622260959</v>
       </c>
       <c r="R21">
-        <v>3.295043266883406</v>
+        <v>3.238246131503166</v>
       </c>
       <c r="S21">
-        <v>0.329032409824808</v>
+        <v>0.3755698910833398</v>
       </c>
       <c r="T21">
-        <v>41.52273532145119</v>
+        <v>41.69614665204416</v>
       </c>
       <c r="U21">
-        <v>1.185142268088945</v>
+        <v>1.227812277251108</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -7540,64 +7540,64 @@
         <v>2040</v>
       </c>
       <c r="B22">
-        <v>73.34447360002353</v>
+        <v>73.78692225142612</v>
       </c>
       <c r="C22">
-        <v>4.45331822297246</v>
+        <v>4.610673252253872</v>
       </c>
       <c r="D22">
-        <v>993.3094371996693</v>
+        <v>998.1011860486436</v>
       </c>
       <c r="E22">
-        <v>11.85717207895846</v>
+        <v>15.59333503377854</v>
       </c>
       <c r="F22">
-        <v>7.352202935097779</v>
+        <v>7.463669480957143</v>
       </c>
       <c r="G22">
-        <v>0.6517551313542057</v>
+        <v>0.6256049088259888</v>
       </c>
       <c r="H22">
-        <v>100.1357638475933</v>
+        <v>99.81730086456905</v>
       </c>
       <c r="I22">
-        <v>2.34345612074575</v>
+        <v>1.994421218874057</v>
       </c>
       <c r="J22">
-        <v>1.655007560405082</v>
+        <v>2.421022764111095</v>
       </c>
       <c r="K22">
-        <v>2.465807889862182</v>
+        <v>3.537262510295854</v>
       </c>
       <c r="L22">
-        <v>57.52293855534961</v>
+        <v>58.98450745954476</v>
       </c>
       <c r="M22">
-        <v>4.024215085498647</v>
+        <v>4.144680873155503</v>
       </c>
       <c r="N22">
-        <v>61.8581029570726</v>
+        <v>62.0960207486801</v>
       </c>
       <c r="O22">
-        <v>2.061325382092866</v>
+        <v>2.661711440231772</v>
       </c>
       <c r="P22">
-        <v>795.870786079524</v>
+        <v>793.9265263440823</v>
       </c>
       <c r="Q22">
-        <v>10.76065074208508</v>
+        <v>13.78999497599116</v>
       </c>
       <c r="R22">
-        <v>3.417944860063586</v>
+        <v>3.317771990564613</v>
       </c>
       <c r="S22">
-        <v>0.3859950034421889</v>
+        <v>0.4098642837762938</v>
       </c>
       <c r="T22">
-        <v>44.94068018151476</v>
+        <v>45.01391864260878</v>
       </c>
       <c r="U22">
-        <v>1.222727344853583</v>
+        <v>1.304788383796971</v>
       </c>
     </row>
   </sheetData>
